--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-10 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-14 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-10</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_LIFECYCLE.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_LIFECYCLE.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10003,7 +10003,7 @@
       </c>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11026,7 +11026,7 @@
       </c>
       <c r="M170" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12921,7 +12921,7 @@
       </c>
       <c r="M199" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_LIFECYCLE.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · GA↔CRM identity 커버리지 종속</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · GA↔CRM identity 커버리지 종속</t>
         </is>
       </c>
     </row>
@@ -14149,7 +14149,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-10</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -17271,7 +17271,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-10</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -21163,7 +21163,7 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -21253,7 +21253,7 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -21343,7 +21343,7 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.JOIN_DATE</t>
+          <t>FACT_MEMBER_EVENT.JOIN_DATE</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr"/>
@@ -22266,7 +22266,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_DATE</t>
+          <t>FACT_MEMBER_EVENT.STOP_DATE</t>
         </is>
       </c>
       <c r="H118" s="4" t="inlineStr"/>
@@ -22696,7 +22696,7 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>SV metric — 누계 = base 의 YTD running sum (P7·물리 미저장) · base: FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
+          <t>SV metric — 누계 = base 의 YTD running sum (P7·물리 미저장) · base: FACT_MEMBER_EVENT.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -23021,7 +23021,7 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr"/>
@@ -23467,7 +23467,7 @@
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.UNPAID_STOP_MEMBERS</t>
+          <t>FACT_MEMBER_EVENT.UNPAID_STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr"/>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.UNPAID_STOP_CNT</t>
+          <t>FACT_MEMBER_EVENT.UNPAID_STOP_CNT</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr"/>
@@ -26784,7 +26784,7 @@
       </c>
       <c r="G224" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H224" s="4" t="inlineStr"/>
@@ -28101,7 +28101,7 @@
       </c>
       <c r="G255" s="4" t="inlineStr">
         <is>
-          <t>FACT_MEMBER_LIFECYCLE.STOP_MEMBERS</t>
+          <t>FACT_MEMBER_EVENT.STOP_MEMBERS</t>
         </is>
       </c>
       <c r="H255" s="4" t="inlineStr"/>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -56,17 +56,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-14 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-15 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-14</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -693,16 +693,8 @@
           <t>SV metric — 분자: DEV_CNT / 분모: GOAL_CNT</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr">
         <is>
           <t>월 개발건 / 월 회원개발목표</t>
@@ -710,12 +702,12 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -760,16 +752,8 @@
           <t>SV metric — 분자: DEV_CNT(YTD) / 분모: GOAL_CNT(YTD)</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
           <t>누계 개발건 / 누계 회원개발목표</t>
@@ -777,12 +761,12 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -827,16 +811,8 @@
           <t>SV metric — 분자: DEV_CNT(YR) / 분모: GOAL_CNT(YR)</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr">
         <is>
           <t>연 개발건 / 연 회원개발목표</t>
@@ -844,12 +820,12 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -894,16 +870,8 @@
           <t>FMM.DEV_CNT</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 회원의 CRM 개발 건 ( = 전체 후원금액 / 10,000 )</t>
@@ -911,12 +879,12 @@
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,996,977/40,054,884 (5.0%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -961,16 +929,8 @@
           <t>FMM.DEV_CNT</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr">
         <is>
           <t>GA 개발 건 ( = 전체 후원금액 / 10,000 )</t>
@@ -978,12 +938,12 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,996,977/40,054,884 (5.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1005,12 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,488/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1072,12 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,488/255,452 (94.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1139,12 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 240,488/255,452 (94.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1206,12 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1273,12 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 47,987/255,452 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -1374,14 +1334,14 @@
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L15" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1441,14 +1401,14 @@
           <t>YOUTUBE, KBS, 당근 등 광고를 송출하는 플랫폼</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="L16" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1504,14 +1464,14 @@
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L17" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1567,14 +1527,14 @@
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="L18" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1586,7 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -1634,14 +1594,14 @@
           <t>1) 국내 2) 해외 3) 전체 4) 통합</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="L19" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1653,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
@@ -1701,14 +1661,14 @@
           <t>1) 사례 2) 사업 3) 굿즈 4) 통합</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="L20" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1720,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -1768,14 +1728,14 @@
           <t>1) 국내 사례 2) 국내 사업 3) 해외 사례 4) 해외 굿즈 5) 전체 굿즈 6) 통합</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="L21" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1827,18 +1787,18 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="6" t="inlineStr">
+      <c r="L22" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1890,18 +1850,18 @@
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="6" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1957,14 +1917,14 @@
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="L24" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2020,14 +1980,14 @@
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="L25" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2083,14 +2043,14 @@
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="L26" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,165행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2148,12 +2108,12 @@
       <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 205,407/255,452 (80.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2171,12 @@
       <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 182,977/255,452 (71.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2234,12 @@
       <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,081/255,452 (8.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2287,7 @@
       <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr"/>
       <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="6" t="inlineStr">
+      <c r="L30" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2382,7 +2342,7 @@
       <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr"/>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L31" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2434,25 +2394,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr"/>
       <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="6" t="inlineStr">
+      <c r="L32" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2497,29 +2449,21 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr"/>
       <c r="K33" s="4" t="inlineStr">
         <is>
           <t>회원이 최초가입 시 가입캠페인</t>
         </is>
       </c>
-      <c r="L33" s="6" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2564,29 +2508,21 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I34" s="4" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr"/>
       <c r="K34" s="4" t="inlineStr">
         <is>
           <t>회원의 최종중단일자</t>
         </is>
       </c>
-      <c r="L34" s="6" t="inlineStr">
+      <c r="L34" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2631,29 +2567,21 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr"/>
       <c r="K35" s="4" t="inlineStr">
         <is>
           <t>회원이 최종중단 시 최종캠페인</t>
         </is>
       </c>
-      <c r="L35" s="6" t="inlineStr">
+      <c r="L35" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2629,7 @@
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr"/>
       <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="6" t="inlineStr">
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2756,7 +2684,7 @@
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="6" t="inlineStr">
+      <c r="L37" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2811,7 +2739,7 @@
       <c r="I38" s="4" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="6" t="inlineStr">
+      <c r="L38" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2863,16 +2791,8 @@
           <t>FME→FMM.STOP_CNT</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr"/>
       <c r="K39" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 후원중단한 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
@@ -2880,12 +2800,12 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -2930,29 +2850,21 @@
           <t>FME→FMM.UNPAID_CNT</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr"/>
       <c r="K40" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 회원상태가 미납인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -2997,29 +2909,21 @@
           <t>FMM.ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr"/>
       <c r="K41" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 회원상태가 활동인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -3064,29 +2968,21 @@
           <t>FMM.DECREASE_CNT</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr"/>
       <c r="K42" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 후원사업(세부캠페인)별 총 감액 건 ( = 전체 감액금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L42" s="7" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -3131,25 +3027,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr"/>
       <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="6" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3194,25 +3082,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I44" s="4" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr"/>
       <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="6" t="inlineStr">
+      <c r="L44" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3257,25 +3137,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr"/>
       <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="6" t="inlineStr">
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3320,25 +3192,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr"/>
       <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="6" t="inlineStr">
+      <c r="L46" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3383,25 +3247,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr"/>
       <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="6" t="inlineStr">
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3446,25 +3302,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr"/>
       <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="6" t="inlineStr">
+      <c r="L48" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3509,29 +3357,21 @@
           <t>SV metric — 분자: MONTH_END_ACTIVE_CNT / 분모: YEAR_START_ACTIVE_CNT + DEV_CNT(YTD)</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I49" s="4" t="inlineStr"/>
+      <c r="J49" s="4" t="inlineStr"/>
       <c r="K49" s="4" t="inlineStr">
         <is>
           <t>월말활동회원건 / 총 개발회원건 (연도초활동회원건 + 누계개발건)</t>
         </is>
       </c>
-      <c r="L49" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -3576,16 +3416,8 @@
           <t>SV metric — 분자: DEV_CNT(YTD) / 분모: ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr"/>
       <c r="K50" s="4" t="inlineStr">
         <is>
           <t>누계개발 건 / 활동건</t>
@@ -3593,12 +3425,12 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,996,977/40,054,884 (5.0%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -3643,29 +3475,21 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD) + YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I51" s="4" t="inlineStr"/>
+      <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
           <t>활동 건 / (누계개발 건 + 연도초활동 건)</t>
         </is>
       </c>
-      <c r="L51" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L51" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -3710,25 +3534,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I52" s="4" t="inlineStr"/>
+      <c r="J52" s="4" t="inlineStr"/>
       <c r="K52" s="4" t="inlineStr"/>
-      <c r="L52" s="6" t="inlineStr">
+      <c r="L52" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3773,16 +3589,8 @@
           <t>FMM.YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I53" s="4" t="inlineStr"/>
+      <c r="J53" s="4" t="inlineStr"/>
       <c r="K53" s="4" t="inlineStr">
         <is>
           <t>전년도 연도말 활동회원 건수</t>
@@ -3790,12 +3598,12 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 35,527,741/40,054,884 (88.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -3840,18 +3648,10 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I54" s="4" t="inlineStr"/>
+      <c r="J54" s="4" t="inlineStr"/>
       <c r="K54" s="4" t="inlineStr"/>
-      <c r="L54" s="6" t="inlineStr">
+      <c r="L54" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3903,29 +3703,21 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr"/>
       <c r="K55" s="4" t="inlineStr">
         <is>
           <t>활동, 미납1~미납5까지의 회원 포함</t>
         </is>
       </c>
-      <c r="L55" s="6" t="inlineStr">
+      <c r="L55" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3970,29 +3762,21 @@
           <t>FMM.MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I56" s="4" t="inlineStr"/>
+      <c r="J56" s="4" t="inlineStr"/>
       <c r="K56" s="4" t="inlineStr">
         <is>
           <t>월 활동회원(회원상태가 활동, 미납1~미납5)의 전체후원사업금액 / 10,000</t>
         </is>
       </c>
-      <c r="L56" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L56" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4037,25 +3821,17 @@
           <t>FMM.PREV_MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I57" s="4" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr"/>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 37,695,312/40,054,884 (94.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4100,16 +3876,8 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT + YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr"/>
       <c r="K58" s="4" t="inlineStr">
         <is>
           <t>중단(건) / (개발(건) + 연도초활동회원(건))</t>
@@ -4117,12 +3885,12 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4167,16 +3935,8 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr"/>
       <c r="K59" s="4" t="inlineStr">
         <is>
           <t>중단(건) / 개발(건)</t>
@@ -4184,12 +3944,12 @@
       </c>
       <c r="L59" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4234,16 +3994,8 @@
           <t>SV metric — 분자: STOP_CNT[신규] / 분모: DEV_CNT[신규] + PREV_MONTH_END_ACTIVE_CNT[신규]</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I60" s="4" t="inlineStr"/>
+      <c r="J60" s="4" t="inlineStr"/>
       <c r="K60" s="4" t="inlineStr">
         <is>
           <t>신규중단(건) / (당월 신규개발(건) + 전월말 신규활동회원건)</t>
@@ -4251,12 +4003,12 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4053,8 @@
           <t>SV metric — 분자: STOP_CNT[기존] / 분모: DEV_CNT[기존] + PREV_MONTH_END_ACTIVE_CNT[기존]</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I61" s="4" t="inlineStr"/>
+      <c r="J61" s="4" t="inlineStr"/>
       <c r="K61" s="4" t="inlineStr">
         <is>
           <t>기존중단(건) / (당월 기존개발(건) + 전월말 기존활동회원건)</t>
@@ -4318,12 +4062,12 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4368,16 +4112,8 @@
           <t>SV metric — 분자: STOP_CNT(주합) / 분모: 주간 일수(DIM_DATE)</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I62" s="4" t="inlineStr"/>
+      <c r="J62" s="4" t="inlineStr"/>
       <c r="K62" s="4" t="inlineStr">
         <is>
           <t>해당주간 총 중단건수 / 해당 주간 일수</t>
@@ -4385,12 +4121,12 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,038,262/4,633,105 (22.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4178,7 @@
           <t>(당해년도 전주/전월/전년 수치 − 전주/전월/전년 수치)</t>
         </is>
       </c>
-      <c r="L63" s="6" t="inlineStr">
+      <c r="L63" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4501,7 +4237,7 @@
           <t>(당해년도 전주/전월/전년 수치 − 전주/전월/전년 수치) / (전주/전월/전년 수치) * 100</t>
         </is>
       </c>
-      <c r="L64" s="6" t="inlineStr">
+      <c r="L64" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4553,29 +4289,21 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: ACTIVE_MEMBERS</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I65" s="4" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr"/>
       <c r="K65" s="4" t="inlineStr">
         <is>
           <t>활동회원 건 / 활동회원 명</t>
         </is>
       </c>
-      <c r="L65" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4620,16 +4348,8 @@
           <t>SV metric — 분자: PAID_FEE / 분모: ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J66" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I66" s="4" t="inlineStr"/>
+      <c r="J66" s="4" t="inlineStr"/>
       <c r="K66" s="4" t="inlineStr">
         <is>
           <t>납입회비 원 / (활동회원 건 * 10,000)</t>
@@ -4637,12 +4357,12 @@
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4687,16 +4407,8 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: ACTIVE_CUM_CNT ×10000</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I67" s="4" t="inlineStr"/>
+      <c r="J67" s="4" t="inlineStr"/>
       <c r="K67" s="4" t="inlineStr">
         <is>
           <t>누계납입회비 원 / (누계 활동회원 건 * 10,000)</t>
@@ -4704,12 +4416,12 @@
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4754,16 +4466,8 @@
           <t>SV metric — 분자: PAID_FEE / 분모: BILLED_AMT</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I68" s="4" t="inlineStr"/>
+      <c r="J68" s="4" t="inlineStr"/>
       <c r="K68" s="4" t="inlineStr">
         <is>
           <t>(납입회비 원 / 청구회비 원) * 100</t>
@@ -4771,12 +4475,12 @@
       </c>
       <c r="L68" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4821,16 +4525,8 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: BILLED_AMT(YTD)</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I69" s="4" t="inlineStr"/>
+      <c r="J69" s="4" t="inlineStr"/>
       <c r="K69" s="4" t="inlineStr">
         <is>
           <t>(누계납부회비 원 / 누계 청구회비 원) * 100</t>
@@ -4838,12 +4534,12 @@
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4888,25 +4584,17 @@
           <t>FMM.REGULAR_FEE</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I70" s="4" t="inlineStr"/>
+      <c r="J70" s="4" t="inlineStr"/>
       <c r="K70" s="4" t="inlineStr"/>
       <c r="L70" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 35,433,288/40,054,884 (88.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -4951,22 +4639,14 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
-        </is>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I71" s="4" t="inlineStr"/>
+      <c r="J71" s="4" t="inlineStr"/>
       <c r="K71" s="4" t="inlineStr">
         <is>
           <t>정기회원이 정기후원사업 외 비지정(기타, 국내사업, 해외사업)으로 납부하는 일시회비</t>
         </is>
       </c>
-      <c r="L71" s="6" t="inlineStr">
+      <c r="L71" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5018,22 +4698,14 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
-        </is>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I72" s="4" t="inlineStr"/>
+      <c r="J72" s="4" t="inlineStr"/>
       <c r="K72" s="4" t="inlineStr">
         <is>
           <t>일시회원이 납부하는 회비</t>
         </is>
       </c>
-      <c r="L72" s="6" t="inlineStr">
+      <c r="L72" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5085,25 +4757,17 @@
           <t>FMM.PAID_FEE</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I73" s="4" t="inlineStr"/>
+      <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr"/>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5148,25 +4812,17 @@
           <t>FMM.PAID_FEE</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I74" s="4" t="inlineStr"/>
+      <c r="J74" s="4" t="inlineStr"/>
       <c r="K74" s="4" t="inlineStr"/>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5211,25 +4867,17 @@
           <t>FMM.BILLED_AMT</t>
         </is>
       </c>
-      <c r="I75" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
-        </is>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I75" s="4" t="inlineStr"/>
+      <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr"/>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 37,148,525/40,054,884 (92.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5281,7 +4929,7 @@
           <t>조회년월 기준 후원 약정금액 ( = 개발된 후원사업별 금액 ) / 10,000원</t>
         </is>
       </c>
-      <c r="L76" s="6" t="inlineStr">
+      <c r="L76" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5340,7 +4988,7 @@
           <t>조회년월 기준 후원 약정금액 ( = 개발된 후원사업별 금액 ) / 10,000원</t>
         </is>
       </c>
-      <c r="L77" s="6" t="inlineStr">
+      <c r="L77" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5399,7 +5047,7 @@
           <t>캠페인 가입일자부터 조회년월까지의 기간을 개월 기준으로, 년 기준으로 구분</t>
         </is>
       </c>
-      <c r="L78" s="6" t="inlineStr">
+      <c r="L78" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5458,7 +5106,7 @@
           <t>캠페인 가입일자부터 조회년월까지의 기간을 개월 기준으로, 년 기준으로 구분</t>
         </is>
       </c>
-      <c r="L79" s="6" t="inlineStr">
+      <c r="L79" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5510,29 +5158,21 @@
           <t>SV metric — 분자: UNPAID_CNT / 분모: ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I80" s="4" t="inlineStr"/>
+      <c r="J80" s="4" t="inlineStr"/>
       <c r="K80" s="4" t="inlineStr">
         <is>
           <t>미납(건) / 활동(건)</t>
         </is>
       </c>
-      <c r="L80" s="7" t="inlineStr">
+      <c r="L80" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5577,29 +5217,21 @@
           <t>SV metric — 분자: UNPAID_CNT[신규] / 분모: ACTIVE_CNT[신규]</t>
         </is>
       </c>
-      <c r="I81" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I81" s="4" t="inlineStr"/>
+      <c r="J81" s="4" t="inlineStr"/>
       <c r="K81" s="4" t="inlineStr">
         <is>
           <t>신규미납(건) / 신규활동(건)</t>
         </is>
       </c>
-      <c r="L81" s="7" t="inlineStr">
+      <c r="L81" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5644,29 +5276,21 @@
           <t>SV metric — 분자: UNPAID_CNT[기존] / 분모: ACTIVE_CNT[기존]</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I82" s="4" t="inlineStr"/>
+      <c r="J82" s="4" t="inlineStr"/>
       <c r="K82" s="4" t="inlineStr">
         <is>
           <t>기존미납(건) / 기존활동(건)</t>
         </is>
       </c>
-      <c r="L82" s="7" t="inlineStr">
+      <c r="L82" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5711,29 +5335,21 @@
           <t>SV metric — 분자: UNPAID_CNT / 분모: ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I83" s="4" t="inlineStr"/>
+      <c r="J83" s="4" t="inlineStr"/>
       <c r="K83" s="4" t="inlineStr">
         <is>
           <t>후원사업 미납(건) / 후원사업 활동(건)</t>
         </is>
       </c>
-      <c r="L83" s="7" t="inlineStr">
+      <c r="L83" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5401,7 @@
           <t>(월초미납명수 − 월말미납명수) / 월초미납명수</t>
         </is>
       </c>
-      <c r="L84" s="6" t="inlineStr">
+      <c r="L84" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5844,7 +5460,7 @@
           <t>납입회원(명) / 미납서비스 클릭회원(명) * 100</t>
         </is>
       </c>
-      <c r="L85" s="5" t="inlineStr">
+      <c r="L85" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5896,29 +5512,21 @@
           <t>DIM_REASON</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr">
-        <is>
-          <t>CRM_CODE.DTL_CD_ID</t>
-        </is>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD</t>
-        </is>
-      </c>
+      <c r="I86" s="4" t="inlineStr"/>
+      <c r="J86" s="4" t="inlineStr"/>
       <c r="K86" s="4" t="inlineStr">
         <is>
           <t>CRM &gt; 회원요약정보 &gt; 회비내역 &gt; 미납/환급정보 &gt; 미납내역</t>
         </is>
       </c>
-      <c r="L86" s="6" t="inlineStr">
+      <c r="L86" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,854행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -5963,29 +5571,21 @@
           <t>FMM.CAMPAIGN_UNPAID_CNT</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J87" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I87" s="4" t="inlineStr"/>
+      <c r="J87" s="4" t="inlineStr"/>
       <c r="K87" s="4" t="inlineStr">
         <is>
           <t>캠페인별 미납회비금액 / 10,000원</t>
         </is>
       </c>
-      <c r="L87" s="7" t="inlineStr">
+      <c r="L87" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6030,22 +5630,14 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
-        </is>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I88" s="4" t="inlineStr"/>
+      <c r="J88" s="4" t="inlineStr"/>
       <c r="K88" s="4" t="inlineStr">
         <is>
           <t>회원상태별 미납회비금액 / 10,000원</t>
         </is>
       </c>
-      <c r="L88" s="6" t="inlineStr">
+      <c r="L88" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6097,29 +5689,21 @@
           <t>FSE.SEND_MEMBERS</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I89" s="4" t="inlineStr"/>
+      <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L89" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L89" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 38,467,142/38,467,142 (100.0%)</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6164,16 +5748,8 @@
           <t>FSE.SUCCESS_MEMBERS</t>
         </is>
       </c>
-      <c r="I90" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
-        </is>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
-        </is>
-      </c>
+      <c r="I90" s="4" t="inlineStr"/>
+      <c r="J90" s="4" t="inlineStr"/>
       <c r="K90" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
@@ -6181,12 +5757,12 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 24,263,968/38,467,142 (63.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6231,16 +5807,8 @@
           <t>FSE.FAIL_MEMBERS</t>
         </is>
       </c>
-      <c r="I91" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
-        </is>
-      </c>
+      <c r="I91" s="4" t="inlineStr"/>
+      <c r="J91" s="4" t="inlineStr"/>
       <c r="K91" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
@@ -6248,12 +5816,12 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 1,986,871/38,467,142 (5.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6298,29 +5866,21 @@
           <t>FSE.LETTER_PART_MEMBERS</t>
         </is>
       </c>
-      <c r="I92" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
-        </is>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
-        </is>
-      </c>
+      <c r="I92" s="4" t="inlineStr"/>
+      <c r="J92" s="4" t="inlineStr"/>
       <c r="K92" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L92" s="7" t="inlineStr">
+      <c r="L92" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.LETTER_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6368,7 +5928,7 @@
       <c r="I93" s="4" t="inlineStr"/>
       <c r="J93" s="4" t="inlineStr"/>
       <c r="K93" s="4" t="inlineStr"/>
-      <c r="L93" s="6" t="inlineStr">
+      <c r="L93" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6420,29 +5980,21 @@
           <t>FSE.GIFT_PART_MEMBERS</t>
         </is>
       </c>
-      <c r="I94" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
-        </is>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I94" s="4" t="inlineStr"/>
+      <c r="J94" s="4" t="inlineStr"/>
       <c r="K94" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L94" s="7" t="inlineStr">
+      <c r="L94" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.GIFT_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6487,25 +6039,17 @@
           <t>FSE.GIFT_PART_AMT</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
-        </is>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I95" s="4" t="inlineStr"/>
+      <c r="J95" s="4" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr"/>
-      <c r="L95" s="7" t="inlineStr">
+      <c r="L95" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.GIFT_PART_AMT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6097,7 @@
       <c r="I96" s="4" t="inlineStr"/>
       <c r="J96" s="4" t="inlineStr"/>
       <c r="K96" s="4" t="inlineStr"/>
-      <c r="L96" s="5" t="inlineStr">
+      <c r="L96" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6608,7 +6152,7 @@
       <c r="I97" s="4" t="inlineStr"/>
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr"/>
-      <c r="L97" s="5" t="inlineStr">
+      <c r="L97" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6663,7 +6207,7 @@
       <c r="I98" s="4" t="inlineStr"/>
       <c r="J98" s="4" t="inlineStr"/>
       <c r="K98" s="4" t="inlineStr"/>
-      <c r="L98" s="5" t="inlineStr">
+      <c r="L98" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6718,7 +6262,7 @@
       <c r="I99" s="4" t="inlineStr"/>
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr"/>
-      <c r="L99" s="5" t="inlineStr">
+      <c r="L99" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6773,7 +6317,7 @@
       <c r="I100" s="4" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr"/>
       <c r="K100" s="4" t="inlineStr"/>
-      <c r="L100" s="5" t="inlineStr">
+      <c r="L100" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6827,7 +6371,7 @@
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>BIGQUERY_EVENT.GA_SESSION_ID</t>
+          <t>BIGQUERY_EVENT.BIGQUERY_SESSION_ID</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
@@ -6838,12 +6382,12 @@
       <c r="K101" s="4" t="inlineStr"/>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 151,564/151,564 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6891,14 +6435,14 @@
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr"/>
       <c r="K102" s="4" t="inlineStr"/>
-      <c r="L102" s="7" t="inlineStr">
+      <c r="L102" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.AVG_SESSION_DURATION` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6958,14 +6502,14 @@
           <t>member_id가 (not set)이 아닌 데이터</t>
         </is>
       </c>
-      <c r="L103" s="5" t="inlineStr">
+      <c r="L103" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 7,223행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7025,14 +6569,14 @@
           <t>후원b1, 후원b2, 1단_대문, 퀵버튼 등</t>
         </is>
       </c>
-      <c r="L104" s="5" t="inlineStr">
+      <c r="L104" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 7,223행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7092,14 +6636,14 @@
           <t>member_id가 (not set)이 아닌 데이터</t>
         </is>
       </c>
-      <c r="L105" s="5" t="inlineStr">
+      <c r="L105" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 7,223행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7151,7 +6695,7 @@
       </c>
       <c r="J106" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr">
@@ -7159,14 +6703,14 @@
           <t>2024 기념일 캠페인 / 2024 ACL 등</t>
         </is>
       </c>
-      <c r="L106" s="5" t="inlineStr">
+      <c r="L106" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7226,14 +6770,14 @@
           <t>기부금영수증 인쇄 / 로그인하기 / 전체메뉴보기 등</t>
         </is>
       </c>
-      <c r="L107" s="5" t="inlineStr">
+      <c r="L107" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 208행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7289,14 +6833,14 @@
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr"/>
-      <c r="L108" s="5" t="inlineStr">
+      <c r="L108" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 208행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7344,7 +6888,7 @@
       <c r="I109" s="4" t="inlineStr"/>
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr"/>
-      <c r="L109" s="5" t="inlineStr">
+      <c r="L109" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7403,7 +6947,7 @@
           <t>예) https://m.goodneighbors.kr/campaign/turn25b</t>
         </is>
       </c>
-      <c r="L110" s="5" t="inlineStr">
+      <c r="L110" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7468,12 +7012,12 @@
       <c r="K111" s="4" t="inlineStr"/>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 30,323/151,564 (20.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -7521,14 +7065,14 @@
       <c r="I112" s="4" t="inlineStr"/>
       <c r="J112" s="4" t="inlineStr"/>
       <c r="K112" s="4" t="inlineStr"/>
-      <c r="L112" s="7" t="inlineStr">
+      <c r="L112" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.BOUNCE_RATE` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -7584,14 +7128,14 @@
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr"/>
-      <c r="L113" s="5" t="inlineStr">
+      <c r="L113" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 208행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7647,14 +7191,14 @@
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr"/>
-      <c r="L114" s="6" t="inlineStr">
+      <c r="L114" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,763,066행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7710,14 +7254,14 @@
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr"/>
-      <c r="L115" s="6" t="inlineStr">
+      <c r="L115" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,763,066행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7773,14 +7317,14 @@
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr"/>
-      <c r="L116" s="5" t="inlineStr">
+      <c r="L116" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,763,066행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7825,29 +7369,21 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I117" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I117" s="4" t="inlineStr"/>
+      <c r="J117" s="4" t="inlineStr"/>
       <c r="K117" s="4" t="inlineStr">
         <is>
           <t>신규: 당해년도 개발, 기존: 당해년도 이전 개발</t>
         </is>
       </c>
-      <c r="L117" s="6" t="inlineStr">
+      <c r="L117" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7903,14 +7439,14 @@
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr"/>
-      <c r="L118" s="6" t="inlineStr">
+      <c r="L118" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7966,14 +7502,14 @@
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr"/>
-      <c r="L119" s="6" t="inlineStr">
+      <c r="L119" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8029,14 +7565,14 @@
         </is>
       </c>
       <c r="K120" s="4" t="inlineStr"/>
-      <c r="L120" s="6" t="inlineStr">
+      <c r="L120" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M120" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8088,18 +7624,18 @@
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr"/>
-      <c r="L121" s="6" t="inlineStr">
+      <c r="L121" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8151,18 +7687,18 @@
       </c>
       <c r="J122" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr"/>
-      <c r="L122" s="6" t="inlineStr">
+      <c r="L122" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8214,18 +7750,18 @@
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr"/>
-      <c r="L123" s="6" t="inlineStr">
+      <c r="L123" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8277,18 +7813,18 @@
       </c>
       <c r="J124" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr"/>
-      <c r="L124" s="6" t="inlineStr">
+      <c r="L124" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8336,7 +7872,7 @@
       <c r="I125" s="4" t="inlineStr"/>
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr"/>
-      <c r="L125" s="6" t="inlineStr">
+      <c r="L125" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8403,7 +7939,7 @@
           <t>"페이지 경로+쿼리 문자열"에서 파생. URL에서 childnum= 뒤에 오는 13자리. 예) https://gni.kr/url/25acl_25ABC.gn?memnum=1831636&amp;childnum=CMR-0102-002758 → 결연아동코드 = CMR-0102-002758</t>
         </is>
       </c>
-      <c r="L126" s="5" t="inlineStr">
+      <c r="L126" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -8466,14 +8002,14 @@
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr"/>
-      <c r="L127" s="6" t="inlineStr">
+      <c r="L127" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_SPONSORSHIP` 51행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8533,14 +8069,14 @@
           <t>국내사단(국내아동권리보호사업(사단법인), 결식아동지원, 아동학대예방, 저소득가정지원), 국내사복(국내아동권리보호사업(사회복지법인), 국내사업, 좋은이웃(사복)), 결연(해외아동결연), 해외구호(희망학교지원사업, 해외교육지원사업, 보건의료지원사업, 식수위생지원사업, 재난구호지원사업, 해외지역개발지원사업), 기타(대북지원사업, 좋은이웃, 전체사업지원)</t>
         </is>
       </c>
-      <c r="L128" s="6" t="inlineStr">
+      <c r="L128" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_SPONSORSHIP` 51행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8585,25 +8121,17 @@
           <t>DIM_PAYMENT</t>
         </is>
       </c>
-      <c r="I129" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
-        </is>
-      </c>
-      <c r="J129" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
-        </is>
-      </c>
+      <c r="I129" s="4" t="inlineStr"/>
+      <c r="J129" s="4" t="inlineStr"/>
       <c r="K129" s="4" t="inlineStr"/>
-      <c r="L129" s="6" t="inlineStr">
+      <c r="L129" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_PAYMENT` 7행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8648,25 +8176,17 @@
           <t>DIM_PAYMENT</t>
         </is>
       </c>
-      <c r="I130" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
-        </is>
-      </c>
-      <c r="J130" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
-        </is>
-      </c>
+      <c r="I130" s="4" t="inlineStr"/>
+      <c r="J130" s="4" t="inlineStr"/>
       <c r="K130" s="4" t="inlineStr"/>
-      <c r="L130" s="6" t="inlineStr">
+      <c r="L130" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_PAYMENT` 7행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8234,7 @@
       <c r="I131" s="4" t="inlineStr"/>
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr"/>
-      <c r="L131" s="6" t="inlineStr">
+      <c r="L131" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8769,7 +8289,7 @@
       <c r="I132" s="4" t="inlineStr"/>
       <c r="J132" s="4" t="inlineStr"/>
       <c r="K132" s="4" t="inlineStr"/>
-      <c r="L132" s="6" t="inlineStr">
+      <c r="L132" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8824,7 +8344,7 @@
       <c r="I133" s="4" t="inlineStr"/>
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr"/>
-      <c r="L133" s="6" t="inlineStr">
+      <c r="L133" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8876,25 +8396,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I134" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J134" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I134" s="4" t="inlineStr"/>
+      <c r="J134" s="4" t="inlineStr"/>
       <c r="K134" s="4" t="inlineStr"/>
-      <c r="L134" s="6" t="inlineStr">
+      <c r="L134" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8939,25 +8451,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I135" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J135" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I135" s="4" t="inlineStr"/>
+      <c r="J135" s="4" t="inlineStr"/>
       <c r="K135" s="4" t="inlineStr"/>
-      <c r="L135" s="6" t="inlineStr">
+      <c r="L135" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9002,25 +8506,17 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I136" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER.MBER_STAT_CD</t>
-        </is>
-      </c>
-      <c r="J136" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
-        </is>
-      </c>
+      <c r="I136" s="4" t="inlineStr"/>
+      <c r="J136" s="4" t="inlineStr"/>
       <c r="K136" s="4" t="inlineStr"/>
-      <c r="L136" s="6" t="inlineStr">
+      <c r="L136" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,763,065행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9065,25 +8561,17 @@
           <t>DIM_SERVICE</t>
         </is>
       </c>
-      <c r="I137" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
-        </is>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I137" s="4" t="inlineStr"/>
+      <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr"/>
-      <c r="L137" s="6" t="inlineStr">
+      <c r="L137" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9128,25 +8616,17 @@
           <t>DIM_SERVICE</t>
         </is>
       </c>
-      <c r="I138" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
-        </is>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I138" s="4" t="inlineStr"/>
+      <c r="J138" s="4" t="inlineStr"/>
       <c r="K138" s="4" t="inlineStr"/>
-      <c r="L138" s="6" t="inlineStr">
+      <c r="L138" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9191,25 +8671,17 @@
           <t>DIM_SERVICE</t>
         </is>
       </c>
-      <c r="I139" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
-        </is>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I139" s="4" t="inlineStr"/>
+      <c r="J139" s="4" t="inlineStr"/>
       <c r="K139" s="4" t="inlineStr"/>
-      <c r="L139" s="6" t="inlineStr">
+      <c r="L139" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9257,7 +8729,7 @@
       <c r="I140" s="4" t="inlineStr"/>
       <c r="J140" s="4" t="inlineStr"/>
       <c r="K140" s="4" t="inlineStr"/>
-      <c r="L140" s="6" t="inlineStr">
+      <c r="L140" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9312,14 +8784,14 @@
       <c r="I141" s="4" t="inlineStr"/>
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr"/>
-      <c r="L141" s="6" t="inlineStr">
+      <c r="L141" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M141" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_DATE` 16,437행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9367,7 +8839,7 @@
       <c r="I142" s="4" t="inlineStr"/>
       <c r="J142" s="4" t="inlineStr"/>
       <c r="K142" s="4" t="inlineStr"/>
-      <c r="L142" s="6" t="inlineStr">
+      <c r="L142" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9422,7 +8894,7 @@
       <c r="I143" s="4" t="inlineStr"/>
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr"/>
-      <c r="L143" s="6" t="inlineStr">
+      <c r="L143" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9477,7 +8949,7 @@
       <c r="I144" s="4" t="inlineStr"/>
       <c r="J144" s="4" t="inlineStr"/>
       <c r="K144" s="4" t="inlineStr"/>
-      <c r="L144" s="6" t="inlineStr">
+      <c r="L144" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9532,7 +9004,7 @@
       <c r="I145" s="4" t="inlineStr"/>
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr"/>
-      <c r="L145" s="6" t="inlineStr">
+      <c r="L145" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9587,7 +9059,7 @@
       <c r="I146" s="4" t="inlineStr"/>
       <c r="J146" s="4" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr"/>
-      <c r="L146" s="6" t="inlineStr">
+      <c r="L146" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9642,7 +9114,7 @@
       <c r="I147" s="4" t="inlineStr"/>
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr"/>
-      <c r="L147" s="6" t="inlineStr">
+      <c r="L147" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9697,7 +9169,7 @@
       <c r="I148" s="4" t="inlineStr"/>
       <c r="J148" s="4" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr"/>
-      <c r="L148" s="6" t="inlineStr">
+      <c r="L148" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9752,7 +9224,7 @@
       <c r="I149" s="4" t="inlineStr"/>
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr"/>
-      <c r="L149" s="6" t="inlineStr">
+      <c r="L149" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9807,7 +9279,7 @@
       <c r="I150" s="4" t="inlineStr"/>
       <c r="J150" s="4" t="inlineStr"/>
       <c r="K150" s="4" t="inlineStr"/>
-      <c r="L150" s="6" t="inlineStr">
+      <c r="L150" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9866,18 +9338,18 @@
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr"/>
-      <c r="L151" s="6" t="inlineStr">
+      <c r="L151" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9922,25 +9394,17 @@
           <t>FME→FMM.DEV_MEMBERS</t>
         </is>
       </c>
-      <c r="I152" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I152" s="4" t="inlineStr"/>
+      <c r="J152" s="4" t="inlineStr"/>
       <c r="K152" s="4" t="inlineStr"/>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -9985,25 +9449,17 @@
           <t>FME→FMM.DEV_CNT</t>
         </is>
       </c>
-      <c r="I153" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I153" s="4" t="inlineStr"/>
+      <c r="J153" s="4" t="inlineStr"/>
       <c r="K153" s="4" t="inlineStr"/>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -10048,25 +9504,17 @@
           <t>FME→FMM.INCREASE_MEMBERS</t>
         </is>
       </c>
-      <c r="I154" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I154" s="4" t="inlineStr"/>
+      <c r="J154" s="4" t="inlineStr"/>
       <c r="K154" s="4" t="inlineStr"/>
-      <c r="L154" s="7" t="inlineStr">
+      <c r="L154" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -10111,25 +9559,17 @@
           <t>FME→FMM.INCREASE_CNT</t>
         </is>
       </c>
-      <c r="I155" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I155" s="4" t="inlineStr"/>
+      <c r="J155" s="4" t="inlineStr"/>
       <c r="K155" s="4" t="inlineStr"/>
-      <c r="L155" s="7" t="inlineStr">
+      <c r="L155" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -10177,7 +9617,7 @@
       <c r="I156" s="4" t="inlineStr"/>
       <c r="J156" s="4" t="inlineStr"/>
       <c r="K156" s="4" t="inlineStr"/>
-      <c r="L156" s="7" t="inlineStr">
+      <c r="L156" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -10232,7 +9672,7 @@
       <c r="I157" s="4" t="inlineStr"/>
       <c r="J157" s="4" t="inlineStr"/>
       <c r="K157" s="4" t="inlineStr"/>
-      <c r="L157" s="7" t="inlineStr">
+      <c r="L157" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -10287,7 +9727,7 @@
       <c r="I158" s="4" t="inlineStr"/>
       <c r="J158" s="4" t="inlineStr"/>
       <c r="K158" s="4" t="inlineStr"/>
-      <c r="L158" s="7" t="inlineStr">
+      <c r="L158" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -10342,7 +9782,7 @@
       <c r="I159" s="4" t="inlineStr"/>
       <c r="J159" s="4" t="inlineStr"/>
       <c r="K159" s="4" t="inlineStr"/>
-      <c r="L159" s="7" t="inlineStr">
+      <c r="L159" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -10394,25 +9834,17 @@
           <t>FMM.ACTIVE_MEMBERS</t>
         </is>
       </c>
-      <c r="I160" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I160" s="4" t="inlineStr"/>
+      <c r="J160" s="4" t="inlineStr"/>
       <c r="K160" s="4" t="inlineStr"/>
-      <c r="L160" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L160" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 38,423,126/40,054,884 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -10457,25 +9889,17 @@
           <t>FMM.ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I161" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I161" s="4" t="inlineStr"/>
+      <c r="J161" s="4" t="inlineStr"/>
       <c r="K161" s="4" t="inlineStr"/>
-      <c r="L161" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L161" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -10520,18 +9944,10 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I162" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
-        </is>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I162" s="4" t="inlineStr"/>
+      <c r="J162" s="4" t="inlineStr"/>
       <c r="K162" s="4" t="inlineStr"/>
-      <c r="L162" s="6" t="inlineStr">
+      <c r="L162" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10583,25 +9999,17 @@
           <t>FMM.ACTIVE_CUM_CNT</t>
         </is>
       </c>
-      <c r="I163" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J163" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I163" s="4" t="inlineStr"/>
+      <c r="J163" s="4" t="inlineStr"/>
       <c r="K163" s="4" t="inlineStr"/>
-      <c r="L163" s="7" t="inlineStr">
+      <c r="L163" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10057,7 @@
       <c r="I164" s="4" t="inlineStr"/>
       <c r="J164" s="4" t="inlineStr"/>
       <c r="K164" s="4" t="inlineStr"/>
-      <c r="L164" s="6" t="inlineStr">
+      <c r="L164" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10704,7 +10112,7 @@
       <c r="I165" s="4" t="inlineStr"/>
       <c r="J165" s="4" t="inlineStr"/>
       <c r="K165" s="4" t="inlineStr"/>
-      <c r="L165" s="6" t="inlineStr">
+      <c r="L165" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10756,25 +10164,17 @@
           <t>DIM_REASON</t>
         </is>
       </c>
-      <c r="I166" s="4" t="inlineStr">
-        <is>
-          <t>CRM_CODE.DTL_CD_ID</t>
-        </is>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD</t>
-        </is>
-      </c>
+      <c r="I166" s="4" t="inlineStr"/>
+      <c r="J166" s="4" t="inlineStr"/>
       <c r="K166" s="4" t="inlineStr"/>
-      <c r="L166" s="6" t="inlineStr">
+      <c r="L166" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M166" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,854행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -10819,22 +10219,14 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I167" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
-        </is>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I167" s="4" t="inlineStr"/>
+      <c r="J167" s="4" t="inlineStr"/>
       <c r="K167" s="4" t="inlineStr">
         <is>
           <t>캠페인 가입 이후 납입하는 회비</t>
         </is>
       </c>
-      <c r="L167" s="6" t="inlineStr">
+      <c r="L167" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10893,7 +10285,7 @@
           <t>고유ID(회원번호×캠페인가입일×후원사업×캠페인명) 기준 매칭되는 캠페인가입일로부터 조회기준일까지의 총 개월수</t>
         </is>
       </c>
-      <c r="L168" s="6" t="inlineStr">
+      <c r="L168" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10952,7 +10344,7 @@
           <t>고유ID(회원번호×캠페인가입일×후원사업×캠페인명) 기준 매칭되는 캠페인가입일로부터 조회기준일까지의 총 년수</t>
         </is>
       </c>
-      <c r="L169" s="6" t="inlineStr">
+      <c r="L169" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11004,16 +10396,8 @@
           <t>SV metric — 분자: Σ(유지기간×DEV_MEMBERS) / 분모: DEV_MEMBERS(총)</t>
         </is>
       </c>
-      <c r="I170" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I170" s="4" t="inlineStr"/>
+      <c r="J170" s="4" t="inlineStr"/>
       <c r="K170" s="4" t="inlineStr">
         <is>
           <t>{(개발캠페인별 유지기간×해당 유지기간 총 회원수)의 합} / 캠페인 가입한 총 회원수</t>
@@ -11021,12 +10405,12 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11078,7 +10462,7 @@
           <t>{(개발캠페인별 유지기간×해당 유지기간 총 회원수)의 합} / 캠페인 가입한 총 회원수</t>
         </is>
       </c>
-      <c r="L171" s="6" t="inlineStr">
+      <c r="L171" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11137,7 +10521,7 @@
           <t>N개월 시점에 캠페인 가입유지중인 회원수 / N개월까지 가입한 회원수</t>
         </is>
       </c>
-      <c r="L172" s="6" t="inlineStr">
+      <c r="L172" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11196,7 +10580,7 @@
           <t>(N개월 시점에 캠페인 가입유지중인 회원수 / N개월까지 가입한 회원수) × 100</t>
         </is>
       </c>
-      <c r="L173" s="6" t="inlineStr">
+      <c r="L173" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11255,7 +10639,7 @@
           <t>평균 납입회비 × 평균 활동 기간</t>
         </is>
       </c>
-      <c r="L174" s="6" t="inlineStr">
+      <c r="L174" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -11314,7 +10698,7 @@
           <t>광고비(편성비) 비용 / 신규 획득 개발 건수</t>
         </is>
       </c>
-      <c r="L175" s="5" t="inlineStr">
+      <c r="L175" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -11381,14 +10765,14 @@
           <t>ERP 모금성 비용 / 신규 획득 개발 건수</t>
         </is>
       </c>
-      <c r="L176" s="7" t="inlineStr">
+      <c r="L176" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BUDGET.FUNDRAISING_COST` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_BUDGET` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11433,16 +10817,8 @@
           <t>SV metric — 분자: PAID_FEE(또는 LTV) − 비용 / 분모: 비용(FBD)</t>
         </is>
       </c>
-      <c r="I177" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J177" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I177" s="4" t="inlineStr"/>
+      <c r="J177" s="4" t="inlineStr"/>
       <c r="K177" s="4" t="inlineStr">
         <is>
           <t>(총 수익−총 비용) / 총 비용 × 100</t>
@@ -11450,12 +10826,12 @@
       </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M177" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11500,29 +10876,21 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I178" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J178" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I178" s="4" t="inlineStr"/>
+      <c r="J178" s="4" t="inlineStr"/>
       <c r="K178" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동건 / (캠페인별 개발누계건 + 캠페인별 연도초활동건)</t>
         </is>
       </c>
-      <c r="L178" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L178" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11567,29 +10935,21 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I179" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J179" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I179" s="4" t="inlineStr"/>
+      <c r="J179" s="4" t="inlineStr"/>
       <c r="K179" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인 활동건 / (캠페인 개발누계건 + 캠페인 연도초활동건)</t>
         </is>
       </c>
-      <c r="L179" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L179" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M179" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11634,29 +10994,21 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I180" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J180" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I180" s="4" t="inlineStr"/>
+      <c r="J180" s="4" t="inlineStr"/>
       <c r="K180" s="4" t="inlineStr">
         <is>
           <t>캠페인별 납입방식 활동건 / (캠페인별 납입방식 개발누계건 + 캠페인별 납입방식 연도초활동건)</t>
         </is>
       </c>
-      <c r="L180" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L180" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 38,423,117/40,054,884 (95.9%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11701,16 +11053,8 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I181" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J181" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I181" s="4" t="inlineStr"/>
+      <c r="J181" s="4" t="inlineStr"/>
       <c r="K181" s="4" t="inlineStr">
         <is>
           <t>캠페인별 중단(건) / (캠페인별 개발(건) + 캠페인별 연도초활동회원(건))</t>
@@ -11718,12 +11062,12 @@
       </c>
       <c r="L181" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M181" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11768,16 +11112,8 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT+PREV_MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I182" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J182" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I182" s="4" t="inlineStr"/>
+      <c r="J182" s="4" t="inlineStr"/>
       <c r="K182" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인 중단(건) / (캠페인 개발(건) + 캠페인 전월말활동회원(건))</t>
@@ -11785,12 +11121,12 @@
       </c>
       <c r="L182" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M182" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11835,16 +11171,8 @@
           <t>SV metric — 분자: STOP_CNT(YTD) / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I183" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J183" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I183" s="4" t="inlineStr"/>
+      <c r="J183" s="4" t="inlineStr"/>
       <c r="K183" s="4" t="inlineStr">
         <is>
           <t>캠페인별 누계중단(건) / (캠페인별 누계개발(건) + 캠페인별 연도초활동회원(건))</t>
@@ -11852,12 +11180,12 @@
       </c>
       <c r="L183" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M183" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11902,16 +11230,8 @@
           <t>SV metric — 분자: STOP_CNT(YTD) / 분모: DEV_CNT(YTD)</t>
         </is>
       </c>
-      <c r="I184" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J184" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I184" s="4" t="inlineStr"/>
+      <c r="J184" s="4" t="inlineStr"/>
       <c r="K184" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인 누계중단(건) / 캠페인별 누계개발(건)</t>
@@ -11919,12 +11239,12 @@
       </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M184" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -11969,16 +11289,8 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I185" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J185" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I185" s="4" t="inlineStr"/>
+      <c r="J185" s="4" t="inlineStr"/>
       <c r="K185" s="4" t="inlineStr">
         <is>
           <t>캠페인별 납입방식 중단(건) / (캠페인별 납입방식 개발(건) + 캠페인별 연도초활동회원(건))</t>
@@ -11986,12 +11298,12 @@
       </c>
       <c r="L185" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M185" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 972,376/40,054,884 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12036,29 +11348,21 @@
           <t>FMM.CHURN_CNT</t>
         </is>
       </c>
-      <c r="I186" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J186" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I186" s="4" t="inlineStr"/>
+      <c r="J186" s="4" t="inlineStr"/>
       <c r="K186" s="4" t="inlineStr">
         <is>
           <t>후원취소 및 감액한 후원사업의 금액 / 10,000</t>
         </is>
       </c>
-      <c r="L186" s="7" t="inlineStr">
+      <c r="L186" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M186" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12103,29 +11407,21 @@
           <t>SV metric — 분자: CHURN_CNT / 분모: DEV_CNT</t>
         </is>
       </c>
-      <c r="I187" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J187" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I187" s="4" t="inlineStr"/>
+      <c r="J187" s="4" t="inlineStr"/>
       <c r="K187" s="4" t="inlineStr">
         <is>
           <t>캠페인별 이탈(건) / 캠페인별 개발(건)</t>
         </is>
       </c>
-      <c r="L187" s="7" t="inlineStr">
+      <c r="L187" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M187" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12170,16 +11466,8 @@
           <t>SV metric — 분자: PAID_FEE / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I188" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J188" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I188" s="4" t="inlineStr"/>
+      <c r="J188" s="4" t="inlineStr"/>
       <c r="K188" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동회원의 월 납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
@@ -12187,12 +11475,12 @@
       </c>
       <c r="L188" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M188" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12237,16 +11525,8 @@
           <t>SV metric — 분자: PAID_FEE / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I189" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J189" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I189" s="4" t="inlineStr"/>
+      <c r="J189" s="4" t="inlineStr"/>
       <c r="K189" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인별 활동회원의 월 납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
@@ -12254,12 +11534,12 @@
       </c>
       <c r="L189" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M189" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12304,16 +11584,8 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I190" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J190" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I190" s="4" t="inlineStr"/>
+      <c r="J190" s="4" t="inlineStr"/>
       <c r="K190" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동회원 월 누계납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
@@ -12321,12 +11593,12 @@
       </c>
       <c r="L190" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M190" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12371,16 +11643,8 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I191" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J191" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I191" s="4" t="inlineStr"/>
+      <c r="J191" s="4" t="inlineStr"/>
       <c r="K191" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인별 활동회원 월 누계납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
@@ -12388,12 +11652,12 @@
       </c>
       <c r="L191" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M191" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12438,16 +11702,8 @@
           <t>SV metric — 분자: PAID_FEE(캠페인) / 분모: PAID_FEE(전체)</t>
         </is>
       </c>
-      <c r="I192" s="4" t="inlineStr">
-        <is>
-          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
-        </is>
-      </c>
-      <c r="J192" s="4" t="inlineStr">
-        <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I192" s="4" t="inlineStr"/>
+      <c r="J192" s="4" t="inlineStr"/>
       <c r="K192" s="4" t="inlineStr">
         <is>
           <t>캠페인별 납입회비 / 총 납입회비 금액 × 100</t>
@@ -12455,12 +11711,12 @@
       </c>
       <c r="L192" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M192" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 36,089,539/40,054,884 (90.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12505,29 +11761,21 @@
           <t>SV metric — 분자: CAMPAIGN_UNPAID_CNT ×10000 / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I193" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J193" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I193" s="4" t="inlineStr"/>
+      <c r="J193" s="4" t="inlineStr"/>
       <c r="K193" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동회원의 월 미납회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L193" s="7" t="inlineStr">
+      <c r="L193" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M193" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12572,29 +11820,21 @@
           <t>SV metric — 분자: CAMPAIGN_UNPAID_CNT ×10000 / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I194" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J194" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I194" s="4" t="inlineStr"/>
+      <c r="J194" s="4" t="inlineStr"/>
       <c r="K194" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인별 활동회원의 월 미납회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L194" s="7" t="inlineStr">
+      <c r="L194" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12639,29 +11879,21 @@
           <t>SV metric — 분자: CAMPAIGN_UNPAID_CNT(캠페인) / 분모: CAMPAIGN_UNPAID_CNT(전체)</t>
         </is>
       </c>
-      <c r="I195" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
-        </is>
-      </c>
-      <c r="J195" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
-        </is>
-      </c>
+      <c r="I195" s="4" t="inlineStr"/>
+      <c r="J195" s="4" t="inlineStr"/>
       <c r="K195" s="4" t="inlineStr">
         <is>
           <t>캠페인별 미납회비 / 총 미납회비 금액 × 100</t>
         </is>
       </c>
-      <c r="L195" s="7" t="inlineStr">
+      <c r="L195" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M195" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12706,29 +11938,21 @@
           <t>SV metric — 분자: SEND_MEMBERS / 분모: 전체회원수(명)</t>
         </is>
       </c>
-      <c r="I196" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
-        </is>
-      </c>
-      <c r="J196" s="4" t="inlineStr">
-        <is>
-          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I196" s="4" t="inlineStr"/>
+      <c r="J196" s="4" t="inlineStr"/>
       <c r="K196" s="4" t="inlineStr">
         <is>
           <t>서비스별 발송수(명) / 전체회원수(명) × 100</t>
         </is>
       </c>
-      <c r="L196" s="6" t="inlineStr">
-        <is>
-          <t>OK</t>
+      <c r="L196" s="5" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 38,467,142/38,467,142 (100.0%)</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12773,16 +11997,8 @@
           <t>SV metric — 분자: SUCCESS_MEMBERS / 분모: SEND_MEMBERS</t>
         </is>
       </c>
-      <c r="I197" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
-        </is>
-      </c>
-      <c r="J197" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
-        </is>
-      </c>
+      <c r="I197" s="4" t="inlineStr"/>
+      <c r="J197" s="4" t="inlineStr"/>
       <c r="K197" s="4" t="inlineStr">
         <is>
           <t>발송성공수(명) / 발송수(명) × 100</t>
@@ -12790,12 +12006,12 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M197" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 24,263,968/38,467,142 (63.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12847,7 +12063,7 @@
           <t>클릭수(명) / 발송수(명) × 100</t>
         </is>
       </c>
-      <c r="L198" s="5" t="inlineStr">
+      <c r="L198" s="6" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -12899,16 +12115,8 @@
           <t>SV metric — 분자: DEV_MEMBERS / 분모: BigQuery 클릭회원(명)</t>
         </is>
       </c>
-      <c r="I199" s="4" t="inlineStr">
-        <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
-        </is>
-      </c>
-      <c r="J199" s="4" t="inlineStr">
-        <is>
-          <t>TC_CMMN_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_CM_MKTNG_CMPGN_MNG;TM_CM_MKTNG_UTM;TM_MM_FDRM_MBER_DVLP_AMT</t>
-        </is>
-      </c>
+      <c r="I199" s="4" t="inlineStr"/>
+      <c r="J199" s="4" t="inlineStr"/>
       <c r="K199" s="4" t="inlineStr">
         <is>
           <t>개발회원(명) / 서비스 클릭수(명) × 100</t>
@@ -12916,12 +12124,12 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M199" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,291,878/4,633,105 (49.5%) · GA↔CRM identity 커버리지 종속</t>
+          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -12973,7 +12181,7 @@
           <t>(증액 회원수(명,건) / 서비스별 발송 성공회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L200" s="6" t="inlineStr">
+      <c r="L200" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13032,7 +12240,7 @@
           <t>(서비스별 증액 후 N개월 시점 유지 회원(명,건) / 서비스별 증액 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L201" s="6" t="inlineStr">
+      <c r="L201" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13091,7 +12299,7 @@
           <t>(서비스별 발송 후 N개월 시점 유지 회원(명,건) / 서비스별 참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L202" s="6" t="inlineStr">
+      <c r="L202" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13150,7 +12358,7 @@
           <t>(서비스별 증액회원 중 납입회원(명,건) / 서비스별 증액회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 증액회원의 납입회비) / 서비스별 증액회원(명)</t>
         </is>
       </c>
-      <c r="L203" s="6" t="inlineStr">
+      <c r="L203" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13209,7 +12417,7 @@
           <t>(서비스별 참여회원 중 납입회원(명,건) / 서비스별 참여회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 참여회원의 납입회비) / 서비스별 참여회원(명)</t>
         </is>
       </c>
-      <c r="L204" s="6" t="inlineStr">
+      <c r="L204" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13268,7 +12476,7 @@
           <t>(서비스별 증액회원 중 중단회원(명,건) / 서비스별 증액회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L205" s="6" t="inlineStr">
+      <c r="L205" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13327,7 +12535,7 @@
           <t>(서비스별 참여회원 중 중단회원(명,건) / 서비스별 참여회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L206" s="6" t="inlineStr">
+      <c r="L206" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13386,7 +12594,7 @@
           <t>(해당 캠페인 서비스별 증액회원(명,건) / 서비스별 전체 증액회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L207" s="6" t="inlineStr">
+      <c r="L207" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13445,7 +12653,7 @@
           <t>(해당 캠페인 서비스별 참여회원(명,건) / 서비스별 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L208" s="6" t="inlineStr">
+      <c r="L208" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13504,7 +12712,7 @@
           <t>(해당 서비스·캠페인 조합에서 N개월 시점 유지 회원(명,건) / 해당 캠페인 가입회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L209" s="6" t="inlineStr">
+      <c r="L209" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13556,29 +12764,21 @@
           <t>SV metric — 분자: LETTER_PART_MEMBERS / 분모: 참여회원수</t>
         </is>
       </c>
-      <c r="I210" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
-        </is>
-      </c>
-      <c r="J210" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
-        </is>
-      </c>
+      <c r="I210" s="4" t="inlineStr"/>
+      <c r="J210" s="4" t="inlineStr"/>
       <c r="K210" s="4" t="inlineStr">
         <is>
           <t>(서비스별 서신 참여회원(명,건) / 해당 서비스 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L210" s="7" t="inlineStr">
+      <c r="L210" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M210" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.LETTER_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -13630,7 +12830,7 @@
           <t>(서신참여 후 N개월 시점 유지 회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L211" s="6" t="inlineStr">
+      <c r="L211" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13689,7 +12889,7 @@
           <t>(서비스별 서신참여회원 중 납입회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 서신참여회원의 납입회비) / 서비스별 서신참여회원(명)</t>
         </is>
       </c>
-      <c r="L212" s="6" t="inlineStr">
+      <c r="L212" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13748,7 +12948,7 @@
           <t>(서비스별 서신참여회원 중 중단회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L213" s="6" t="inlineStr">
+      <c r="L213" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13807,7 +13007,7 @@
           <t>(해당 캠페인 서비스별 서신참여회원(명,건) / 서비스별 전체 서신참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L214" s="6" t="inlineStr">
+      <c r="L214" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13859,29 +13059,21 @@
           <t>SV metric — 분자: GIFT_PART_MEMBERS / 분모: 참여회원수</t>
         </is>
       </c>
-      <c r="I215" s="4" t="inlineStr">
-        <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
-        </is>
-      </c>
-      <c r="J215" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
-        </is>
-      </c>
+      <c r="I215" s="4" t="inlineStr"/>
+      <c r="J215" s="4" t="inlineStr"/>
       <c r="K215" s="4" t="inlineStr">
         <is>
           <t>(서비스별 선물금 참여회원(명,건) / 해당 서비스 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L215" s="7" t="inlineStr">
+      <c r="L215" s="5" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M215" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.GIFT_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -13933,7 +13125,7 @@
           <t>(서비스별 선물금참여 후 N개월 시점 유지 회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L216" s="6" t="inlineStr">
+      <c r="L216" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13992,7 +13184,7 @@
           <t>(서비스별 선물금참여회원 중 납입회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 선물금참여회원의 납입회비) / 서비스별 선물금참여회원수(명)</t>
         </is>
       </c>
-      <c r="L217" s="6" t="inlineStr">
+      <c r="L217" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -14051,7 +13243,7 @@
           <t>(서비스별 선물금참여회원 중 중단회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L218" s="6" t="inlineStr">
+      <c r="L218" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -14110,7 +13302,7 @@
           <t>(해당 캠페인 서비스별 선물금참여회원(명,건) / 서비스별 전체 선물금참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L219" s="6" t="inlineStr">
+      <c r="L219" s="7" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -14149,7 +13341,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-14</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -17271,7 +16463,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-14</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-15</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -56,12 +56,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -702,12 +702,12 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,729/4,716,360 (49.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,729/4,716,360 (49.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,729/4,716,360 (49.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
           <t>회원번호 기준, 회원의 CRM 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="L8" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -936,7 +936,7 @@
           <t>GA 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="L9" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 234,859/248,196 (94.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 234,859/248,196 (94.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 234,859/248,196 (94.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 176,578/248,196 (71.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 46,485/248,196 (18.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1334,14 +1334,14 @@
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="6" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1401,14 +1401,14 @@
           <t>YOUTUBE, KBS, 당근 등 광고를 송출하는 플랫폼</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1464,14 +1464,14 @@
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1527,14 +1527,14 @@
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="6" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1594,14 +1594,14 @@
           <t>1) 국내 2) 해외 3) 전체 4) 통합</t>
         </is>
       </c>
-      <c r="L19" s="6" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1661,14 +1661,14 @@
           <t>1) 사례 2) 사업 3) 굿즈 4) 통합</t>
         </is>
       </c>
-      <c r="L20" s="6" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1728,14 +1728,14 @@
           <t>1) 국내 사례 2) 국내 사업 3) 해외 사례 4) 해외 굿즈 5) 전체 굿즈 6) 통합</t>
         </is>
       </c>
-      <c r="L21" s="6" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1917,14 +1917,14 @@
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="6" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1980,14 +1980,14 @@
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
-      <c r="L25" s="6" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2043,14 +2043,14 @@
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="6" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2108,12 +2108,12 @@
       <c r="K27" s="4" t="inlineStr"/>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 199,322/248,196 (80.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 176,578/248,196 (71.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,452/248,196 (9.0%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2800,12 +2800,12 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,431/4,716,360 (22.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
           <t>회원번호 기준, 회원상태가 미납인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="L40" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -2916,7 +2916,7 @@
           <t>회원번호 기준, 회원상태가 활동인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="L41" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -2975,7 +2975,7 @@
           <t>회원번호 기준, 후원사업(세부캠페인)별 총 감액 건 ( = 전체 감액금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="L42" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3257,7 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
           <t>월말활동회원건 / 총 개발회원건 (연도초활동회원건 + 누계개발건)</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="L49" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -3423,7 +3423,7 @@
           <t>누계개발 건 / 활동건</t>
         </is>
       </c>
-      <c r="L50" s="5" t="inlineStr">
+      <c r="L50" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -3482,7 +3482,7 @@
           <t>활동 건 / (누계개발 건 + 연도초활동 건)</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr">
+      <c r="L51" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
           <t>전년도 연도말 활동회원 건수</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr">
+      <c r="L53" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3769,7 @@
           <t>월 활동회원(회원상태가 활동, 미납1~미납5)의 전체후원사업금액 / 10,000</t>
         </is>
       </c>
-      <c r="L56" s="5" t="inlineStr">
+      <c r="L56" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -3824,7 +3824,7 @@
       <c r="I57" s="4" t="inlineStr"/>
       <c r="J57" s="4" t="inlineStr"/>
       <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="5" t="inlineStr">
+      <c r="L57" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -3883,7 +3883,7 @@
           <t>중단(건) / (개발(건) + 연도초활동회원(건))</t>
         </is>
       </c>
-      <c r="L58" s="5" t="inlineStr">
+      <c r="L58" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -3942,7 +3942,7 @@
           <t>중단(건) / 개발(건)</t>
         </is>
       </c>
-      <c r="L59" s="5" t="inlineStr">
+      <c r="L59" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -4003,12 +4003,12 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,431/4,716,360 (22.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4062,12 +4062,12 @@
       </c>
       <c r="L61" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,431/4,716,360 (22.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4121,12 +4121,12 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,431/4,716,360 (22.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4296,7 +4296,7 @@
           <t>활동회원 건 / 활동회원 명</t>
         </is>
       </c>
-      <c r="L65" s="5" t="inlineStr">
+      <c r="L65" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -4355,7 +4355,7 @@
           <t>납입회비 원 / (활동회원 건 * 10,000)</t>
         </is>
       </c>
-      <c r="L66" s="5" t="inlineStr">
+      <c r="L66" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -4414,7 +4414,7 @@
           <t>누계납입회비 원 / (누계 활동회원 건 * 10,000)</t>
         </is>
       </c>
-      <c r="L67" s="5" t="inlineStr">
+      <c r="L67" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -4473,7 +4473,7 @@
           <t>(납입회비 원 / 청구회비 원) * 100</t>
         </is>
       </c>
-      <c r="L68" s="5" t="inlineStr">
+      <c r="L68" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -4532,7 +4532,7 @@
           <t>(누계납부회비 원 / 누계 청구회비 원) * 100</t>
         </is>
       </c>
-      <c r="L69" s="5" t="inlineStr">
+      <c r="L69" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -4587,7 +4587,7 @@
       <c r="I70" s="4" t="inlineStr"/>
       <c r="J70" s="4" t="inlineStr"/>
       <c r="K70" s="4" t="inlineStr"/>
-      <c r="L70" s="5" t="inlineStr">
+      <c r="L70" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -4760,7 +4760,7 @@
       <c r="I73" s="4" t="inlineStr"/>
       <c r="J73" s="4" t="inlineStr"/>
       <c r="K73" s="4" t="inlineStr"/>
-      <c r="L73" s="5" t="inlineStr">
+      <c r="L73" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -4815,7 +4815,7 @@
       <c r="I74" s="4" t="inlineStr"/>
       <c r="J74" s="4" t="inlineStr"/>
       <c r="K74" s="4" t="inlineStr"/>
-      <c r="L74" s="5" t="inlineStr">
+      <c r="L74" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -4870,7 +4870,7 @@
       <c r="I75" s="4" t="inlineStr"/>
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr"/>
-      <c r="L75" s="5" t="inlineStr">
+      <c r="L75" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -5165,7 +5165,7 @@
           <t>미납(건) / 활동(건)</t>
         </is>
       </c>
-      <c r="L80" s="5" t="inlineStr">
+      <c r="L80" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -5224,7 +5224,7 @@
           <t>신규미납(건) / 신규활동(건)</t>
         </is>
       </c>
-      <c r="L81" s="5" t="inlineStr">
+      <c r="L81" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -5283,7 +5283,7 @@
           <t>기존미납(건) / 기존활동(건)</t>
         </is>
       </c>
-      <c r="L82" s="5" t="inlineStr">
+      <c r="L82" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -5342,7 +5342,7 @@
           <t>후원사업 미납(건) / 후원사업 활동(건)</t>
         </is>
       </c>
-      <c r="L83" s="5" t="inlineStr">
+      <c r="L83" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -5460,7 +5460,7 @@
           <t>납입회원(명) / 미납서비스 클릭회원(명) * 100</t>
         </is>
       </c>
-      <c r="L85" s="6" t="inlineStr">
+      <c r="L85" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,885행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -5578,7 +5578,7 @@
           <t>캠페인별 미납회비금액 / 10,000원</t>
         </is>
       </c>
-      <c r="L87" s="5" t="inlineStr">
+      <c r="L87" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -5689,21 +5689,29 @@
           <t>FSE.SEND_MEMBERS</t>
         </is>
       </c>
-      <c r="I89" s="4" t="inlineStr"/>
-      <c r="J89" s="4" t="inlineStr"/>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K89" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L89" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 41,969,590/41,969,590 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -5748,8 +5756,16 @@
           <t>FSE.SUCCESS_MEMBERS</t>
         </is>
       </c>
-      <c r="I90" s="4" t="inlineStr"/>
-      <c r="J90" s="4" t="inlineStr"/>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
@@ -5757,12 +5773,12 @@
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 25,417,305/41,969,590 (60.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5807,8 +5823,16 @@
           <t>FSE.FAIL_MEMBERS</t>
         </is>
       </c>
-      <c r="I91" s="4" t="inlineStr"/>
-      <c r="J91" s="4" t="inlineStr"/>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="K91" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
@@ -5816,12 +5840,12 @@
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 2,034,794/41,969,590 (4.8%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5866,21 +5890,29 @@
           <t>FSE.LETTER_PART_MEMBERS</t>
         </is>
       </c>
-      <c r="I92" s="4" t="inlineStr"/>
-      <c r="J92" s="4" t="inlineStr"/>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L92" s="5" t="inlineStr">
+      <c r="L92" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.LETTER_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5980,21 +6012,29 @@
           <t>FSE.GIFT_PART_MEMBERS</t>
         </is>
       </c>
-      <c r="I94" s="4" t="inlineStr"/>
-      <c r="J94" s="4" t="inlineStr"/>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L94" s="5" t="inlineStr">
+      <c r="L94" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.GIFT_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -6039,17 +6079,25 @@
           <t>FSE.GIFT_PART_AMT</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr"/>
-      <c r="J95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K95" s="4" t="inlineStr"/>
-      <c r="L95" s="5" t="inlineStr">
+      <c r="L95" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.GIFT_PART_AMT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -6097,7 +6145,7 @@
       <c r="I96" s="4" t="inlineStr"/>
       <c r="J96" s="4" t="inlineStr"/>
       <c r="K96" s="4" t="inlineStr"/>
-      <c r="L96" s="6" t="inlineStr">
+      <c r="L96" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6152,7 +6200,7 @@
       <c r="I97" s="4" t="inlineStr"/>
       <c r="J97" s="4" t="inlineStr"/>
       <c r="K97" s="4" t="inlineStr"/>
-      <c r="L97" s="6" t="inlineStr">
+      <c r="L97" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6207,7 +6255,7 @@
       <c r="I98" s="4" t="inlineStr"/>
       <c r="J98" s="4" t="inlineStr"/>
       <c r="K98" s="4" t="inlineStr"/>
-      <c r="L98" s="6" t="inlineStr">
+      <c r="L98" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6262,7 +6310,7 @@
       <c r="I99" s="4" t="inlineStr"/>
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr"/>
-      <c r="L99" s="6" t="inlineStr">
+      <c r="L99" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6317,7 +6365,7 @@
       <c r="I100" s="4" t="inlineStr"/>
       <c r="J100" s="4" t="inlineStr"/>
       <c r="K100" s="4" t="inlineStr"/>
-      <c r="L100" s="6" t="inlineStr">
+      <c r="L100" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6382,12 +6430,12 @@
       <c r="K101" s="4" t="inlineStr"/>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 166,114/166,114 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -6435,14 +6483,14 @@
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr"/>
       <c r="K102" s="4" t="inlineStr"/>
-      <c r="L102" s="5" t="inlineStr">
+      <c r="L102" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.AVG_SESSION_DURATION` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -6502,14 +6550,14 @@
           <t>member_id가 (not set)이 아닌 데이터</t>
         </is>
       </c>
-      <c r="L103" s="6" t="inlineStr">
+      <c r="L103" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 8,679행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6569,14 +6617,14 @@
           <t>후원b1, 후원b2, 1단_대문, 퀵버튼 등</t>
         </is>
       </c>
-      <c r="L104" s="6" t="inlineStr">
+      <c r="L104" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 8,679행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6636,14 +6684,14 @@
           <t>member_id가 (not set)이 아닌 데이터</t>
         </is>
       </c>
-      <c r="L105" s="6" t="inlineStr">
+      <c r="L105" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 8,679행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6703,14 +6751,14 @@
           <t>2024 기념일 캠페인 / 2024 ACL 등</t>
         </is>
       </c>
-      <c r="L106" s="6" t="inlineStr">
+      <c r="L106" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6770,14 +6818,14 @@
           <t>기부금영수증 인쇄 / 로그인하기 / 전체메뉴보기 등</t>
         </is>
       </c>
-      <c r="L107" s="6" t="inlineStr">
+      <c r="L107" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 209행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6833,14 +6881,14 @@
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr"/>
-      <c r="L108" s="6" t="inlineStr">
+      <c r="L108" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 209행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6888,7 +6936,7 @@
       <c r="I109" s="4" t="inlineStr"/>
       <c r="J109" s="4" t="inlineStr"/>
       <c r="K109" s="4" t="inlineStr"/>
-      <c r="L109" s="6" t="inlineStr">
+      <c r="L109" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -6947,7 +6995,7 @@
           <t>예) https://m.goodneighbors.kr/campaign/turn25b</t>
         </is>
       </c>
-      <c r="L110" s="6" t="inlineStr">
+      <c r="L110" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -7012,12 +7060,12 @@
       <c r="K111" s="4" t="inlineStr"/>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 33,757/166,114 (20.3%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -7065,14 +7113,14 @@
       <c r="I112" s="4" t="inlineStr"/>
       <c r="J112" s="4" t="inlineStr"/>
       <c r="K112" s="4" t="inlineStr"/>
-      <c r="L112" s="5" t="inlineStr">
+      <c r="L112" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.BOUNCE_RATE` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -7128,14 +7176,14 @@
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr"/>
-      <c r="L113" s="6" t="inlineStr">
+      <c r="L113" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 209행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7246,7 @@
       </c>
       <c r="M114" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,785,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7261,7 +7309,7 @@
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,785,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7317,14 +7365,14 @@
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr"/>
-      <c r="L116" s="6" t="inlineStr">
+      <c r="L116" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,785,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7431,7 @@
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7446,7 +7494,7 @@
       </c>
       <c r="M118" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7509,7 +7557,7 @@
       </c>
       <c r="M119" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7572,7 +7620,7 @@
       </c>
       <c r="M120" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7635,7 +7683,7 @@
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7746,7 @@
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7809,7 @@
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7872,7 @@
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7987,7 @@
           <t>"페이지 경로+쿼리 문자열"에서 파생. URL에서 childnum= 뒤에 오는 13자리. 예) https://gni.kr/url/25acl_25ABC.gn?memnum=1831636&amp;childnum=CMR-0102-002758 → 결연아동코드 = CMR-0102-002758</t>
         </is>
       </c>
-      <c r="L126" s="6" t="inlineStr">
+      <c r="L126" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -8009,7 +8057,7 @@
       </c>
       <c r="M127" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_SPONSORSHIP` 51행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8124,7 @@
       </c>
       <c r="M128" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_SPONSORSHIP` 51행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8179,7 @@
       </c>
       <c r="M129" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_PAYMENT` 7행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8186,7 +8234,7 @@
       </c>
       <c r="M130" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_PAYMENT` 7행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8454,7 @@
       </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8461,7 +8509,7 @@
       </c>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8564,7 @@
       </c>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8561,8 +8609,16 @@
           <t>DIM_SERVICE</t>
         </is>
       </c>
-      <c r="I137" s="4" t="inlineStr"/>
-      <c r="J137" s="4" t="inlineStr"/>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K137" s="4" t="inlineStr"/>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -8571,7 +8627,7 @@
       </c>
       <c r="M137" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8616,8 +8672,16 @@
           <t>DIM_SERVICE</t>
         </is>
       </c>
-      <c r="I138" s="4" t="inlineStr"/>
-      <c r="J138" s="4" t="inlineStr"/>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+        </is>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K138" s="4" t="inlineStr"/>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -8626,7 +8690,7 @@
       </c>
       <c r="M138" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8671,8 +8735,16 @@
           <t>DIM_SERVICE</t>
         </is>
       </c>
-      <c r="I139" s="4" t="inlineStr"/>
-      <c r="J139" s="4" t="inlineStr"/>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K139" s="4" t="inlineStr"/>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -8681,7 +8753,7 @@
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8863,7 @@
       </c>
       <c r="M141" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_DATE` 16,437행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9421,7 @@
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9399,12 +9471,12 @@
       <c r="K152" s="4" t="inlineStr"/>
       <c r="L152" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,325,729/4,716,360 (49.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -9454,12 +9526,12 @@
       <c r="K153" s="4" t="inlineStr"/>
       <c r="L153" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,729/4,716,360 (49.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -9507,7 +9579,7 @@
       <c r="I154" s="4" t="inlineStr"/>
       <c r="J154" s="4" t="inlineStr"/>
       <c r="K154" s="4" t="inlineStr"/>
-      <c r="L154" s="5" t="inlineStr">
+      <c r="L154" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -9562,7 +9634,7 @@
       <c r="I155" s="4" t="inlineStr"/>
       <c r="J155" s="4" t="inlineStr"/>
       <c r="K155" s="4" t="inlineStr"/>
-      <c r="L155" s="5" t="inlineStr">
+      <c r="L155" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -9617,7 +9689,7 @@
       <c r="I156" s="4" t="inlineStr"/>
       <c r="J156" s="4" t="inlineStr"/>
       <c r="K156" s="4" t="inlineStr"/>
-      <c r="L156" s="5" t="inlineStr">
+      <c r="L156" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -9672,7 +9744,7 @@
       <c r="I157" s="4" t="inlineStr"/>
       <c r="J157" s="4" t="inlineStr"/>
       <c r="K157" s="4" t="inlineStr"/>
-      <c r="L157" s="5" t="inlineStr">
+      <c r="L157" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -9727,7 +9799,7 @@
       <c r="I158" s="4" t="inlineStr"/>
       <c r="J158" s="4" t="inlineStr"/>
       <c r="K158" s="4" t="inlineStr"/>
-      <c r="L158" s="5" t="inlineStr">
+      <c r="L158" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -9782,7 +9854,7 @@
       <c r="I159" s="4" t="inlineStr"/>
       <c r="J159" s="4" t="inlineStr"/>
       <c r="K159" s="4" t="inlineStr"/>
-      <c r="L159" s="5" t="inlineStr">
+      <c r="L159" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -9837,7 +9909,7 @@
       <c r="I160" s="4" t="inlineStr"/>
       <c r="J160" s="4" t="inlineStr"/>
       <c r="K160" s="4" t="inlineStr"/>
-      <c r="L160" s="5" t="inlineStr">
+      <c r="L160" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -9892,7 +9964,7 @@
       <c r="I161" s="4" t="inlineStr"/>
       <c r="J161" s="4" t="inlineStr"/>
       <c r="K161" s="4" t="inlineStr"/>
-      <c r="L161" s="5" t="inlineStr">
+      <c r="L161" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -10002,7 +10074,7 @@
       <c r="I163" s="4" t="inlineStr"/>
       <c r="J163" s="4" t="inlineStr"/>
       <c r="K163" s="4" t="inlineStr"/>
-      <c r="L163" s="5" t="inlineStr">
+      <c r="L163" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -10174,7 +10246,7 @@
       </c>
       <c r="M166" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,885행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10477,12 @@
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,325,729/4,716,360 (49.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10770,7 @@
           <t>광고비(편성비) 비용 / 신규 획득 개발 건수</t>
         </is>
       </c>
-      <c r="L175" s="6" t="inlineStr">
+      <c r="L175" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -10765,14 +10837,14 @@
           <t>ERP 모금성 비용 / 신규 획득 개발 건수</t>
         </is>
       </c>
-      <c r="L176" s="5" t="inlineStr">
+      <c r="L176" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BUDGET` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BUDGET.FUNDRAISING_COST` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10896,7 @@
           <t>(총 수익−총 비용) / 총 비용 × 100</t>
         </is>
       </c>
-      <c r="L177" s="5" t="inlineStr">
+      <c r="L177" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -10883,7 +10955,7 @@
           <t>캠페인별 활동건 / (캠페인별 개발누계건 + 캠페인별 연도초활동건)</t>
         </is>
       </c>
-      <c r="L178" s="5" t="inlineStr">
+      <c r="L178" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -10942,7 +11014,7 @@
           <t>조회시점 기준 캠페인 활동건 / (캠페인 개발누계건 + 캠페인 연도초활동건)</t>
         </is>
       </c>
-      <c r="L179" s="5" t="inlineStr">
+      <c r="L179" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11001,7 +11073,7 @@
           <t>캠페인별 납입방식 활동건 / (캠페인별 납입방식 개발누계건 + 캠페인별 납입방식 연도초활동건)</t>
         </is>
       </c>
-      <c r="L180" s="5" t="inlineStr">
+      <c r="L180" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11060,7 +11132,7 @@
           <t>캠페인별 중단(건) / (캠페인별 개발(건) + 캠페인별 연도초활동회원(건))</t>
         </is>
       </c>
-      <c r="L181" s="5" t="inlineStr">
+      <c r="L181" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11119,7 +11191,7 @@
           <t>조회시점 기준 캠페인 중단(건) / (캠페인 개발(건) + 캠페인 전월말활동회원(건))</t>
         </is>
       </c>
-      <c r="L182" s="5" t="inlineStr">
+      <c r="L182" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11178,7 +11250,7 @@
           <t>캠페인별 누계중단(건) / (캠페인별 누계개발(건) + 캠페인별 연도초활동회원(건))</t>
         </is>
       </c>
-      <c r="L183" s="5" t="inlineStr">
+      <c r="L183" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11237,7 +11309,7 @@
           <t>조회시점 기준 캠페인 누계중단(건) / 캠페인별 누계개발(건)</t>
         </is>
       </c>
-      <c r="L184" s="5" t="inlineStr">
+      <c r="L184" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11296,7 +11368,7 @@
           <t>캠페인별 납입방식 중단(건) / (캠페인별 납입방식 개발(건) + 캠페인별 연도초활동회원(건))</t>
         </is>
       </c>
-      <c r="L185" s="5" t="inlineStr">
+      <c r="L185" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11355,7 +11427,7 @@
           <t>후원취소 및 감액한 후원사업의 금액 / 10,000</t>
         </is>
       </c>
-      <c r="L186" s="5" t="inlineStr">
+      <c r="L186" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11414,7 +11486,7 @@
           <t>캠페인별 이탈(건) / 캠페인별 개발(건)</t>
         </is>
       </c>
-      <c r="L187" s="5" t="inlineStr">
+      <c r="L187" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11473,7 +11545,7 @@
           <t>캠페인별 활동회원의 월 납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L188" s="5" t="inlineStr">
+      <c r="L188" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11532,7 +11604,7 @@
           <t>조회시점 기준 캠페인별 활동회원의 월 납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L189" s="5" t="inlineStr">
+      <c r="L189" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11591,7 +11663,7 @@
           <t>캠페인별 활동회원 월 누계납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L190" s="5" t="inlineStr">
+      <c r="L190" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11650,7 +11722,7 @@
           <t>조회시점 기준 캠페인별 활동회원 월 누계납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L191" s="5" t="inlineStr">
+      <c r="L191" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11709,7 +11781,7 @@
           <t>캠페인별 납입회비 / 총 납입회비 금액 × 100</t>
         </is>
       </c>
-      <c r="L192" s="5" t="inlineStr">
+      <c r="L192" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11768,7 +11840,7 @@
           <t>캠페인별 활동회원의 월 미납회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L193" s="5" t="inlineStr">
+      <c r="L193" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11827,7 +11899,7 @@
           <t>조회시점 기준 캠페인별 활동회원의 월 미납회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L194" s="5" t="inlineStr">
+      <c r="L194" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11886,7 +11958,7 @@
           <t>캠페인별 미납회비 / 총 미납회비 금액 × 100</t>
         </is>
       </c>
-      <c r="L195" s="5" t="inlineStr">
+      <c r="L195" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -11938,21 +12010,29 @@
           <t>SV metric — 분자: SEND_MEMBERS / 분모: 전체회원수(명)</t>
         </is>
       </c>
-      <c r="I196" s="4" t="inlineStr"/>
-      <c r="J196" s="4" t="inlineStr"/>
+      <c r="I196" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_REQUEST.SNDNG_TY_CD</t>
+        </is>
+      </c>
+      <c r="J196" s="4" t="inlineStr">
+        <is>
+          <t>SND_REQ_MST;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K196" s="4" t="inlineStr">
         <is>
           <t>서비스별 발송수(명) / 전체회원수(명) × 100</t>
         </is>
       </c>
-      <c r="L196" s="5" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L196" s="7" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 41,969,590/41,969,590 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -11997,8 +12077,16 @@
           <t>SV metric — 분자: SUCCESS_MEMBERS / 분모: SEND_MEMBERS</t>
         </is>
       </c>
-      <c r="I197" s="4" t="inlineStr"/>
-      <c r="J197" s="4" t="inlineStr"/>
+      <c r="I197" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SNDNG_RST_CD</t>
+        </is>
+      </c>
+      <c r="J197" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="K197" s="4" t="inlineStr">
         <is>
           <t>발송성공수(명) / 발송수(명) × 100</t>
@@ -12006,12 +12094,12 @@
       </c>
       <c r="L197" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M197" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 25,417,305/41,969,590 (60.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12063,7 +12151,7 @@
           <t>클릭수(명) / 발송수(명) × 100</t>
         </is>
       </c>
-      <c r="L198" s="6" t="inlineStr">
+      <c r="L198" s="5" t="inlineStr">
         <is>
           <t>PARTIAL</t>
         </is>
@@ -12124,12 +12212,12 @@
       </c>
       <c r="L199" s="5" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M199" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,325,729/4,716,360 (49.3%) · GA↔CRM identity 커버리지 종속</t>
         </is>
       </c>
     </row>
@@ -12764,21 +12852,29 @@
           <t>SV metric — 분자: LETTER_PART_MEMBERS / 분모: 참여회원수</t>
         </is>
       </c>
-      <c r="I210" s="4" t="inlineStr"/>
-      <c r="J210" s="4" t="inlineStr"/>
+      <c r="I210" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+        </is>
+      </c>
+      <c r="J210" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="K210" s="4" t="inlineStr">
         <is>
           <t>(서비스별 서신 참여회원(명,건) / 해당 서비스 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L210" s="5" t="inlineStr">
+      <c r="L210" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M210" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.LETTER_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -13059,21 +13155,29 @@
           <t>SV metric — 분자: GIFT_PART_MEMBERS / 분모: 참여회원수</t>
         </is>
       </c>
-      <c r="I215" s="4" t="inlineStr"/>
-      <c r="J215" s="4" t="inlineStr"/>
+      <c r="I215" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+        </is>
+      </c>
+      <c r="J215" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+        </is>
+      </c>
       <c r="K215" s="4" t="inlineStr">
         <is>
           <t>(서비스별 선물금 참여회원(명,건) / 해당 서비스 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L215" s="5" t="inlineStr">
+      <c r="L215" s="6" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M215" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.GIFT_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-15 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-16 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-15</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -693,8 +693,16 @@
           <t>SV metric — 분자: DEV_CNT / 분모: GOAL_CNT</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
           <t>월 개발건 / 월 회원개발목표</t>
@@ -752,8 +760,16 @@
           <t>SV metric — 분자: DEV_CNT(YTD) / 분모: GOAL_CNT(YTD)</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr"/>
-      <c r="J6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
           <t>누계 개발건 / 누계 회원개발목표</t>
@@ -811,8 +827,16 @@
           <t>SV metric — 분자: DEV_CNT(YR) / 분모: GOAL_CNT(YR)</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
           <t>연 개발건 / 연 회원개발목표</t>
@@ -870,21 +894,29 @@
           <t>FMM.DEV_CNT</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr"/>
-      <c r="J8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 회원의 CRM 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 2,025,238/41,508,842 (4.9%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -929,21 +961,29 @@
           <t>FMM.DEV_CNT</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr"/>
-      <c r="J9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
           <t>GA 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 2,025,238/41,508,842 (4.9%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1641,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1708,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1735,7 +1775,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1791,14 +1831,14 @@
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="7" t="inlineStr">
+      <c r="L22" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1854,14 +1894,14 @@
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="L23" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2327,7 @@
       <c r="I30" s="4" t="inlineStr"/>
       <c r="J30" s="4" t="inlineStr"/>
       <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="7" t="inlineStr">
+      <c r="L30" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2342,7 +2382,7 @@
       <c r="I31" s="4" t="inlineStr"/>
       <c r="J31" s="4" t="inlineStr"/>
       <c r="K31" s="4" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr">
+      <c r="L31" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2394,10 +2434,18 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I32" s="4" t="inlineStr"/>
-      <c r="J32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="7" t="inlineStr">
+      <c r="L32" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2449,14 +2497,22 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I33" s="4" t="inlineStr"/>
-      <c r="J33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
           <t>회원이 최초가입 시 가입캠페인</t>
         </is>
       </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="L33" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2508,14 +2564,22 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr"/>
-      <c r="J34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
           <t>회원의 최종중단일자</t>
         </is>
       </c>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="L34" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2567,14 +2631,22 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I35" s="4" t="inlineStr"/>
-      <c r="J35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
           <t>회원이 최종중단 시 최종캠페인</t>
         </is>
       </c>
-      <c r="L35" s="7" t="inlineStr">
+      <c r="L35" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2629,7 +2701,7 @@
       <c r="I36" s="4" t="inlineStr"/>
       <c r="J36" s="4" t="inlineStr"/>
       <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="7" t="inlineStr">
+      <c r="L36" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2684,7 +2756,7 @@
       <c r="I37" s="4" t="inlineStr"/>
       <c r="J37" s="4" t="inlineStr"/>
       <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="7" t="inlineStr">
+      <c r="L37" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2739,7 +2811,7 @@
       <c r="I38" s="4" t="inlineStr"/>
       <c r="J38" s="4" t="inlineStr"/>
       <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="7" t="inlineStr">
+      <c r="L38" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2791,8 +2863,16 @@
           <t>FME→FMM.STOP_CNT</t>
         </is>
       </c>
-      <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 후원중단한 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
@@ -2850,21 +2930,29 @@
           <t>FME→FMM.UNPAID_CNT</t>
         </is>
       </c>
-      <c r="I40" s="4" t="inlineStr"/>
-      <c r="J40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 회원상태가 미납인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L40" s="6" t="inlineStr">
+      <c r="L40" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -2909,8 +2997,16 @@
           <t>FMM.ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I41" s="4" t="inlineStr"/>
-      <c r="J41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 회원상태가 활동인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
@@ -2918,12 +3014,12 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -2968,21 +3064,29 @@
           <t>FMM.DECREASE_CNT</t>
         </is>
       </c>
-      <c r="I42" s="4" t="inlineStr"/>
-      <c r="J42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
           <t>회원번호 기준, 후원사업(세부캠페인)별 총 감액 건 ( = 전체 감액금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L42" s="6" t="inlineStr">
+      <c r="L42" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -3027,10 +3131,18 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I43" s="4" t="inlineStr"/>
-      <c r="J43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="7" t="inlineStr">
+      <c r="L43" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3082,10 +3194,18 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I44" s="4" t="inlineStr"/>
-      <c r="J44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K44" s="4" t="inlineStr"/>
-      <c r="L44" s="7" t="inlineStr">
+      <c r="L44" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3137,10 +3257,18 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I45" s="4" t="inlineStr"/>
-      <c r="J45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="7" t="inlineStr">
+      <c r="L45" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3192,10 +3320,18 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr"/>
-      <c r="J46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="7" t="inlineStr">
+      <c r="L46" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3247,10 +3383,18 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I47" s="4" t="inlineStr"/>
-      <c r="J47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K47" s="4" t="inlineStr"/>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="L47" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3302,10 +3446,18 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr"/>
-      <c r="J48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="7" t="inlineStr">
+      <c r="L48" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3357,8 +3509,16 @@
           <t>SV metric — 분자: MONTH_END_ACTIVE_CNT / 분모: YEAR_START_ACTIVE_CNT + DEV_CNT(YTD)</t>
         </is>
       </c>
-      <c r="I49" s="4" t="inlineStr"/>
-      <c r="J49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
           <t>월말활동회원건 / 총 개발회원건 (연도초활동회원건 + 누계개발건)</t>
@@ -3366,12 +3526,12 @@
       </c>
       <c r="L49" s="6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -3416,21 +3576,29 @@
           <t>SV metric — 분자: DEV_CNT(YTD) / 분모: ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr"/>
-      <c r="J50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
           <t>누계개발 건 / 활동건</t>
         </is>
       </c>
-      <c r="L50" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L50" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 2,025,238/41,508,842 (4.9%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3475,8 +3643,16 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD) + YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I51" s="4" t="inlineStr"/>
-      <c r="J51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
           <t>활동 건 / (누계개발 건 + 연도초활동 건)</t>
@@ -3484,12 +3660,12 @@
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -3534,10 +3710,18 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I52" s="4" t="inlineStr"/>
-      <c r="J52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K52" s="4" t="inlineStr"/>
-      <c r="L52" s="7" t="inlineStr">
+      <c r="L52" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3589,21 +3773,29 @@
           <t>FMM.YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I53" s="4" t="inlineStr"/>
-      <c r="J53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
           <t>전년도 연도말 활동회원 건수</t>
         </is>
       </c>
-      <c r="L53" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 36,847,772/41,508,842 (88.8%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3648,10 +3840,18 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I54" s="4" t="inlineStr"/>
-      <c r="J54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K54" s="4" t="inlineStr"/>
-      <c r="L54" s="7" t="inlineStr">
+      <c r="L54" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3703,14 +3903,22 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I55" s="4" t="inlineStr"/>
-      <c r="J55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
           <t>활동, 미납1~미납5까지의 회원 포함</t>
         </is>
       </c>
-      <c r="L55" s="7" t="inlineStr">
+      <c r="L55" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -3762,8 +3970,16 @@
           <t>FMM.MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I56" s="4" t="inlineStr"/>
-      <c r="J56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
           <t>월 활동회원(회원상태가 활동, 미납1~미납5)의 전체후원사업금액 / 10,000</t>
@@ -3771,12 +3987,12 @@
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -3821,17 +4037,25 @@
           <t>FMM.PREV_MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I57" s="4" t="inlineStr"/>
-      <c r="J57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 39,122,763/41,508,842 (94.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3876,21 +4100,29 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT + YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I58" s="4" t="inlineStr"/>
-      <c r="J58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
           <t>중단(건) / (개발(건) + 연도초활동회원(건))</t>
         </is>
       </c>
-      <c r="L58" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3935,21 +4167,29 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT</t>
         </is>
       </c>
-      <c r="I59" s="4" t="inlineStr"/>
-      <c r="J59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
           <t>중단(건) / 개발(건)</t>
         </is>
       </c>
-      <c r="L59" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3994,8 +4234,16 @@
           <t>SV metric — 분자: STOP_CNT[신규] / 분모: DEV_CNT[신규] + PREV_MONTH_END_ACTIVE_CNT[신규]</t>
         </is>
       </c>
-      <c r="I60" s="4" t="inlineStr"/>
-      <c r="J60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
           <t>신규중단(건) / (당월 신규개발(건) + 전월말 신규활동회원건)</t>
@@ -4053,8 +4301,16 @@
           <t>SV metric — 분자: STOP_CNT[기존] / 분모: DEV_CNT[기존] + PREV_MONTH_END_ACTIVE_CNT[기존]</t>
         </is>
       </c>
-      <c r="I61" s="4" t="inlineStr"/>
-      <c r="J61" s="4" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
           <t>기존중단(건) / (당월 기존개발(건) + 전월말 기존활동회원건)</t>
@@ -4112,8 +4368,16 @@
           <t>SV metric — 분자: STOP_CNT(주합) / 분모: 주간 일수(DIM_DATE)</t>
         </is>
       </c>
-      <c r="I62" s="4" t="inlineStr"/>
-      <c r="J62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
           <t>해당주간 총 중단건수 / 해당 주간 일수</t>
@@ -4178,7 +4442,7 @@
           <t>(당해년도 전주/전월/전년 수치 − 전주/전월/전년 수치)</t>
         </is>
       </c>
-      <c r="L63" s="7" t="inlineStr">
+      <c r="L63" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4237,7 +4501,7 @@
           <t>(당해년도 전주/전월/전년 수치 − 전주/전월/전년 수치) / (전주/전월/전년 수치) * 100</t>
         </is>
       </c>
-      <c r="L64" s="7" t="inlineStr">
+      <c r="L64" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4289,8 +4553,16 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: ACTIVE_MEMBERS</t>
         </is>
       </c>
-      <c r="I65" s="4" t="inlineStr"/>
-      <c r="J65" s="4" t="inlineStr"/>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K65" s="4" t="inlineStr">
         <is>
           <t>활동회원 건 / 활동회원 명</t>
@@ -4298,12 +4570,12 @@
       </c>
       <c r="L65" s="6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -4348,21 +4620,29 @@
           <t>SV metric — 분자: PAID_FEE / 분모: ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I66" s="4" t="inlineStr"/>
-      <c r="J66" s="4" t="inlineStr"/>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
           <t>납입회비 원 / (활동회원 건 * 10,000)</t>
         </is>
       </c>
-      <c r="L66" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L66" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4407,21 +4687,29 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: ACTIVE_CUM_CNT ×10000</t>
         </is>
       </c>
-      <c r="I67" s="4" t="inlineStr"/>
-      <c r="J67" s="4" t="inlineStr"/>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K67" s="4" t="inlineStr">
         <is>
           <t>누계납입회비 원 / (누계 활동회원 건 * 10,000)</t>
         </is>
       </c>
-      <c r="L67" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4466,21 +4754,29 @@
           <t>SV metric — 분자: PAID_FEE / 분모: BILLED_AMT</t>
         </is>
       </c>
-      <c r="I68" s="4" t="inlineStr"/>
-      <c r="J68" s="4" t="inlineStr"/>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
           <t>(납입회비 원 / 청구회비 원) * 100</t>
         </is>
       </c>
-      <c r="L68" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L68" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4525,21 +4821,29 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: BILLED_AMT(YTD)</t>
         </is>
       </c>
-      <c r="I69" s="4" t="inlineStr"/>
-      <c r="J69" s="4" t="inlineStr"/>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K69" s="4" t="inlineStr">
         <is>
           <t>(누계납부회비 원 / 누계 청구회비 원) * 100</t>
         </is>
       </c>
-      <c r="L69" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4584,17 +4888,25 @@
           <t>FMM.REGULAR_FEE</t>
         </is>
       </c>
-      <c r="I70" s="4" t="inlineStr"/>
-      <c r="J70" s="4" t="inlineStr"/>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K70" s="4" t="inlineStr"/>
-      <c r="L70" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L70" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 36,800,958/41,508,842 (88.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4639,14 +4951,22 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I71" s="4" t="inlineStr"/>
-      <c r="J71" s="4" t="inlineStr"/>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K71" s="4" t="inlineStr">
         <is>
           <t>정기회원이 정기후원사업 외 비지정(기타, 국내사업, 해외사업)으로 납부하는 일시회비</t>
         </is>
       </c>
-      <c r="L71" s="7" t="inlineStr">
+      <c r="L71" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4698,14 +5018,22 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I72" s="4" t="inlineStr"/>
-      <c r="J72" s="4" t="inlineStr"/>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
           <t>일시회원이 납부하는 회비</t>
         </is>
       </c>
-      <c r="L72" s="7" t="inlineStr">
+      <c r="L72" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4757,17 +5085,25 @@
           <t>FMM.PAID_FEE</t>
         </is>
       </c>
-      <c r="I73" s="4" t="inlineStr"/>
-      <c r="J73" s="4" t="inlineStr"/>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K73" s="4" t="inlineStr"/>
-      <c r="L73" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4812,17 +5148,25 @@
           <t>FMM.PAID_FEE</t>
         </is>
       </c>
-      <c r="I74" s="4" t="inlineStr"/>
-      <c r="J74" s="4" t="inlineStr"/>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K74" s="4" t="inlineStr"/>
-      <c r="L74" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L74" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4867,17 +5211,25 @@
           <t>FMM.BILLED_AMT</t>
         </is>
       </c>
-      <c r="I75" s="4" t="inlineStr"/>
-      <c r="J75" s="4" t="inlineStr"/>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.RQEST_AMT</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K75" s="4" t="inlineStr"/>
-      <c r="L75" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 38,579,737/41,508,842 (92.9%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4929,7 +5281,7 @@
           <t>조회년월 기준 후원 약정금액 ( = 개발된 후원사업별 금액 ) / 10,000원</t>
         </is>
       </c>
-      <c r="L76" s="7" t="inlineStr">
+      <c r="L76" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -4988,7 +5340,7 @@
           <t>조회년월 기준 후원 약정금액 ( = 개발된 후원사업별 금액 ) / 10,000원</t>
         </is>
       </c>
-      <c r="L77" s="7" t="inlineStr">
+      <c r="L77" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5047,7 +5399,7 @@
           <t>캠페인 가입일자부터 조회년월까지의 기간을 개월 기준으로, 년 기준으로 구분</t>
         </is>
       </c>
-      <c r="L78" s="7" t="inlineStr">
+      <c r="L78" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5106,7 +5458,7 @@
           <t>캠페인 가입일자부터 조회년월까지의 기간을 개월 기준으로, 년 기준으로 구분</t>
         </is>
       </c>
-      <c r="L79" s="7" t="inlineStr">
+      <c r="L79" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5158,21 +5510,29 @@
           <t>SV metric — 분자: UNPAID_CNT / 분모: ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I80" s="4" t="inlineStr"/>
-      <c r="J80" s="4" t="inlineStr"/>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
           <t>미납(건) / 활동(건)</t>
         </is>
       </c>
-      <c r="L80" s="6" t="inlineStr">
+      <c r="L80" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5217,21 +5577,29 @@
           <t>SV metric — 분자: UNPAID_CNT[신규] / 분모: ACTIVE_CNT[신규]</t>
         </is>
       </c>
-      <c r="I81" s="4" t="inlineStr"/>
-      <c r="J81" s="4" t="inlineStr"/>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
           <t>신규미납(건) / 신규활동(건)</t>
         </is>
       </c>
-      <c r="L81" s="6" t="inlineStr">
+      <c r="L81" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5276,21 +5644,29 @@
           <t>SV metric — 분자: UNPAID_CNT[기존] / 분모: ACTIVE_CNT[기존]</t>
         </is>
       </c>
-      <c r="I82" s="4" t="inlineStr"/>
-      <c r="J82" s="4" t="inlineStr"/>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
           <t>기존미납(건) / 기존활동(건)</t>
         </is>
       </c>
-      <c r="L82" s="6" t="inlineStr">
+      <c r="L82" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5335,21 +5711,29 @@
           <t>SV metric — 분자: UNPAID_CNT / 분모: ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
           <t>후원사업 미납(건) / 후원사업 활동(건)</t>
         </is>
       </c>
-      <c r="L83" s="6" t="inlineStr">
+      <c r="L83" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5785,7 @@
           <t>(월초미납명수 − 월말미납명수) / 월초미납명수</t>
         </is>
       </c>
-      <c r="L84" s="7" t="inlineStr">
+      <c r="L84" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5512,14 +5896,22 @@
           <t>DIM_REASON</t>
         </is>
       </c>
-      <c r="I86" s="4" t="inlineStr"/>
-      <c r="J86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_ID</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
           <t>CRM &gt; 회원요약정보 &gt; 회비내역 &gt; 미납/환급정보 &gt; 미납내역</t>
         </is>
       </c>
-      <c r="L86" s="7" t="inlineStr">
+      <c r="L86" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5571,21 +5963,29 @@
           <t>FMM.CAMPAIGN_UNPAID_CNT</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr"/>
-      <c r="J87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
           <t>캠페인별 미납회비금액 / 10,000원</t>
         </is>
       </c>
-      <c r="L87" s="6" t="inlineStr">
+      <c r="L87" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -5630,14 +6030,22 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I88" s="4" t="inlineStr"/>
-      <c r="J88" s="4" t="inlineStr"/>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
           <t>회원상태별 미납회비금액 / 10,000원</t>
         </is>
       </c>
-      <c r="L88" s="7" t="inlineStr">
+      <c r="L88" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5704,7 +6112,7 @@
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L89" s="7" t="inlineStr">
+      <c r="L89" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -5905,7 +6313,7 @@
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L92" s="6" t="inlineStr">
+      <c r="L92" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -5957,10 +6365,18 @@
           <t>FSE (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I93" s="4" t="inlineStr"/>
-      <c r="J93" s="4" t="inlineStr"/>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="K93" s="4" t="inlineStr"/>
-      <c r="L93" s="7" t="inlineStr">
+      <c r="L93" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -6027,7 +6443,7 @@
           <t>회원번호 개수 기준 (중복 포함)</t>
         </is>
       </c>
-      <c r="L94" s="6" t="inlineStr">
+      <c r="L94" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -6090,7 +6506,7 @@
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr"/>
-      <c r="L95" s="6" t="inlineStr">
+      <c r="L95" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -6435,7 +6851,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 166,114/166,114 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 160,166/160,166 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6899,7 @@
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr"/>
       <c r="K102" s="4" t="inlineStr"/>
-      <c r="L102" s="6" t="inlineStr">
+      <c r="L102" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -6557,7 +6973,7 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 8,679행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 7,862행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6624,7 +7040,7 @@
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 8,679행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 7,862행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6691,7 +7107,7 @@
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 8,679행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 7,862행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6758,7 +7174,7 @@
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6825,7 +7241,7 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 209행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 142행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6888,7 +7304,7 @@
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 209행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 142행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7065,7 +7481,7 @@
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 33,757/166,114 (20.3%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 30,842/160,166 (19.3%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7529,7 @@
       <c r="I112" s="4" t="inlineStr"/>
       <c r="J112" s="4" t="inlineStr"/>
       <c r="K112" s="4" t="inlineStr"/>
-      <c r="L112" s="6" t="inlineStr">
+      <c r="L112" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -7183,7 +7599,7 @@
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 209행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 142행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7655,7 @@
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr"/>
-      <c r="L114" s="7" t="inlineStr">
+      <c r="L114" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7302,7 +7718,7 @@
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr"/>
-      <c r="L115" s="7" t="inlineStr">
+      <c r="L115" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7417,14 +7833,22 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I117" s="4" t="inlineStr"/>
-      <c r="J117" s="4" t="inlineStr"/>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
           <t>신규: 당해년도 개발, 기존: 당해년도 이전 개발</t>
         </is>
       </c>
-      <c r="L117" s="7" t="inlineStr">
+      <c r="L117" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7487,7 +7911,7 @@
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr"/>
-      <c r="L118" s="7" t="inlineStr">
+      <c r="L118" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7550,7 +7974,7 @@
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr"/>
-      <c r="L119" s="7" t="inlineStr">
+      <c r="L119" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7613,7 +8037,7 @@
         </is>
       </c>
       <c r="K120" s="4" t="inlineStr"/>
-      <c r="L120" s="7" t="inlineStr">
+      <c r="L120" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -7676,14 +8100,14 @@
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr"/>
-      <c r="L121" s="7" t="inlineStr">
+      <c r="L121" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7739,14 +8163,14 @@
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr"/>
-      <c r="L122" s="7" t="inlineStr">
+      <c r="L122" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7802,14 +8226,14 @@
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr"/>
-      <c r="L123" s="7" t="inlineStr">
+      <c r="L123" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7865,14 +8289,14 @@
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr"/>
-      <c r="L124" s="7" t="inlineStr">
+      <c r="L124" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7920,7 +8344,7 @@
       <c r="I125" s="4" t="inlineStr"/>
       <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr"/>
-      <c r="L125" s="7" t="inlineStr">
+      <c r="L125" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8050,7 +8474,7 @@
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr"/>
-      <c r="L127" s="7" t="inlineStr">
+      <c r="L127" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8117,7 +8541,7 @@
           <t>국내사단(국내아동권리보호사업(사단법인), 결식아동지원, 아동학대예방, 저소득가정지원), 국내사복(국내아동권리보호사업(사회복지법인), 국내사업, 좋은이웃(사복)), 결연(해외아동결연), 해외구호(희망학교지원사업, 해외교육지원사업, 보건의료지원사업, 식수위생지원사업, 재난구호지원사업, 해외지역개발지원사업), 기타(대북지원사업, 좋은이웃, 전체사업지원)</t>
         </is>
       </c>
-      <c r="L128" s="7" t="inlineStr">
+      <c r="L128" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8169,10 +8593,18 @@
           <t>DIM_PAYMENT</t>
         </is>
       </c>
-      <c r="I129" s="4" t="inlineStr"/>
-      <c r="J129" s="4" t="inlineStr"/>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
+        </is>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
+        </is>
+      </c>
       <c r="K129" s="4" t="inlineStr"/>
-      <c r="L129" s="7" t="inlineStr">
+      <c r="L129" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8224,10 +8656,18 @@
           <t>DIM_PAYMENT</t>
         </is>
       </c>
-      <c r="I130" s="4" t="inlineStr"/>
-      <c r="J130" s="4" t="inlineStr"/>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_METHOD.SETLE_NM</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_PM_SETLE_INFO</t>
+        </is>
+      </c>
       <c r="K130" s="4" t="inlineStr"/>
-      <c r="L130" s="7" t="inlineStr">
+      <c r="L130" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8282,7 +8722,7 @@
       <c r="I131" s="4" t="inlineStr"/>
       <c r="J131" s="4" t="inlineStr"/>
       <c r="K131" s="4" t="inlineStr"/>
-      <c r="L131" s="7" t="inlineStr">
+      <c r="L131" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8337,7 +8777,7 @@
       <c r="I132" s="4" t="inlineStr"/>
       <c r="J132" s="4" t="inlineStr"/>
       <c r="K132" s="4" t="inlineStr"/>
-      <c r="L132" s="7" t="inlineStr">
+      <c r="L132" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8392,7 +8832,7 @@
       <c r="I133" s="4" t="inlineStr"/>
       <c r="J133" s="4" t="inlineStr"/>
       <c r="K133" s="4" t="inlineStr"/>
-      <c r="L133" s="7" t="inlineStr">
+      <c r="L133" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8444,10 +8884,18 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I134" s="4" t="inlineStr"/>
-      <c r="J134" s="4" t="inlineStr"/>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K134" s="4" t="inlineStr"/>
-      <c r="L134" s="7" t="inlineStr">
+      <c r="L134" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8499,10 +8947,18 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I135" s="4" t="inlineStr"/>
-      <c r="J135" s="4" t="inlineStr"/>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K135" s="4" t="inlineStr"/>
-      <c r="L135" s="7" t="inlineStr">
+      <c r="L135" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8554,10 +9010,18 @@
           <t>DIM_MEMBER</t>
         </is>
       </c>
-      <c r="I136" s="4" t="inlineStr"/>
-      <c r="J136" s="4" t="inlineStr"/>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER.MBER_STAT_CD</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
+        </is>
+      </c>
       <c r="K136" s="4" t="inlineStr"/>
-      <c r="L136" s="7" t="inlineStr">
+      <c r="L136" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8620,7 +9084,7 @@
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr"/>
-      <c r="L137" s="7" t="inlineStr">
+      <c r="L137" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8683,7 +9147,7 @@
         </is>
       </c>
       <c r="K138" s="4" t="inlineStr"/>
-      <c r="L138" s="7" t="inlineStr">
+      <c r="L138" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8746,7 +9210,7 @@
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr"/>
-      <c r="L139" s="7" t="inlineStr">
+      <c r="L139" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8801,7 +9265,7 @@
       <c r="I140" s="4" t="inlineStr"/>
       <c r="J140" s="4" t="inlineStr"/>
       <c r="K140" s="4" t="inlineStr"/>
-      <c r="L140" s="7" t="inlineStr">
+      <c r="L140" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8856,7 +9320,7 @@
       <c r="I141" s="4" t="inlineStr"/>
       <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr"/>
-      <c r="L141" s="7" t="inlineStr">
+      <c r="L141" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8911,7 +9375,7 @@
       <c r="I142" s="4" t="inlineStr"/>
       <c r="J142" s="4" t="inlineStr"/>
       <c r="K142" s="4" t="inlineStr"/>
-      <c r="L142" s="7" t="inlineStr">
+      <c r="L142" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -8966,7 +9430,7 @@
       <c r="I143" s="4" t="inlineStr"/>
       <c r="J143" s="4" t="inlineStr"/>
       <c r="K143" s="4" t="inlineStr"/>
-      <c r="L143" s="7" t="inlineStr">
+      <c r="L143" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9021,7 +9485,7 @@
       <c r="I144" s="4" t="inlineStr"/>
       <c r="J144" s="4" t="inlineStr"/>
       <c r="K144" s="4" t="inlineStr"/>
-      <c r="L144" s="7" t="inlineStr">
+      <c r="L144" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9076,7 +9540,7 @@
       <c r="I145" s="4" t="inlineStr"/>
       <c r="J145" s="4" t="inlineStr"/>
       <c r="K145" s="4" t="inlineStr"/>
-      <c r="L145" s="7" t="inlineStr">
+      <c r="L145" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9131,7 +9595,7 @@
       <c r="I146" s="4" t="inlineStr"/>
       <c r="J146" s="4" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr"/>
-      <c r="L146" s="7" t="inlineStr">
+      <c r="L146" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9186,7 +9650,7 @@
       <c r="I147" s="4" t="inlineStr"/>
       <c r="J147" s="4" t="inlineStr"/>
       <c r="K147" s="4" t="inlineStr"/>
-      <c r="L147" s="7" t="inlineStr">
+      <c r="L147" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9241,7 +9705,7 @@
       <c r="I148" s="4" t="inlineStr"/>
       <c r="J148" s="4" t="inlineStr"/>
       <c r="K148" s="4" t="inlineStr"/>
-      <c r="L148" s="7" t="inlineStr">
+      <c r="L148" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9296,7 +9760,7 @@
       <c r="I149" s="4" t="inlineStr"/>
       <c r="J149" s="4" t="inlineStr"/>
       <c r="K149" s="4" t="inlineStr"/>
-      <c r="L149" s="7" t="inlineStr">
+      <c r="L149" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9351,7 +9815,7 @@
       <c r="I150" s="4" t="inlineStr"/>
       <c r="J150" s="4" t="inlineStr"/>
       <c r="K150" s="4" t="inlineStr"/>
-      <c r="L150" s="7" t="inlineStr">
+      <c r="L150" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -9414,14 +9878,14 @@
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr"/>
-      <c r="L151" s="7" t="inlineStr">
+      <c r="L151" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9466,8 +9930,16 @@
           <t>FME→FMM.DEV_MEMBERS</t>
         </is>
       </c>
-      <c r="I152" s="4" t="inlineStr"/>
-      <c r="J152" s="4" t="inlineStr"/>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K152" s="4" t="inlineStr"/>
       <c r="L152" s="5" t="inlineStr">
         <is>
@@ -9521,8 +9993,16 @@
           <t>FME→FMM.DEV_CNT</t>
         </is>
       </c>
-      <c r="I153" s="4" t="inlineStr"/>
-      <c r="J153" s="4" t="inlineStr"/>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K153" s="4" t="inlineStr"/>
       <c r="L153" s="5" t="inlineStr">
         <is>
@@ -9576,17 +10056,25 @@
           <t>FME→FMM.INCREASE_MEMBERS</t>
         </is>
       </c>
-      <c r="I154" s="4" t="inlineStr"/>
-      <c r="J154" s="4" t="inlineStr"/>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K154" s="4" t="inlineStr"/>
-      <c r="L154" s="6" t="inlineStr">
+      <c r="L154" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -9631,17 +10119,25 @@
           <t>FME→FMM.INCREASE_CNT</t>
         </is>
       </c>
-      <c r="I155" s="4" t="inlineStr"/>
-      <c r="J155" s="4" t="inlineStr"/>
+      <c r="I155" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K155" s="4" t="inlineStr"/>
-      <c r="L155" s="6" t="inlineStr">
+      <c r="L155" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -9686,17 +10182,21 @@
           <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I156" s="4" t="inlineStr"/>
+      <c r="I156" s="4" t="inlineStr">
+        <is>
+          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
+        </is>
+      </c>
       <c r="J156" s="4" t="inlineStr"/>
       <c r="K156" s="4" t="inlineStr"/>
-      <c r="L156" s="6" t="inlineStr">
+      <c r="L156" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr">
         <is>
-          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_BIZ` 0행</t>
+          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
         </is>
       </c>
     </row>
@@ -9741,17 +10241,21 @@
           <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I157" s="4" t="inlineStr"/>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
+        </is>
+      </c>
       <c r="J157" s="4" t="inlineStr"/>
       <c r="K157" s="4" t="inlineStr"/>
-      <c r="L157" s="6" t="inlineStr">
+      <c r="L157" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
         <is>
-          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_BIZ` 0행</t>
+          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
         </is>
       </c>
     </row>
@@ -9796,17 +10300,21 @@
           <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I158" s="4" t="inlineStr"/>
+      <c r="I158" s="4" t="inlineStr">
+        <is>
+          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
+        </is>
+      </c>
       <c r="J158" s="4" t="inlineStr"/>
       <c r="K158" s="4" t="inlineStr"/>
-      <c r="L158" s="6" t="inlineStr">
+      <c r="L158" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M158" s="4" t="inlineStr">
         <is>
-          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_BIZ` 0행</t>
+          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
         </is>
       </c>
     </row>
@@ -9851,17 +10359,21 @@
           <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I159" s="4" t="inlineStr"/>
+      <c r="I159" s="4" t="inlineStr">
+        <is>
+          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
+        </is>
+      </c>
       <c r="J159" s="4" t="inlineStr"/>
       <c r="K159" s="4" t="inlineStr"/>
-      <c r="L159" s="6" t="inlineStr">
+      <c r="L159" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M159" s="4" t="inlineStr">
         <is>
-          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_BIZ` 0행</t>
+          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
         </is>
       </c>
     </row>
@@ -9906,17 +10418,25 @@
           <t>FMM.ACTIVE_MEMBERS</t>
         </is>
       </c>
-      <c r="I160" s="4" t="inlineStr"/>
-      <c r="J160" s="4" t="inlineStr"/>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K160" s="4" t="inlineStr"/>
       <c r="L160" s="6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 39,854,335/41,508,842 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -9961,17 +10481,25 @@
           <t>FMM.ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I161" s="4" t="inlineStr"/>
-      <c r="J161" s="4" t="inlineStr"/>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K161" s="4" t="inlineStr"/>
       <c r="L161" s="6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -10016,10 +10544,18 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I162" s="4" t="inlineStr"/>
-      <c r="J162" s="4" t="inlineStr"/>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K162" s="4" t="inlineStr"/>
-      <c r="L162" s="7" t="inlineStr">
+      <c r="L162" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10071,17 +10607,25 @@
           <t>FMM.ACTIVE_CUM_CNT</t>
         </is>
       </c>
-      <c r="I163" s="4" t="inlineStr"/>
-      <c r="J163" s="4" t="inlineStr"/>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K163" s="4" t="inlineStr"/>
-      <c r="L163" s="6" t="inlineStr">
+      <c r="L163" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -10126,10 +10670,18 @@
           <t>FSE (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I164" s="4" t="inlineStr"/>
-      <c r="J164" s="4" t="inlineStr"/>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+        </is>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="K164" s="4" t="inlineStr"/>
-      <c r="L164" s="7" t="inlineStr">
+      <c r="L164" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10181,10 +10733,18 @@
           <t>FSE (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I165" s="4" t="inlineStr"/>
-      <c r="J165" s="4" t="inlineStr"/>
+      <c r="I165" s="4" t="inlineStr">
+        <is>
+          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+        </is>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+        </is>
+      </c>
       <c r="K165" s="4" t="inlineStr"/>
-      <c r="L165" s="7" t="inlineStr">
+      <c r="L165" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10236,10 +10796,18 @@
           <t>DIM_REASON</t>
         </is>
       </c>
-      <c r="I166" s="4" t="inlineStr"/>
-      <c r="J166" s="4" t="inlineStr"/>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t>CRM_CODE.DTL_CD_ID</t>
+        </is>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD</t>
+        </is>
+      </c>
       <c r="K166" s="4" t="inlineStr"/>
-      <c r="L166" s="7" t="inlineStr">
+      <c r="L166" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10291,14 +10859,22 @@
           <t>FMM (measure — 컬럼 06_DDL.sql 확인)</t>
         </is>
       </c>
-      <c r="I167" s="4" t="inlineStr"/>
-      <c r="J167" s="4" t="inlineStr"/>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+        </is>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K167" s="4" t="inlineStr">
         <is>
           <t>캠페인 가입 이후 납입하는 회비</t>
         </is>
       </c>
-      <c r="L167" s="7" t="inlineStr">
+      <c r="L167" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10357,7 +10933,7 @@
           <t>고유ID(회원번호×캠페인가입일×후원사업×캠페인명) 기준 매칭되는 캠페인가입일로부터 조회기준일까지의 총 개월수</t>
         </is>
       </c>
-      <c r="L168" s="7" t="inlineStr">
+      <c r="L168" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10416,7 +10992,7 @@
           <t>고유ID(회원번호×캠페인가입일×후원사업×캠페인명) 기준 매칭되는 캠페인가입일로부터 조회기준일까지의 총 년수</t>
         </is>
       </c>
-      <c r="L169" s="7" t="inlineStr">
+      <c r="L169" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10468,8 +11044,16 @@
           <t>SV metric — 분자: Σ(유지기간×DEV_MEMBERS) / 분모: DEV_MEMBERS(총)</t>
         </is>
       </c>
-      <c r="I170" s="4" t="inlineStr"/>
-      <c r="J170" s="4" t="inlineStr"/>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K170" s="4" t="inlineStr">
         <is>
           <t>{(개발캠페인별 유지기간×해당 유지기간 총 회원수)의 합} / 캠페인 가입한 총 회원수</t>
@@ -10534,7 +11118,7 @@
           <t>{(개발캠페인별 유지기간×해당 유지기간 총 회원수)의 합} / 캠페인 가입한 총 회원수</t>
         </is>
       </c>
-      <c r="L171" s="7" t="inlineStr">
+      <c r="L171" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10593,7 +11177,7 @@
           <t>N개월 시점에 캠페인 가입유지중인 회원수 / N개월까지 가입한 회원수</t>
         </is>
       </c>
-      <c r="L172" s="7" t="inlineStr">
+      <c r="L172" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10652,7 +11236,7 @@
           <t>(N개월 시점에 캠페인 가입유지중인 회원수 / N개월까지 가입한 회원수) × 100</t>
         </is>
       </c>
-      <c r="L173" s="7" t="inlineStr">
+      <c r="L173" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10711,7 +11295,7 @@
           <t>평균 납입회비 × 평균 활동 기간</t>
         </is>
       </c>
-      <c r="L174" s="7" t="inlineStr">
+      <c r="L174" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -10837,7 +11421,7 @@
           <t>ERP 모금성 비용 / 신규 획득 개발 건수</t>
         </is>
       </c>
-      <c r="L176" s="6" t="inlineStr">
+      <c r="L176" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -10889,21 +11473,29 @@
           <t>SV metric — 분자: PAID_FEE(또는 LTV) − 비용 / 분모: 비용(FBD)</t>
         </is>
       </c>
-      <c r="I177" s="4" t="inlineStr"/>
-      <c r="J177" s="4" t="inlineStr"/>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K177" s="4" t="inlineStr">
         <is>
           <t>(총 수익−총 비용) / 총 비용 × 100</t>
         </is>
       </c>
-      <c r="L177" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L177" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M177" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10948,8 +11540,16 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I178" s="4" t="inlineStr"/>
-      <c r="J178" s="4" t="inlineStr"/>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동건 / (캠페인별 개발누계건 + 캠페인별 연도초활동건)</t>
@@ -10957,12 +11557,12 @@
       </c>
       <c r="L178" s="6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -11007,8 +11607,16 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I179" s="4" t="inlineStr"/>
-      <c r="J179" s="4" t="inlineStr"/>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인 활동건 / (캠페인 개발누계건 + 캠페인 연도초활동건)</t>
@@ -11016,12 +11624,12 @@
       </c>
       <c r="L179" s="6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M179" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -11066,8 +11674,16 @@
           <t>SV metric — 분자: ACTIVE_CNT / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I180" s="4" t="inlineStr"/>
-      <c r="J180" s="4" t="inlineStr"/>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K180" s="4" t="inlineStr">
         <is>
           <t>캠페인별 납입방식 활동건 / (캠페인별 납입방식 개발누계건 + 캠페인별 납입방식 연도초활동건)</t>
@@ -11075,12 +11691,12 @@
       </c>
       <c r="L180" s="6" t="inlineStr">
         <is>
-          <t>WAIT</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -11125,21 +11741,29 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I181" s="4" t="inlineStr"/>
-      <c r="J181" s="4" t="inlineStr"/>
+      <c r="I181" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K181" s="4" t="inlineStr">
         <is>
           <t>캠페인별 중단(건) / (캠페인별 개발(건) + 캠페인별 연도초활동회원(건))</t>
         </is>
       </c>
-      <c r="L181" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L181" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M181" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11184,21 +11808,29 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT+PREV_MONTH_END_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I182" s="4" t="inlineStr"/>
-      <c r="J182" s="4" t="inlineStr"/>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K182" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인 중단(건) / (캠페인 개발(건) + 캠페인 전월말활동회원(건))</t>
         </is>
       </c>
-      <c r="L182" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L182" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M182" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11243,21 +11875,29 @@
           <t>SV metric — 분자: STOP_CNT(YTD) / 분모: DEV_CNT(YTD)+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I183" s="4" t="inlineStr"/>
-      <c r="J183" s="4" t="inlineStr"/>
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K183" s="4" t="inlineStr">
         <is>
           <t>캠페인별 누계중단(건) / (캠페인별 누계개발(건) + 캠페인별 연도초활동회원(건))</t>
         </is>
       </c>
-      <c r="L183" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L183" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M183" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11302,21 +11942,29 @@
           <t>SV metric — 분자: STOP_CNT(YTD) / 분모: DEV_CNT(YTD)</t>
         </is>
       </c>
-      <c r="I184" s="4" t="inlineStr"/>
-      <c r="J184" s="4" t="inlineStr"/>
+      <c r="I184" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J184" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K184" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인 누계중단(건) / 캠페인별 누계개발(건)</t>
         </is>
       </c>
-      <c r="L184" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L184" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M184" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11361,21 +12009,29 @@
           <t>SV metric — 분자: STOP_CNT / 분모: DEV_CNT+YEAR_START_ACTIVE_CNT</t>
         </is>
       </c>
-      <c r="I185" s="4" t="inlineStr"/>
-      <c r="J185" s="4" t="inlineStr"/>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J185" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K185" s="4" t="inlineStr">
         <is>
           <t>캠페인별 납입방식 중단(건) / (캠페인별 납입방식 개발(건) + 캠페인별 연도초활동회원(건))</t>
         </is>
       </c>
-      <c r="L185" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L185" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M185" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11420,21 +12076,29 @@
           <t>FMM.CHURN_CNT</t>
         </is>
       </c>
-      <c r="I186" s="4" t="inlineStr"/>
-      <c r="J186" s="4" t="inlineStr"/>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K186" s="4" t="inlineStr">
         <is>
           <t>후원취소 및 감액한 후원사업의 금액 / 10,000</t>
         </is>
       </c>
-      <c r="L186" s="6" t="inlineStr">
+      <c r="L186" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M186" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -11479,21 +12143,29 @@
           <t>SV metric — 분자: CHURN_CNT / 분모: DEV_CNT</t>
         </is>
       </c>
-      <c r="I187" s="4" t="inlineStr"/>
-      <c r="J187" s="4" t="inlineStr"/>
+      <c r="I187" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J187" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K187" s="4" t="inlineStr">
         <is>
           <t>캠페인별 이탈(건) / 캠페인별 개발(건)</t>
         </is>
       </c>
-      <c r="L187" s="6" t="inlineStr">
+      <c r="L187" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M187" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -11538,21 +12210,29 @@
           <t>SV metric — 분자: PAID_FEE / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I188" s="4" t="inlineStr"/>
-      <c r="J188" s="4" t="inlineStr"/>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J188" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K188" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동회원의 월 납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L188" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L188" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M188" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11597,21 +12277,29 @@
           <t>SV metric — 분자: PAID_FEE / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I189" s="4" t="inlineStr"/>
-      <c r="J189" s="4" t="inlineStr"/>
+      <c r="I189" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J189" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K189" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인별 활동회원의 월 납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L189" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L189" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M189" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11656,21 +12344,29 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I190" s="4" t="inlineStr"/>
-      <c r="J190" s="4" t="inlineStr"/>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J190" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K190" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동회원 월 누계납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L190" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L190" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M190" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11715,21 +12411,29 @@
           <t>SV metric — 분자: PAID_FEE(YTD) / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I191" s="4" t="inlineStr"/>
-      <c r="J191" s="4" t="inlineStr"/>
+      <c r="I191" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J191" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K191" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인별 활동회원 월 누계납입회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L191" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L191" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M191" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11774,21 +12478,29 @@
           <t>SV metric — 분자: PAID_FEE(캠페인) / 분모: PAID_FEE(전체)</t>
         </is>
       </c>
-      <c r="I192" s="4" t="inlineStr"/>
-      <c r="J192" s="4" t="inlineStr"/>
+      <c r="I192" s="4" t="inlineStr">
+        <is>
+          <t>CRM_PAYMENT_BILLING.PAY_AMT</t>
+        </is>
+      </c>
+      <c r="J192" s="4" t="inlineStr">
+        <is>
+          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K192" s="4" t="inlineStr">
         <is>
           <t>캠페인별 납입회비 / 총 납입회비 금액 × 100</t>
         </is>
       </c>
-      <c r="L192" s="6" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L192" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M192" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11833,21 +12545,29 @@
           <t>SV metric — 분자: CAMPAIGN_UNPAID_CNT ×10000 / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I193" s="4" t="inlineStr"/>
-      <c r="J193" s="4" t="inlineStr"/>
+      <c r="I193" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J193" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K193" s="4" t="inlineStr">
         <is>
           <t>캠페인별 활동회원의 월 미납회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L193" s="6" t="inlineStr">
+      <c r="L193" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M193" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -11892,21 +12612,29 @@
           <t>SV metric — 분자: CAMPAIGN_UNPAID_CNT ×10000 / 분모: MONTH_END_ACTIVE_CNT ×10000</t>
         </is>
       </c>
-      <c r="I194" s="4" t="inlineStr"/>
-      <c r="J194" s="4" t="inlineStr"/>
+      <c r="I194" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J194" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K194" s="4" t="inlineStr">
         <is>
           <t>조회시점 기준 캠페인별 활동회원의 월 미납회비 / (캠페인별 월말활동회원건 × 10,000)</t>
         </is>
       </c>
-      <c r="L194" s="6" t="inlineStr">
+      <c r="L194" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -11951,21 +12679,29 @@
           <t>SV metric — 분자: CAMPAIGN_UNPAID_CNT(캠페인) / 분모: CAMPAIGN_UNPAID_CNT(전체)</t>
         </is>
       </c>
-      <c r="I195" s="4" t="inlineStr"/>
-      <c r="J195" s="4" t="inlineStr"/>
+      <c r="I195" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+        </is>
+      </c>
+      <c r="J195" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+        </is>
+      </c>
       <c r="K195" s="4" t="inlineStr">
         <is>
           <t>캠페인별 미납회비 / 총 미납회비 금액 × 100</t>
         </is>
       </c>
-      <c r="L195" s="6" t="inlineStr">
+      <c r="L195" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
       </c>
       <c r="M195" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12761,7 @@
           <t>서비스별 발송수(명) / 전체회원수(명) × 100</t>
         </is>
       </c>
-      <c r="L196" s="7" t="inlineStr">
+      <c r="L196" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12203,8 +12939,16 @@
           <t>SV metric — 분자: DEV_MEMBERS / 분모: BigQuery 클릭회원(명)</t>
         </is>
       </c>
-      <c r="I199" s="4" t="inlineStr"/>
-      <c r="J199" s="4" t="inlineStr"/>
+      <c r="I199" s="4" t="inlineStr">
+        <is>
+          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="J199" s="4" t="inlineStr">
+        <is>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+        </is>
+      </c>
       <c r="K199" s="4" t="inlineStr">
         <is>
           <t>개발회원(명) / 서비스 클릭수(명) × 100</t>
@@ -12269,7 +13013,7 @@
           <t>(증액 회원수(명,건) / 서비스별 발송 성공회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L200" s="7" t="inlineStr">
+      <c r="L200" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12328,7 +13072,7 @@
           <t>(서비스별 증액 후 N개월 시점 유지 회원(명,건) / 서비스별 증액 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L201" s="7" t="inlineStr">
+      <c r="L201" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12387,7 +13131,7 @@
           <t>(서비스별 발송 후 N개월 시점 유지 회원(명,건) / 서비스별 참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L202" s="7" t="inlineStr">
+      <c r="L202" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12446,7 +13190,7 @@
           <t>(서비스별 증액회원 중 납입회원(명,건) / 서비스별 증액회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 증액회원의 납입회비) / 서비스별 증액회원(명)</t>
         </is>
       </c>
-      <c r="L203" s="7" t="inlineStr">
+      <c r="L203" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12505,7 +13249,7 @@
           <t>(서비스별 참여회원 중 납입회원(명,건) / 서비스별 참여회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 참여회원의 납입회비) / 서비스별 참여회원(명)</t>
         </is>
       </c>
-      <c r="L204" s="7" t="inlineStr">
+      <c r="L204" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12564,7 +13308,7 @@
           <t>(서비스별 증액회원 중 중단회원(명,건) / 서비스별 증액회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L205" s="7" t="inlineStr">
+      <c r="L205" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12623,7 +13367,7 @@
           <t>(서비스별 참여회원 중 중단회원(명,건) / 서비스별 참여회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L206" s="7" t="inlineStr">
+      <c r="L206" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12682,7 +13426,7 @@
           <t>(해당 캠페인 서비스별 증액회원(명,건) / 서비스별 전체 증액회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L207" s="7" t="inlineStr">
+      <c r="L207" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12741,7 +13485,7 @@
           <t>(해당 캠페인 서비스별 참여회원(명,건) / 서비스별 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L208" s="7" t="inlineStr">
+      <c r="L208" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12800,7 +13544,7 @@
           <t>(해당 서비스·캠페인 조합에서 N개월 시점 유지 회원(명,건) / 해당 캠페인 가입회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L209" s="7" t="inlineStr">
+      <c r="L209" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12867,7 +13611,7 @@
           <t>(서비스별 서신 참여회원(명,건) / 해당 서비스 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L210" s="6" t="inlineStr">
+      <c r="L210" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -12926,7 +13670,7 @@
           <t>(서신참여 후 N개월 시점 유지 회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L211" s="7" t="inlineStr">
+      <c r="L211" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -12985,7 +13729,7 @@
           <t>(서비스별 서신참여회원 중 납입회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 서신참여회원의 납입회비) / 서비스별 서신참여회원(명)</t>
         </is>
       </c>
-      <c r="L212" s="7" t="inlineStr">
+      <c r="L212" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13044,7 +13788,7 @@
           <t>(서비스별 서신참여회원 중 중단회원(명,건) / 서비스별 서신참여 회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L213" s="7" t="inlineStr">
+      <c r="L213" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13103,7 +13847,7 @@
           <t>(해당 캠페인 서비스별 서신참여회원(명,건) / 서비스별 전체 서신참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L214" s="7" t="inlineStr">
+      <c r="L214" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13170,7 +13914,7 @@
           <t>(서비스별 선물금 참여회원(명,건) / 해당 서비스 참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L215" s="6" t="inlineStr">
+      <c r="L215" s="7" t="inlineStr">
         <is>
           <t>WAIT</t>
         </is>
@@ -13229,7 +13973,7 @@
           <t>(서비스별 선물금참여 후 N개월 시점 유지 회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. 유지기간 = AVG(중단일자−가입일자) or AVG(기준일자−가입일자)</t>
         </is>
       </c>
-      <c r="L216" s="7" t="inlineStr">
+      <c r="L216" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13288,7 +14032,7 @@
           <t>(서비스별 선물금참여회원 중 납입회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. 평균 납입회비 = SUM(서비스별 선물금참여회원의 납입회비) / 서비스별 선물금참여회원수(명)</t>
         </is>
       </c>
-      <c r="L217" s="7" t="inlineStr">
+      <c r="L217" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13347,7 +14091,7 @@
           <t>(서비스별 선물금참여회원 중 중단회원(명,건) / 서비스별 선물금참여 회원(명,건)) × 100. +5일내 중단(명,건) / 총 발송(명,건)</t>
         </is>
       </c>
-      <c r="L218" s="7" t="inlineStr">
+      <c r="L218" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13406,7 +14150,7 @@
           <t>(해당 캠페인 서비스별 선물금참여회원(명,건) / 서비스별 전체 선물금참여회원(명,건)) × 100</t>
         </is>
       </c>
-      <c r="L219" s="7" t="inlineStr">
+      <c r="L219" s="6" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -13445,7 +14189,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-15</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -13724,7 +14468,7 @@
       <c r="F10" s="4" t="inlineStr"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>FACT_DEV_ACHIEVEMENT.ACTUAL_CNT</t>
+          <t>FACT_MEMBER_DEV_ACHIEVEMENT.ACTUAL_CNT</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
@@ -16567,7 +17311,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-15</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-16</t>
         </is>
       </c>
     </row>
@@ -25705,7 +26449,7 @@
       <c r="F215" s="4" t="inlineStr"/>
       <c r="G215" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SUCCESS_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS</t>
         </is>
       </c>
       <c r="H215" s="4" t="inlineStr"/>
@@ -25744,7 +26488,7 @@
       <c r="F216" s="4" t="inlineStr"/>
       <c r="G216" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.FAIL_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.FAIL_MEMBERS</t>
         </is>
       </c>
       <c r="H216" s="4" t="inlineStr"/>
@@ -27186,7 +27930,7 @@
       <c r="F250" s="4" t="inlineStr"/>
       <c r="G250" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SUCCESS_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS</t>
         </is>
       </c>
       <c r="H250" s="4" t="inlineStr"/>
@@ -27225,7 +27969,7 @@
       <c r="F251" s="4" t="inlineStr"/>
       <c r="G251" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.FAIL_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.FAIL_MEMBERS</t>
         </is>
       </c>
       <c r="H251" s="4" t="inlineStr"/>
@@ -29003,7 +29747,7 @@
       <c r="F293" s="4" t="inlineStr"/>
       <c r="G293" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SUCCESS_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS</t>
         </is>
       </c>
       <c r="H293" s="4" t="inlineStr"/>
@@ -29042,7 +29786,7 @@
       <c r="F294" s="4" t="inlineStr"/>
       <c r="G294" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.FAIL_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.FAIL_MEMBERS</t>
         </is>
       </c>
       <c r="H294" s="4" t="inlineStr"/>
@@ -29124,7 +29868,7 @@
       <c r="F296" s="4" t="inlineStr"/>
       <c r="G296" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.OPEN_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.OPEN_MEMBERS</t>
         </is>
       </c>
       <c r="H296" s="4" t="inlineStr"/>
@@ -30214,7 +30958,7 @@
       <c r="F322" s="4" t="inlineStr"/>
       <c r="G322" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SUCCESS_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS</t>
         </is>
       </c>
       <c r="H322" s="4" t="inlineStr"/>
@@ -30253,7 +30997,7 @@
       <c r="F323" s="4" t="inlineStr"/>
       <c r="G323" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.FAIL_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.FAIL_MEMBERS</t>
         </is>
       </c>
       <c r="H323" s="4" t="inlineStr"/>
@@ -34896,7 +35640,7 @@
       <c r="F432" s="4" t="inlineStr"/>
       <c r="G432" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SEND_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.SEND_MEMBERS</t>
         </is>
       </c>
       <c r="H432" s="4" t="inlineStr"/>
@@ -34935,7 +35679,7 @@
       <c r="F433" s="4" t="inlineStr"/>
       <c r="G433" s="4" t="inlineStr">
         <is>
-          <t>FACT_SERVICE_EVENT.SUCCESS_MEMBERS</t>
+          <t>FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS</t>
         </is>
       </c>
       <c r="H433" s="4" t="inlineStr"/>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-16 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-28 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-16</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,729/4,716,360 (49.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,458/4,716,088 (49.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,729/4,716,360 (49.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,458/4,716,088 (49.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,729/4,716,360 (49.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,458/4,716,088 (49.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 2,025,238/41,508,842 (4.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 2,025,221/41,508,824 (4.9%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 2,025,238/41,508,842 (4.9%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 2,025,221/41,508,824 (4.9%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 234,859/248,196 (94.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 58,678/77,505 (75.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 234,859/248,196 (94.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 58,678/77,505 (75.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 234,859/248,196 (94.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 58,678/77,505 (75.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 176,578/248,196 (71.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 25,148/77,505 (32.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 46,485/248,196 (18.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 7,139/77,505 (9.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 8,905행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 199,322/248,196 (80.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 23,255/77,505 (30.0%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 176,578/248,196 (71.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 25,148/77,505 (32.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,452/248,196 (9.0%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 21,459/77,505 (27.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,431/4,716,360 (22.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,430/4,716,088 (22.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2945,14 +2945,14 @@
           <t>회원번호 기준, 회원상태가 미납인 회원의 총 개발 건 ( = 전체 후원금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,381,518/41,508,824 (8.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -3079,14 +3079,14 @@
           <t>회원번호 기준, 후원사업(세부캠페인)별 총 감액 건 ( = 전체 감액금액 / 10,000 )</t>
         </is>
       </c>
-      <c r="L42" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 비영 115,399/41,508,824 (0.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 2,025,238/41,508,842 (4.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 2,025,221/41,508,824 (4.9%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 36,847,772/41,508,842 (88.8%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 36,847,772/41,508,824 (88.8%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 39,122,763/41,508,842 (94.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 39,122,763/41,508,824 (94.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,431/4,716,360 (22.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,430/4,716,088 (22.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,431/4,716,360 (22.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,430/4,716,088 (22.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,431/4,716,360 (22.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,430/4,716,088 (22.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 36,800,958/41,508,842 (88.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 36,800,958/41,508,824 (88.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 38,579,737/41,508,842 (92.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 38,579,737/41,508,824 (92.9%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5525,14 +5525,14 @@
           <t>미납(건) / 활동(건)</t>
         </is>
       </c>
-      <c r="L80" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,381,518/41,508,824 (8.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5592,14 +5592,14 @@
           <t>신규미납(건) / 신규활동(건)</t>
         </is>
       </c>
-      <c r="L81" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,381,518/41,508,824 (8.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5659,14 +5659,14 @@
           <t>기존미납(건) / 기존활동(건)</t>
         </is>
       </c>
-      <c r="L82" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,381,518/41,508,824 (8.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5726,14 +5726,14 @@
           <t>후원사업 미납(건) / 후원사업 활동(건)</t>
         </is>
       </c>
-      <c r="L83" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L83" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,381,518/41,508,824 (8.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 41,969,590/41,969,590 (100.0%)</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 41,935,344/41,935,344 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 25,417,305/41,969,590 (60.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 25,384,521/41,935,344 (60.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 2,034,794/41,969,590 (4.8%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 2,034,467/41,935,344 (4.9%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr"/>
-      <c r="L101" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="L101" s="7" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 160,166/160,166 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.AVG_SESSION_DURATION` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 7,862행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7040,7 +7040,7 @@
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 7,862행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 7,862행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 142행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 142행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7474,14 +7474,14 @@
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr"/>
-      <c r="L111" s="5" t="inlineStr">
-        <is>
-          <t>PARTIAL</t>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>WAIT</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 30,842/160,166 (19.3%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="M112" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.BOUNCE_RATE` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 142행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 1행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="M141" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_DATE` 16,437행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_DATE` 73,415행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,325,729/4,716,360 (49.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,325,458/4,716,088 (49.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,729/4,716,360 (49.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,458/4,716,088 (49.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10067,14 +10067,14 @@
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr"/>
-      <c r="L154" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L154" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 비영 1,840,830/41,508,824 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10130,14 +10130,14 @@
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr"/>
-      <c r="L155" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L155" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 비영 1,840,830/41,508,824 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 39,854,335/41,508,842 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 39,854,330/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -10618,14 +10618,14 @@
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr"/>
-      <c r="L163" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L163" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 비영 40,335,569/41,508,824 (97.2%)</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="M170" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,325,729/4,716,360 (49.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,325,458/4,716,088 (49.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="M177" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11562,7 +11562,7 @@
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -11629,7 +11629,7 @@
       </c>
       <c r="M179" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11696,7 @@
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,326/41,508,842 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="M181" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11830,7 +11830,7 @@
       </c>
       <c r="M182" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11897,7 +11897,7 @@
       </c>
       <c r="M183" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11964,7 +11964,7 @@
       </c>
       <c r="M184" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="M185" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,491/41,508,842 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12091,14 +12091,14 @@
           <t>후원취소 및 감액한 후원사업의 금액 / 10,000</t>
         </is>
       </c>
-      <c r="L186" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L186" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M186" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,227,134/41,508,824 (3.0%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12158,14 +12158,14 @@
           <t>캠페인별 이탈(건) / 캠페인별 개발(건)</t>
         </is>
       </c>
-      <c r="L187" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L187" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M187" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,227,134/41,508,824 (3.0%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12232,7 +12232,7 @@
       </c>
       <c r="M188" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M189" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="M190" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12433,7 +12433,7 @@
       </c>
       <c r="M191" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12500,7 +12500,7 @@
       </c>
       <c r="M192" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,842 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12768,7 @@
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 41,969,590/41,969,590 (100.0%)</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 41,935,344/41,935,344 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="M197" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 25,417,305/41,969,590 (60.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 25,384,521/41,935,344 (60.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12961,7 +12961,7 @@
       </c>
       <c r="M199" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,325,729/4,716,360 (49.3%) · GA↔CRM identity 커버리지 종속</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,325,458/4,716,088 (49.3%) · GA↔CRM identity 커버리지 종속</t>
         </is>
       </c>
     </row>
@@ -14189,7 +14189,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-16</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-28</t>
         </is>
       </c>
     </row>
@@ -17311,7 +17311,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-16</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-28</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -2932,12 +2932,12 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+          <t>CRM_MEMBER_SPONSOR_SPAN.DSCNTC_MONTH_KEY</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr"/>
@@ -4953,12 +4953,12 @@
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+          <t>CRM_MEMBER_SPONSOR_SPAN.DSCNTC_MONTH_KEY</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+          <t>CRM_MEMBER_SPONSOR_SPAN.DSCNTC_MONTH_KEY</t>
         </is>
       </c>
       <c r="J72" s="4" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr">
@@ -5713,12 +5713,12 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+          <t>CRM_MEMBER_SPONSOR_SPAN.DSCNTC_MONTH_KEY</t>
         </is>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr">
@@ -6300,12 +6300,12 @@
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+          <t>CRM_RELATION_ACTIVITY.SNDNG_DE</t>
         </is>
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr">
@@ -6367,12 +6367,12 @@
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+          <t>CRM_RELATION_ACTIVITY.SNDNG_DE</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr"/>
@@ -6430,12 +6430,12 @@
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr"/>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="J154" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr"/>
@@ -10121,12 +10121,12 @@
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr"/>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="I162" s="4" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+          <t>CRM_MEMBER_SPONSOR_SPAN.DSCNTC_MONTH_KEY</t>
         </is>
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS</t>
         </is>
       </c>
       <c r="K162" s="4" t="inlineStr"/>
@@ -10609,12 +10609,12 @@
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER;CRM_MEMBER_AMT_CHANGE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
+          <t>CRM_MEMBER.MEMBER_DK</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_IRSD;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TC_CMMN_DTL_CD;TM_MM_FDRM_MBER_INFO;TM_MM_ONCE_MBER_INFO</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr"/>
@@ -10672,12 +10672,12 @@
       </c>
       <c r="I164" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+          <t>CRM_RELATION_ACTIVITY.SNDNG_DE</t>
         </is>
       </c>
       <c r="J164" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr"/>
@@ -10735,12 +10735,12 @@
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+          <t>CRM_RELATION_ACTIVITY.SNDNG_DE</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr"/>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>CRM_PAYMENT_BILLING.PAY_DE</t>
+          <t>CRM_MEMBER_SPONSOR_SPAN.DSCNTC_MONTH_KEY</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
+          <t>TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
@@ -13598,12 +13598,12 @@
       </c>
       <c r="I210" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER.SNDNG_DE</t>
+          <t>CRM_RELATION_ACTIVITY.SNDNG_DE</t>
         </is>
       </c>
       <c r="J210" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL</t>
+          <t>TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO</t>
         </is>
       </c>
       <c r="K210" s="4" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="I215" s="4" t="inlineStr">
         <is>
-          <t>CRM_SEND_MEMBER;CRM_SEND_REQUEST</t>
+          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
         </is>
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG</t>
+          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
         </is>
       </c>
       <c r="K215" s="4" t="inlineStr">

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-28 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-29 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-28</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -6844,14 +6844,14 @@
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr"/>
-      <c r="L101" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 1,663,437/1,663,437 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="M102" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.AVG_SESSION_DURATION` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 47,859행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7040,7 +7040,7 @@
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 47,859행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 47,859행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 480행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 480행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7474,14 +7474,14 @@
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr"/>
-      <c r="L111" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L111" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 330,438/1,663,437 (19.9%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="M112" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR` **0행** — 테이블 미적재</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.BOUNCE_RATE` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 1행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 480행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -10187,7 +10187,11 @@
           <t>CRM_BIZ_TARGET.MONTH_KEY</t>
         </is>
       </c>
-      <c r="J156" s="4" t="inlineStr"/>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
       <c r="K156" s="4" t="inlineStr"/>
       <c r="L156" s="7" t="inlineStr">
         <is>
@@ -10246,7 +10250,11 @@
           <t>CRM_BIZ_TARGET.MONTH_KEY</t>
         </is>
       </c>
-      <c r="J157" s="4" t="inlineStr"/>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
       <c r="K157" s="4" t="inlineStr"/>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -10305,7 +10313,11 @@
           <t>CRM_BIZ_TARGET.MONTH_KEY</t>
         </is>
       </c>
-      <c r="J158" s="4" t="inlineStr"/>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
       <c r="K158" s="4" t="inlineStr"/>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -10364,7 +10376,11 @@
           <t>CRM_BIZ_TARGET.MONTH_KEY</t>
         </is>
       </c>
-      <c r="J159" s="4" t="inlineStr"/>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>TM_CM_MBER_DVLP_GOAL_DIV</t>
+        </is>
+      </c>
       <c r="K159" s="4" t="inlineStr"/>
       <c r="L159" s="7" t="inlineStr">
         <is>
@@ -14189,7 +14205,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-28</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-29</t>
         </is>
       </c>
     </row>
@@ -17311,7 +17327,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-28</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-29</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-29 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-01 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-29</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 58,678/77,505 (75.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 245,204/271,175 (90.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 58,678/77,505 (75.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 245,204/271,175 (90.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 58,678/77,505 (75.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 245,204/271,175 (90.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 25,148/77,505 (32.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 189,300/271,175 (69.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 7,139/77,505 (9.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 50,949/271,175 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 3,367행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 23,255/77,505 (30.0%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 210,773/271,175 (77.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 25,148/77,505 (32.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 189,300/271,175 (69.8%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 21,459/77,505 (27.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,599/271,175 (8.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 1,663,437/1,663,437 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 1,398,512/1,398,512 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 47,859행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 41,762행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7040,7 +7040,7 @@
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 47,859행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 41,762행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 47,859행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 41,762행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 480행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 533행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 480행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 533행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 330,438/1,663,437 (19.9%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 294,660/1,398,512 (21.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 480행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 533행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-29</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-01</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-09-29</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-01</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-01 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-02 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-01</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-01</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-01</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-02</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-02 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-07 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-02</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,458/4,716,088 (49.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,982,027/4,757,065 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,458/4,716,088 (49.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,982,027/4,757,065 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,458/4,716,088 (49.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,982,027/4,757,065 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 2,025,221/41,508,824 (4.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,879,345/42,272,226 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 2,025,221/41,508,824 (4.9%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,879,345/42,272,226 (4.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 245,204/271,175 (90.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 252,475/279,202 (90.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 245,204/271,175 (90.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 252,475/279,202 (90.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 245,204/271,175 (90.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 252,475/279,202 (90.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 189,300/271,175 (69.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 195,942/279,202 (70.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 50,949/271,175 (18.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 52,336/279,202 (18.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,696행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 210,773/271,175 (77.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 218,127/279,202 (78.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 189,300/271,175 (69.8%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 195,942/279,202 (70.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,599/271,175 (8.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,607/279,202 (8.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,430/4,716,088 (22.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,072,829/4,757,065 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,381,518/41,508,824 (8.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,454,270/42,272,226 (8.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 비영 115,399/41,508,824 (0.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 비영 116,591/42,272,226 (0.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 2,025,221/41,508,824 (4.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,879,345/42,272,226 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 36,847,772/41,508,824 (88.8%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 37,524,187/42,272,226 (88.8%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 39,122,763/41,508,824 (94.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 39,872,779/42,272,226 (94.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,430/4,716,088 (22.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,072,829/4,757,065 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,430/4,716,088 (22.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,072,829/4,757,065 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,061,430/4,716,088 (22.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,072,829/4,757,065 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 36,800,958/41,508,824 (88.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 37,509,013/42,272,226 (88.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 38,579,737/41,508,824 (92.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 39,331,147/42,272,226 (93.0%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,381,518/41,508,824 (8.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,454,270/42,272,226 (8.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,381,518/41,508,824 (8.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,454,270/42,272,226 (8.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,381,518/41,508,824 (8.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,454,270/42,272,226 (8.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,381,518/41,508,824 (8.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,454,270/42,272,226 (8.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 41,935,344/41,935,344 (100.0%)</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 43,440,831/43,440,831 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 25,384,521/41,935,344 (60.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 25,826,805/43,440,831 (59.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 2,034,467/41,935,344 (4.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 2,055,449/43,440,831 (4.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 1,398,512/1,398,512 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 1,536,507/1,536,507 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 41,762행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 40,811행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7040,7 +7040,7 @@
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 41,762행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 40,811행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 41,762행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 40,811행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 533행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 481행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 533행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 481행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 294,660/1,398,512 (21.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 304,845/1,536,507 (19.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 533행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 481행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="M114" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,785,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,796,799행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,785,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,796,799행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,785,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,796,799행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,785,299행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9885,7 +9885,7 @@
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 36,769행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,325,458/4,716,088 (49.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,982,027/4,757,065 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 2,325,458/4,716,088 (49.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,982,027/4,757,065 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="M154" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 비영 1,840,830/41,508,824 (4.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 비영 1,853,923/42,272,226 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="M155" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 비영 1,840,830/41,508,824 (4.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 비영 1,853,923/42,272,226 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 39,854,330/41,508,824 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 40,606,430/42,272,226 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -10641,7 +10641,7 @@
       </c>
       <c r="M163" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 비영 40,335,569/41,508,824 (97.2%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 비영 41,096,945/42,272,226 (97.2%)</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="M170" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,325,458/4,716,088 (49.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,982,027/4,757,065 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11511,7 @@
       </c>
       <c r="M177" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11578,7 +11578,7 @@
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="M179" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 39,854,321/41,508,824 (96.0%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="M181" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="M182" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="M183" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11980,7 +11980,7 @@
       </c>
       <c r="M184" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="M185" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 992,490/41,508,824 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M186" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,227,134/41,508,824 (3.0%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,238,774/42,272,226 (2.9%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="M187" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,227,134/41,508,824 (3.0%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,238,774/42,272,226 (2.9%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="M188" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12315,7 +12315,7 @@
       </c>
       <c r="M189" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="M190" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M191" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12516,7 @@
       </c>
       <c r="M192" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 37,459,838/41,508,824 (90.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 41,935,344/41,935,344 (100.0%)</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 43,440,831/43,440,831 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="M197" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 25,384,521/41,935,344 (60.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 25,826,805/43,440,831 (59.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="M199" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 2,325,458/4,716,088 (49.3%) · GA↔CRM identity 커버리지 종속</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,982,027/4,757,065 (41.7%) · GA↔CRM identity 커버리지 종속</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-02</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-02</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -26792,18 +26792,18 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>(215밖)</t>
+          <t>공138</t>
         </is>
       </c>
       <c r="G223" s="4" t="inlineStr">
         <is>
-          <t>FACT_MESSAGE_DISPATCH.SEND_STATUS2</t>
+          <t>FACT_MESSAGE_DISPATCH.SEND_STATUS</t>
         </is>
       </c>
       <c r="H223" s="4" t="inlineStr"/>
       <c r="I223" s="4" t="inlineStr">
         <is>
-          <t>필드인벤토리</t>
+          <t>필드인벤토리~</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-07 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-16 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-07</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-16</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,982,027/4,757,065 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,982,027/4,757,065 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,982,027/4,757,065 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,879,345/42,272,226 (4.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,884,683/42,791,677 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,879,345/42,272,226 (4.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,884,683/42,791,677 (4.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 252,475/279,202 (90.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 248,133/272,032 (91.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 252,475/279,202 (90.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 248,133/272,032 (91.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 252,475/279,202 (90.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 248,133/272,032 (91.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 195,942/279,202 (70.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 190,712/272,032 (70.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 52,336/279,202 (18.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 50,927/272,032 (18.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,846행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 218,127/279,202 (78.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 213,528/272,032 (78.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 195,942/279,202 (70.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 190,712/272,032 (70.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,607/279,202 (8.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,850/272,032 (8.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,072,829/4,757,065 (22.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_CAMPAIGN_MONTHLY.STOP_CNT` 비영 314,107/2,166,584 (14.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,454,270/42,272,226 (8.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 비영 116,591/42,272,226 (0.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 비영 117,239/42,791,677 (0.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,879,345/42,272,226 (4.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,884,683/42,791,677 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3795,7 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 37,524,187/42,272,226 (88.8%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 37,993,241/42,791,677 (88.8%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 39,872,779/42,272,226 (94.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 40,386,853/42,791,677 (94.4%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4189,7 @@
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4256,7 +4256,7 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,072,829/4,757,065 (22.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,076,058/4,771,165 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,072,829/4,757,065 (22.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,076,058/4,771,165 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,072,829/4,757,065 (22.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,076,058/4,771,165 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4843,7 +4843,7 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 37,509,013/42,272,226 (88.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 37,557,143/42,791,677 (87.8%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 39,331,147/42,272,226 (93.0%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 39,845,615/42,791,677 (93.1%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,454,270/42,272,226 (8.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,454,270/42,272,226 (8.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,454,270/42,272,226 (8.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,454,270/42,272,226 (8.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,885행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,904행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 43,440,831/43,440,831 (100.0%)</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 44,406,102/44,406,102 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 25,826,805/43,440,831 (59.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 26,019,188/44,406,102 (58.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 2,055,449/43,440,831 (4.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 2,064,917/44,406,102 (4.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 1,536,507/1,536,507 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 1,591,255/1,591,255 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 40,811행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 46,255행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7040,7 +7040,7 @@
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 40,811행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 46,255행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 40,811행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 46,255행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 481행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 440행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 481행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 440행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 304,845/1,536,507 (19.8%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 323,161/1,591,255 (20.3%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 481행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 440행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7662,7 @@
       </c>
       <c r="M114" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,796,799행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,801,193행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7725,7 @@
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,796,799행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,801,193행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,796,799행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,801,193행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8296,7 +8296,7 @@
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9028,7 @@
       </c>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,796,798행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9885,7 +9885,7 @@
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,164행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,982,027/4,757,065 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,982,027/4,757,065 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_CAMPAIGN_MONTHLY.DEV_CNT` 비영 118,918/2,166,584 (5.5%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="M154" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 비영 1,853,923/42,272,226 (4.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 비영 1,859,125/42,791,677 (4.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="M155" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 비영 1,853,923/42,272,226 (4.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 비영 1,859,125/42,791,677 (4.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -10452,7 +10452,7 @@
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 40,606,430/42,272,226 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 41,122,461/42,791,677 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -10641,7 +10641,7 @@
       </c>
       <c r="M163" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 비영 41,096,945/42,272,226 (97.2%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 비영 41,615,513/42,791,677 (97.3%)</t>
         </is>
       </c>
     </row>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="M166" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,885행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,904행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
     </row>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="M170" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,982,027/4,757,065 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11511,7 @@
       </c>
       <c r="M177" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11578,7 +11578,7 @@
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="M179" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 40,606,421/42,272,226 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="M181" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="M182" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11913,7 +11913,7 @@
       </c>
       <c r="M183" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -11980,7 +11980,7 @@
       </c>
       <c r="M184" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12047,7 +12047,7 @@
       </c>
       <c r="M185" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,002,567/42,272,226 (2.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="M186" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,238,774/42,272,226 (2.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,242,457/42,791,677 (2.9%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="M187" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,238,774/42,272,226 (2.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,242,457/42,791,677 (2.9%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12248,7 +12248,7 @@
       </c>
       <c r="M188" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12315,7 +12315,7 @@
       </c>
       <c r="M189" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12382,7 +12382,7 @@
       </c>
       <c r="M190" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M191" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12516,7 +12516,7 @@
       </c>
       <c r="M192" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,169,183/42,272,226 (90.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12784,7 +12784,7 @@
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 43,440,831/43,440,831 (100.0%)</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 44,406,102/44,406,102 (100.0%)</t>
         </is>
       </c>
     </row>
@@ -12851,7 +12851,7 @@
       </c>
       <c r="M197" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 25,826,805/43,440,831 (59.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 26,019,188/44,406,102 (58.6%) · 채움률 95% 미만</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12977,7 @@
       </c>
       <c r="M199" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,982,027/4,757,065 (41.7%) · GA↔CRM identity 커버리지 종속</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,987,631/4,771,165 (41.7%) · GA↔CRM identity 커버리지 종속</t>
         </is>
       </c>
     </row>
@@ -14205,7 +14205,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-07</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-16</t>
         </is>
       </c>
     </row>
@@ -17327,7 +17327,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-07</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-16</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -560,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M219"/>
+  <dimension ref="A1:O219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -576,6 +576,8 @@
     <col width="46" customWidth="1" min="11" max="11"/>
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -651,6 +653,16 @@
           <t>상태_근거</t>
         </is>
       </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>SV_배선</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Agent_배선</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -718,6 +730,16 @@
           <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>SV_DEV_ACHIEVEMENT.ACHIEVEMENT_RATE</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -785,6 +807,16 @@
           <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>SV_DEV_ACHIEVEMENT.CAL_MONTH</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -852,6 +884,16 @@
           <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>SV_DEV_ACHIEVEMENT.CAL_YEAR</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -919,6 +961,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,884,683/42,791,677 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.TOTAL_CRM_DEV_CNT · SV_MEMBER_EVENT.TOTAL_DEV_CNT</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -986,6 +1038,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,884,683/42,791,677 (4.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.GA_DEV_CNT</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1053,6 +1115,16 @@
           <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 248,133/272,032 (91.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.TOTAL_AD_COST</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1120,6 +1192,16 @@
           <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 248,133/272,032 (91.2%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.DEV_UNIT_PRICE</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1187,6 +1269,16 @@
           <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 248,133/272,032 (91.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.DEV_UNIT_PRICE · SV_AD.GA_DEV_CNT · SV_AD.GA_DEV_UNIT_PRICE · SV_AD.REBRDC_DEV_UNIT_PRICE</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1254,6 +1346,16 @@
           <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 190,712/272,032 (70.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.CTR</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1321,6 +1423,16 @@
           <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 50,927/272,032 (18.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.CVR</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1384,6 +1496,8 @@
           <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N15" s="4" t="inlineStr"/>
+      <c r="O15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1451,6 +1565,16 @@
           <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.CHANNEL_COMPANY · SV_AD.MEDIA_CHANNEL_NM</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1514,6 +1638,8 @@
           <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1577,6 +1703,16 @@
           <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.DEVICE_TYPE</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1644,6 +1780,16 @@
           <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.DMST_OVSEA_DIV_NM · SV_AD.DOMESTIC_OVERSEAS</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1711,6 +1857,16 @@
           <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.BIZ_CASE_TYPE · SV_AD.BSNS_CASE_DIV_NM</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1778,6 +1934,16 @@
           <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.CMPGN_TYPE_BSN_NM · SV_MEMBER_MONTHLY.BIZ_CASE_TYPE · SV_MEMBER_MONTHLY.DOMESTIC_OVERSEAS</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1841,6 +2007,16 @@
           <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_NAME · SV_MEMBER_EVENT.CAMPAIGN_NAME · SV_MEMBER_MONTHLY.CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1904,6 +2080,16 @@
           <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.CAMPAIGN_OPEN_DATE</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1967,6 +2153,16 @@
           <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.CREATIVE_NM</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2030,6 +2226,16 @@
           <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.CM_POSITION</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2093,6 +2299,16 @@
           <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.DURATION_SEC</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2156,6 +2372,16 @@
           <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 213,528/272,032 (78.5%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.TOTAL_IMPRESSIONS</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2219,6 +2445,16 @@
           <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 190,712/272,032 (70.1%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.TOTAL_CLICKS</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2280,6 +2516,16 @@
       <c r="M29" s="4" t="inlineStr">
         <is>
           <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,850/272,032 (8.4%) · 채움률 95% 미만</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.TOTAL_INBOUND_CALL</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
         </is>
       </c>
     </row>
@@ -2337,6 +2583,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.STOP_DATE</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2392,6 +2648,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_COHORT.ACQ_DATE · SV_MEMBER_EVENT.JOIN_DATE</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2455,6 +2721,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.FIRST_JOIN_DATE</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2522,6 +2798,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.FIRST_CAMPAIGN · SV_MEMBER_MONTHLY.FIRST_CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2589,6 +2875,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.STOP_DATE</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2654,6 +2950,16 @@
       <c r="M35" s="4" t="inlineStr">
         <is>
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.LAST_CAMPAIGN · SV_MEMBER_MONTHLY.LAST_CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -2711,6 +3017,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.NEW_EXISTING_FLAG · SV_MEMBER_MONTHLY.NEW_EXISTING_FLAG</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -2766,6 +3082,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.INCREASE_FLAG</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -2821,6 +3147,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.REDONATE_FLAG</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -2885,7 +3221,17 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_CAMPAIGN_MONTHLY.STOP_CNT` 비영 314,107/2,166,584 (14.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_CAMPAIGN_MONTHLY.STOP_CNT` 비영 206,009/1,686,945 (12.2%) · 채움률 95% 미만</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.STOP_AMT_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -2955,6 +3301,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.UNPAID_CNT_SUM · SV_PAYMENT_BILLING_STATUS.UNPAID_CNT_EQ</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -3022,6 +3378,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.ACTIVE_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -3089,6 +3455,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 비영 117,239/42,791,677 (0.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.DECREASE_EVENT_AMT · SV_MEMBER_MONTHLY.DECREASE_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -3152,6 +3528,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.DEV_MEMBER_COUNT</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -3215,6 +3601,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.ACTIVE_MEMBERS_SUM</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -3278,6 +3674,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.STOP_MEMBER_COUNT</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -3341,6 +3747,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.UNPAID_MEMBERS_EOM</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -3404,6 +3820,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.NEW_EXISTING_FLAG</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -3467,6 +3893,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.NEW_EXISTING_FLAG</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -3534,6 +3970,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY_KPI.ACTIVE_RATE</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -3601,6 +4047,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,884,683/42,791,677 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY_KPI.ACTIVE_RATE_NEW</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -3668,6 +4124,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY_KPI.ACTIVE_RATE_EXISTING</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -3731,6 +4197,8 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N52" s="4" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -3798,6 +4266,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 37,993,241/42,791,677 (88.8%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_CUM_STOP.YEAR_START_ACTIVE · SV_CAMPAIGN_MONTHLY.YEAR_START_ACTIVE_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -3861,6 +4339,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.ACTIVE_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -3928,6 +4416,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.ACTIVE_MEMBERS_SUM</t>
+        </is>
+      </c>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -3995,6 +4493,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.ACTIVE_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -4058,6 +4566,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 40,386,853/42,791,677 (94.4%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.ACTIVE_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -4125,6 +4643,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.STOP_RATE_1</t>
+        </is>
+      </c>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -4192,6 +4720,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.STOP_RATE_2</t>
+        </is>
+      </c>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -4259,6 +4797,16 @@
           <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,076,058/4,771,165 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.NEW_EXISTING_FLAG · SV_MEMBER_MONTHLY.STOP_RATE_NEW</t>
+        </is>
+      </c>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -4326,6 +4874,16 @@
           <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,076,058/4,771,165 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.NEW_EXISTING_FLAG · SV_MEMBER_MONTHLY.STOP_RATE_EXISTING</t>
+        </is>
+      </c>
+      <c r="O61" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -4391,6 +4949,16 @@
       <c r="M62" s="4" t="inlineStr">
         <is>
           <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,076,058/4,771,165 (22.6%) · 채움률 95% 미만</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.TOTAL_STOP_CNT</t>
+        </is>
+      </c>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -4452,6 +5020,8 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N63" s="4" t="inlineStr"/>
+      <c r="O63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -4511,6 +5081,8 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N64" s="4" t="inlineStr"/>
+      <c r="O64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -4578,6 +5150,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.CNT_PER_ACTIVE_MEMBER</t>
+        </is>
+      </c>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -4645,6 +5227,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.PAY_IN_RATE</t>
+        </is>
+      </c>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -4712,6 +5304,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.PAY_IN_RATE</t>
+        </is>
+      </c>
+      <c r="O67" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -4779,6 +5381,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_PAY_IN_RATE · SV_MEMBER_FEE.PAYMENT_RATE_FEE · SV_MEMBER_MONTHLY.PAYMENT_RATE_FEE · SV_MEMBER_MONTHLY.PAY_IN_RATE</t>
+        </is>
+      </c>
+      <c r="O68" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -4846,6 +5458,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.PAYMENT_RATE_FEE</t>
+        </is>
+      </c>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -4909,6 +5531,8 @@
           <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 37,557,143/42,791,677 (87.8%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N70" s="4" t="inlineStr"/>
+      <c r="O70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -4976,6 +5600,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.REGULAR_ONETIME_FEE_SUM</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -5043,6 +5677,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.ONETIME_ONETIME_FEE_SUM</t>
+        </is>
+      </c>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -5106,6 +5750,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_FEE.TOTAL_PAID_FEE_BILLABLE · SV_MEMBER_MONTHLY.TOTAL_PAID_FEE_BILLABLE</t>
+        </is>
+      </c>
+      <c r="O73" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -5169,6 +5823,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_FEE.DISTINCT_PAYING_MEMBERS · SV_MEMBER_FEE.TOTAL_PAID_FEE_BILLABLE</t>
+        </is>
+      </c>
+      <c r="O74" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -5230,6 +5894,16 @@
       <c r="M75" s="4" t="inlineStr">
         <is>
           <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 39,845,615/42,791,677 (93.1%) · 채움률 95% 미만</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_FEE.TOTAL_BILLED_AMT · SV_MEMBER_MONTHLY.TOTAL_BILLED_AMT</t>
+        </is>
+      </c>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -5291,6 +5965,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.AMOUNT_BAND1</t>
+        </is>
+      </c>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -5350,6 +6034,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.AMOUNT_BAND2</t>
+        </is>
+      </c>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -5409,6 +6103,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.PERIOD_BAND1</t>
+        </is>
+      </c>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -5468,6 +6172,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.PERIOD_BAND2</t>
+        </is>
+      </c>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -5535,6 +6249,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_UNPAID_RATE · SV_MEMBER_MONTHLY.UNPAID_RATE_CNT</t>
+        </is>
+      </c>
+      <c r="O80" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -5602,6 +6326,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.UNPAID_RATE_NEW</t>
+        </is>
+      </c>
+      <c r="O81" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -5669,6 +6403,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.UNPAID_RATE_EXISTING</t>
+        </is>
+      </c>
+      <c r="O82" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -5734,6 +6478,16 @@
       <c r="M83" s="4" t="inlineStr">
         <is>
           <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SPONSOR_BIZ.SPONSORSHIP_UNPAID_RATE</t>
+        </is>
+      </c>
+      <c r="O83" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -5795,6 +6549,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.UNPAID_MEMBERS_EOM</t>
+        </is>
+      </c>
+      <c r="O84" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -5854,6 +6618,16 @@
           <t>추정: GA↔CRM identity 브리지 의존 — 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_CHILD_UNPAID.UNPAID_SVC_CONV_RATE_A · SV_GA_CHILD_UNPAID.UNPAID_SVC_CONV_RATE_A_D5 · SV_GA_CHILD_UNPAID.UNPAID_SVC_CONV_RATE_B · SV_GA_CHILD_UNPAID.UNPAID_SVC_CONV_RATE_B_D5</t>
+        </is>
+      </c>
+      <c r="O85" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -5921,6 +6695,16 @@
           <t>추정: 배속 차원 `DIM_REASON` 5,904행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.UNPAID_REASON</t>
+        </is>
+      </c>
+      <c r="O86" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -5988,6 +6772,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>SV_PAYMENT_BILLING_STATUS.UNPAID_CNT_EQ</t>
+        </is>
+      </c>
+      <c r="O87" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -6055,6 +6849,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.STATUS_UNPAID_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O88" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -6122,6 +6926,16 @@
           <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 44,406,102/44,406,102 (100.0%)</t>
         </is>
       </c>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.TOTAL_SEND_MEMBERS</t>
+        </is>
+      </c>
+      <c r="O89" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -6189,6 +7003,16 @@
           <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 26,019,188/44,406,102 (58.6%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.SEND_STATUS_NAME</t>
+        </is>
+      </c>
+      <c r="O90" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -6256,6 +7080,16 @@
           <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 2,064,917/44,406,102 (4.7%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.SEND_STATUS_NAME</t>
+        </is>
+      </c>
+      <c r="O91" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -6323,6 +7157,16 @@
           <t>실측: `FACT_MESSAGE_DISPATCH.LETTER_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_LETTER_MEMBERS</t>
+        </is>
+      </c>
+      <c r="O92" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -6386,6 +7230,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_LETTER_CNT</t>
+        </is>
+      </c>
+      <c r="O93" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -6453,6 +7307,16 @@
           <t>실측: `FACT_MESSAGE_DISPATCH.GIFT_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_GIFT_MEMBERS</t>
+        </is>
+      </c>
+      <c r="O94" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -6514,6 +7378,16 @@
       <c r="M95" s="4" t="inlineStr">
         <is>
           <t>실측: `FACT_MESSAGE_DISPATCH.GIFT_PART_AMT` 전건 0 — 설계O·값 미주입</t>
+        </is>
+      </c>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>SV_RELATION_ACTIVITY.TOTAL_GIFT_AMT · SV_SERVICE.D5_GIFT_AMT</t>
+        </is>
+      </c>
+      <c r="O95" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -6571,6 +7445,16 @@
           <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_SESSION.SESSION_CNT</t>
+        </is>
+      </c>
+      <c r="O96" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -6626,6 +7510,8 @@
           <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N97" s="4" t="inlineStr"/>
+      <c r="O97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -6681,6 +7567,16 @@
           <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_SESSION.USER_CNT</t>
+        </is>
+      </c>
+      <c r="O98" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -6736,6 +7632,16 @@
           <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_BEHAVIOR.TOTAL_EVENT_CNT · SV_GA_SESSION.EVENT_SUM</t>
+        </is>
+      </c>
+      <c r="O99" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -6791,6 +7697,16 @@
           <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_BEHAVIOR.TOTAL_PAGE_VIEWS · SV_GA_SESSION.PAGE_VIEW_SUM</t>
+        </is>
+      </c>
+      <c r="O100" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -6852,6 +7768,16 @@
       <c r="M101" s="4" t="inlineStr">
         <is>
           <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 1,591,255/1,591,255 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+        </is>
+      </c>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_SESSION.SESSION_CNT</t>
+        </is>
+      </c>
+      <c r="O101" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
         </is>
       </c>
     </row>
@@ -6909,6 +7835,16 @@
           <t>실측: `FACT_BIGQUERY_BEHAVIOR.AVG_SESSION_DURATION` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_SESSION.AVG_SESSION_DURATION_SEC · SV_GA_SESSION.AVG_SESSION_ENGAGEMENT_SEC</t>
+        </is>
+      </c>
+      <c r="O102" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -6976,6 +7912,16 @@
           <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 46,255행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_BEHAVIOR.EVENT_CATEGORY</t>
+        </is>
+      </c>
+      <c r="O103" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -7043,6 +7989,16 @@
           <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 46,255행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_BEHAVIOR.EVENT_LABEL</t>
+        </is>
+      </c>
+      <c r="O104" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -7110,6 +8066,16 @@
           <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 46,255행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_BEHAVIOR.EVENT_ACTION</t>
+        </is>
+      </c>
+      <c r="O105" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -7177,6 +8143,16 @@
           <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_BEHAVIOR.UTM_CAMPAIGN · SV_GA_SESSION.STSLC_GAC_CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="O106" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -7244,6 +8220,16 @@
           <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 440행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N107" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_BEHAVIOR.UTM_CONTENT</t>
+        </is>
+      </c>
+      <c r="O107" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -7305,6 +8291,16 @@
       <c r="M108" s="4" t="inlineStr">
         <is>
           <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 440행 실재 — 대응 물리 컬럼 미특정</t>
+        </is>
+      </c>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_BEHAVIOR.UTM_TERM</t>
+        </is>
+      </c>
+      <c r="O108" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
         </is>
       </c>
     </row>
@@ -7362,6 +8358,16 @@
           <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_BEHAVIOR.PAGE_PATH</t>
+        </is>
+      </c>
+      <c r="O109" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -7421,6 +8427,16 @@
           <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_BEHAVIOR.PAGE_PATH</t>
+        </is>
+      </c>
+      <c r="O110" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -7484,6 +8500,8 @@
           <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 323,161/1,591,255 (20.3%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
+      <c r="N111" s="4" t="inlineStr"/>
+      <c r="O111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -7539,6 +8557,16 @@
           <t>실측: `FACT_BIGQUERY_BEHAVIOR.BOUNCE_RATE` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
+      <c r="N112" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_SESSION.BOUNCE_RATE</t>
+        </is>
+      </c>
+      <c r="O112" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -7602,6 +8630,16 @@
           <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 440행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_BEHAVIOR.SOURCE_MEDIUM</t>
+        </is>
+      </c>
+      <c r="O113" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -7665,6 +8703,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,801,193행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SPONSOR_BIZ.MEMBER_DK</t>
+        </is>
+      </c>
+      <c r="O114" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -7728,6 +8776,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,801,193행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_CHILD_UNPAID.CHILD_PAGE_MEMBERS</t>
+        </is>
+      </c>
+      <c r="O115" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -7791,6 +8849,8 @@
           <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,801,193행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N116" s="4" t="inlineStr"/>
+      <c r="O116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -7858,6 +8918,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.NEW_EXISTING_FLAG · SV_MEMBER_MONTHLY.NEW_EXISTING_FLAG · SV_MEMBER_MONTHLY_KPI.NEW_EXISTING_FLAG</t>
+        </is>
+      </c>
+      <c r="O117" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -7921,6 +8991,16 @@
           <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>SV_DVLP_GOAL_ACMSLT.CPR_NM · SV_MEMBER_EVENT.SPONSORSHIP_CPR_DIV_NM · SV_MEMBER_FEE.ACQ_CPR_DIV · SV_TARGET_BIZ.CORP_DIV</t>
+        </is>
+      </c>
+      <c r="O118" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -7984,6 +9064,16 @@
           <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>SV_DVLP_GOAL_ACMSLT.HDQ_BRNCH_GRP_NM · SV_MEMBER_EVENT.ORG_DIV · SV_TARGET_BIZ.ORG_DIV</t>
+        </is>
+      </c>
+      <c r="O119" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -8047,6 +9137,16 @@
           <t>추정: 배속 차원 `DIM_ORG` 1,315행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>SV_DEV_ACHIEVEMENT.ORG_DEPARTMENT · SV_DVLP_GOAL_ACMSLT.DEPT_DIV_NM · SV_MEMBER_EVENT.ORG_DEPARTMENT · SV_MEMBER_EVENT.ORG_PATH · SV_TARGET_BIZ.TEAM_NAME</t>
+        </is>
+      </c>
+      <c r="O120" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -8110,6 +9210,16 @@
           <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CMMN_BRND_NM · SV_MEMBER_EVENT.CMMN_BRND_NM · SV_MEMBER_FEE.ACQ_CMMN_BRAND</t>
+        </is>
+      </c>
+      <c r="O121" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -8173,6 +9283,16 @@
           <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_COHORT.PROMO_METHOD_NAME · SV_MEMBER_EVENT.PROMO_METHOD_NAME · SV_MEMBER_FEE.ACQ_PROMO_METHOD</t>
+        </is>
+      </c>
+      <c r="O122" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -8236,6 +9356,16 @@
           <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.PARENT_CAMPAIGN_NAME · SV_MEMBER_EVENT.PARENT_CAMPAIGN_NAME · SV_MEMBER_MONTHLY.PARENT_CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="O123" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -8297,6 +9427,16 @@
       <c r="M124" s="4" t="inlineStr">
         <is>
           <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+        </is>
+      </c>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_NAME · SV_MEMBER_EVENT.CAMPAIGN_NAME · SV_MEMBER_MONTHLY.CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -8354,6 +9494,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N125" s="4" t="inlineStr">
+        <is>
+          <t>SV_DEV_ACHIEVEMENT.DEV_TYPE · SV_DEV_ACHIEVEMENT.TOTAL_ACTUAL_CNT · SV_MEMBER_MONTHLY.DEV_TYPE</t>
+        </is>
+      </c>
+      <c r="O125" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -8421,6 +9571,16 @@
           <t>추정: GA↔CRM identity 브리지 의존 — 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_CHILD_UNPAID.CHILD_CODE · SV_GA_CHILD_UNPAID.CHILD_CODE_CNT_A · SV_GA_CHILD_UNPAID.CHILD_CODE_CNT_B</t>
+        </is>
+      </c>
+      <c r="O126" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -8484,6 +9644,16 @@
           <t>추정: 배속 차원 `DIM_SPONSORSHIP` 51행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.SPONSORSHIP · SV_MEMBER_FEE.SPONSORSHIP · SV_MEMBER_SPONSOR_BIZ.SPONSORSHIP</t>
+        </is>
+      </c>
+      <c r="O127" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -8551,6 +9721,16 @@
           <t>추정: 배속 차원 `DIM_SPONSORSHIP` 51행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SPONSOR_BIZ.SPONSORSHIP_ABBR_CATEGORY</t>
+        </is>
+      </c>
+      <c r="O128" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -8614,6 +9794,16 @@
           <t>추정: 배속 차원 `DIM_PAYMENT` 7행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.SETTLE_METHOD · SV_MEMBER_FEE.PAYMENT_METHOD</t>
+        </is>
+      </c>
+      <c r="O129" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -8675,6 +9865,16 @@
       <c r="M130" s="4" t="inlineStr">
         <is>
           <t>추정: 배속 차원 `DIM_PAYMENT` 7행 실재 — 대응 물리 컬럼 미특정</t>
+        </is>
+      </c>
+      <c r="N130" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.SETTLE_METHOD</t>
+        </is>
+      </c>
+      <c r="O130" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -8732,6 +9932,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N131" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.AVG_SPONSOR_MONTHS</t>
+        </is>
+      </c>
+      <c r="O131" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -8787,6 +9997,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N132" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.PERIOD_BAND2</t>
+        </is>
+      </c>
+      <c r="O132" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -8842,6 +10062,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N133" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.AVG_PAID_MONTHS</t>
+        </is>
+      </c>
+      <c r="O133" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -8905,6 +10135,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N134" s="4" t="inlineStr">
+        <is>
+          <t>SV_EVENT_PARTICIPATION.GENDER_NAME · SV_MEMBER_EVENT.GENDER_NAME · SV_MEMBER_MONTHLY.GENDER_NAME · SV_RELATION_ACTIVITY.GENDER_NAME · SV_SERVICE.GENDER_NAME</t>
+        </is>
+      </c>
+      <c r="O134" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -8968,6 +10208,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N135" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_COHORT.ACQ_REGION · SV_MEMBER_EVENT.REGION_AT_EVENT · SV_MEMBER_MONTHLY.REGION</t>
+        </is>
+      </c>
+      <c r="O135" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -9031,6 +10281,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N136" s="4" t="inlineStr">
+        <is>
+          <t>SV_EVENT_PARTICIPATION.MEMBER_STATUS_NAME · SV_MEMBER_EVENT.MEMBER_STATUS_NAME · SV_MEMBER_MONTHLY.MEMBER_STATUS_NAME · SV_SERVICE.MEMBER_STATUS_NAME</t>
+        </is>
+      </c>
+      <c r="O136" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -9094,6 +10354,16 @@
           <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N137" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.REQ_SEND_GBN_TOP_NM</t>
+        </is>
+      </c>
+      <c r="O137" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -9157,6 +10427,16 @@
           <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.REQ_SEND_GBN_MID_NM</t>
+        </is>
+      </c>
+      <c r="O138" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -9218,6 +10498,16 @@
       <c r="M139" s="4" t="inlineStr">
         <is>
           <t>추정: 배속 차원 `DIM_SERVICE` 11행 실재 — 대응 물리 컬럼 미특정</t>
+        </is>
+      </c>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.REQ_SEND_GBN_BOT_NM</t>
+        </is>
+      </c>
+      <c r="O139" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -9275,6 +10565,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N140" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.SEND_TITLE</t>
+        </is>
+      </c>
+      <c r="O140" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -9330,6 +10630,16 @@
           <t>추정: 배속 차원 `DIM_DATE` 73,415행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N141" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.SEND_DATE</t>
+        </is>
+      </c>
+      <c r="O141" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -9385,6 +10695,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N142" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.SEND_STATUS_NAME</t>
+        </is>
+      </c>
+      <c r="O142" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -9440,6 +10760,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N143" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_LETTER_MEMBERS</t>
+        </is>
+      </c>
+      <c r="O143" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -9495,6 +10825,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_LETTER_CNT</t>
+        </is>
+      </c>
+      <c r="O144" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -9550,6 +10890,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N145" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_GIFT_MEMBERS</t>
+        </is>
+      </c>
+      <c r="O145" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -9605,6 +10955,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N146" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_GIFT_CNT</t>
+        </is>
+      </c>
+      <c r="O146" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -9660,6 +11020,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N147" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_INCREASE_MEMBERS</t>
+        </is>
+      </c>
+      <c r="O147" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -9715,6 +11085,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N148" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_INCREASE_CNT</t>
+        </is>
+      </c>
+      <c r="O148" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -9770,6 +11150,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N149" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_STOP_MEMBERS_SUM</t>
+        </is>
+      </c>
+      <c r="O149" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -9825,6 +11215,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N150" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_STOP_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O150" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -9888,6 +11288,8 @@
           <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N151" s="4" t="inlineStr"/>
+      <c r="O151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -9951,6 +11353,16 @@
           <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N152" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.DEV_MEMBER_COUNT</t>
+        </is>
+      </c>
+      <c r="O152" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -10011,7 +11423,17 @@
       </c>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_CAMPAIGN_MONTHLY.DEV_CNT` 비영 118,918/2,166,584 (5.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_CAMPAIGN_MONTHLY.DEV_CNT` 비영 76,210/1,686,945 (4.5%) · 채움률 95% 미만</t>
+        </is>
+      </c>
+      <c r="N153" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.TOTAL_DEV_CNT · SV_MEMBER_MONTHLY.TOTAL_DEV_CNT</t>
+        </is>
+      </c>
+      <c r="O153" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -10077,6 +11499,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 비영 1,859,125/42,791,677 (4.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N154" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.INCREASE_EVENT_AMT · SV_MEMBER_MONTHLY.INCREASE_MEMBERS_SUM</t>
+        </is>
+      </c>
+      <c r="O154" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -10140,6 +11572,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 비영 1,859,125/42,791,677 (4.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N155" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.INCREASE_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O155" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -10203,6 +11645,16 @@
           <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
         </is>
       </c>
+      <c r="N156" s="4" t="inlineStr">
+        <is>
+          <t>SV_TARGET_BIZ.GOAL_CNT</t>
+        </is>
+      </c>
+      <c r="O156" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -10266,6 +11718,8 @@
           <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
         </is>
       </c>
+      <c r="N157" s="4" t="inlineStr"/>
+      <c r="O157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -10329,6 +11783,16 @@
           <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
         </is>
       </c>
+      <c r="N158" s="4" t="inlineStr">
+        <is>
+          <t>SV_TARGET_BIZ.GOAL_CNT</t>
+        </is>
+      </c>
+      <c r="O158" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -10392,6 +11856,8 @@
           <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
         </is>
       </c>
+      <c r="N159" s="4" t="inlineStr"/>
+      <c r="O159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -10455,6 +11921,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 41,122,461/42,791,677 (96.1%)</t>
         </is>
       </c>
+      <c r="N160" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.ACTIVE_MEMBERS_SUM</t>
+        </is>
+      </c>
+      <c r="O160" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -10518,6 +11994,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
+      <c r="N161" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.ACTIVE_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O161" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -10581,6 +12067,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N162" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.ACTIVE_CUM_MEMBERS_SUM</t>
+        </is>
+      </c>
+      <c r="O162" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -10644,6 +12140,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 비영 41,615,513/42,791,677 (97.3%)</t>
         </is>
       </c>
+      <c r="N163" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.ACTIVE_CUM_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O163" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -10707,6 +12213,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N164" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.SERVICE_MEMBERS_SUM</t>
+        </is>
+      </c>
+      <c r="O164" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -10770,6 +12286,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N165" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.SERVICE_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O165" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -10833,6 +12359,16 @@
           <t>추정: 배속 차원 `DIM_REASON` 5,904행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N166" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.STOP_REASON_NM</t>
+        </is>
+      </c>
+      <c r="O166" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -10898,6 +12434,16 @@
       <c r="M167" s="4" t="inlineStr">
         <is>
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+        </is>
+      </c>
+      <c r="N167" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_FEE.ACQ_CAMPAIGN · SV_MEMBER_FEE.TOTAL_PAID_FEE_BILLABLE</t>
+        </is>
+      </c>
+      <c r="O167" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -10959,6 +12505,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N168" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_EVENT.DVLP_DIV_CD</t>
+        </is>
+      </c>
+      <c r="O168" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -11018,6 +12574,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N169" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_COHORT.EXP_TENURE_MONTHS</t>
+        </is>
+      </c>
+      <c r="O169" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -11083,6 +12649,16 @@
       <c r="M170" s="4" t="inlineStr">
         <is>
           <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
+        </is>
+      </c>
+      <c r="N170" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_COHORT.EXP_TENURE_MONTHS</t>
+        </is>
+      </c>
+      <c r="O170" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -11144,6 +12720,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N171" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_COHORT.EXP_TENURE_MONTHS</t>
+        </is>
+      </c>
+      <c r="O171" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -11203,6 +12789,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N172" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_COHORT.CHURN_RATE_12M · SV_MEMBER_COHORT.SURVIVAL_RATE</t>
+        </is>
+      </c>
+      <c r="O172" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -11262,6 +12858,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N173" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_COHORT.SURVIVAL_RATE</t>
+        </is>
+      </c>
+      <c r="O173" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
@@ -11321,6 +12927,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N174" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_COHORT.EXP_TENURE_MONTHS · SV_MEMBER_FEE.DISTINCT_PAYING_MEMBERS</t>
+        </is>
+      </c>
+      <c r="O174" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -11380,6 +12996,16 @@
           <t>추정: AGENCY 원천 계통(소재 연결키 Q10) — 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N175" s="4" t="inlineStr">
+        <is>
+          <t>SV_BUDGET.DIRECT_FUNDRAISING_COST_1 · SV_BUDGET.DIRECT_FUNDRAISING_COST_2 · SV_BUDGET.DVLP_INBOUND_PATH</t>
+        </is>
+      </c>
+      <c r="O175" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
@@ -11447,6 +13073,16 @@
           <t>실측: `FACT_BUDGET.FUNDRAISING_COST` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
+      <c r="N176" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.MARKETING_CAMPAIGN · SV_AD.TOTAL_AD_COST</t>
+        </is>
+      </c>
+      <c r="O176" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -11514,6 +13150,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N177" s="4" t="inlineStr">
+        <is>
+          <t>SV_BUDGET.DIRECT_FUNDRAISING_COST_1</t>
+        </is>
+      </c>
+      <c r="O177" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -11581,6 +13227,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
+      <c r="N178" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_ACTIVE_RATE</t>
+        </is>
+      </c>
+      <c r="O178" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -11648,6 +13304,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
+      <c r="N179" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_ACTIVE_RATE</t>
+        </is>
+      </c>
+      <c r="O179" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -11715,6 +13381,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
         </is>
       </c>
+      <c r="N180" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_ACTIVE_RATE</t>
+        </is>
+      </c>
+      <c r="O180" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -11782,6 +13458,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N181" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_STOP_RATE</t>
+        </is>
+      </c>
+      <c r="O181" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -11849,6 +13535,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N182" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_STOP_RATE_PREV</t>
+        </is>
+      </c>
+      <c r="O182" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -11916,6 +13612,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N183" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_CUM_STOP.CUM_STOP_RATE</t>
+        </is>
+      </c>
+      <c r="O183" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -11983,6 +13689,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N184" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_CUM_STOP.CUM_STOP_RATE_DEV</t>
+        </is>
+      </c>
+      <c r="O184" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -12050,6 +13766,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N185" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_STOP_RATE</t>
+        </is>
+      </c>
+      <c r="O185" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -12117,6 +13843,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,242,457/42,791,677 (2.9%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N186" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CHURN_CNT_SUM · SV_MEMBER_MONTHLY.CHURN_CNT_SUM</t>
+        </is>
+      </c>
+      <c r="O186" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -12184,6 +13920,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,242,457/42,791,677 (2.9%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N187" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_CHURN_RATE</t>
+        </is>
+      </c>
+      <c r="O187" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -12251,6 +13997,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N188" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_PAY_IN_RATE</t>
+        </is>
+      </c>
+      <c r="O188" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -12318,6 +14074,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N189" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_PAY_IN_RATE</t>
+        </is>
+      </c>
+      <c r="O189" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -12385,6 +14151,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N190" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_CUM_PAY_IN_RATE</t>
+        </is>
+      </c>
+      <c r="O190" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -12452,6 +14228,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N191" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_CUM_PAY_IN_RATE</t>
+        </is>
+      </c>
+      <c r="O191" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -12519,6 +14305,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
         </is>
       </c>
+      <c r="N192" s="4" t="inlineStr">
+        <is>
+          <t>SV_PAYMENT_BILLING_STATUS.PAID_FEE_SUM</t>
+        </is>
+      </c>
+      <c r="O192" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -12586,6 +14382,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
+      <c r="N193" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_UNPAID_RATE</t>
+        </is>
+      </c>
+      <c r="O193" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -12653,6 +14459,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
+      <c r="N194" s="4" t="inlineStr">
+        <is>
+          <t>SV_CAMPAIGN_MONTHLY.CAMPAIGN_UNPAID_RATE</t>
+        </is>
+      </c>
+      <c r="O194" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -12720,6 +14536,16 @@
           <t>실측: `FACT_MEMBER_MONTHLY.CAMPAIGN_UNPAID_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
+      <c r="N195" s="4" t="inlineStr">
+        <is>
+          <t>SV_PAYMENT_BILLING_STATUS.UNPAID_AMT_SUM</t>
+        </is>
+      </c>
+      <c r="O195" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
@@ -12787,6 +14613,16 @@
           <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 44,406,102/44,406,102 (100.0%)</t>
         </is>
       </c>
+      <c r="N196" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_STATUS_ASOF.MEMBER_COUNT · SV_SERVICE.DISTINCT_SEND_MEMBERS</t>
+        </is>
+      </c>
+      <c r="O196" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -12852,6 +14688,16 @@
       <c r="M197" s="4" t="inlineStr">
         <is>
           <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 26,019,188/44,406,102 (58.6%) · 채움률 95% 미만</t>
+        </is>
+      </c>
+      <c r="N197" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.SEND_STATUS_NAME</t>
+        </is>
+      </c>
+      <c r="O197" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -12913,6 +14759,16 @@
           <t>추정: GA↔CRM identity 브리지 의존 — 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N198" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.OPEN_RATE_SND</t>
+        </is>
+      </c>
+      <c r="O198" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -12978,6 +14834,16 @@
       <c r="M199" s="4" t="inlineStr">
         <is>
           <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,987,631/4,771,165 (41.7%) · GA↔CRM identity 커버리지 종속</t>
+        </is>
+      </c>
+      <c r="N199" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.CLICK_TO_DEV_RATE_D30 · SV_SERVICE.CLICK_TO_DEV_RATE_D5</t>
+        </is>
+      </c>
+      <c r="O199" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -13039,6 +14905,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N200" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_INCREASE_RATE</t>
+        </is>
+      </c>
+      <c r="O200" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -13098,6 +14974,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N201" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.D5_INCREASE_FLAG</t>
+        </is>
+      </c>
+      <c r="O201" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
@@ -13157,6 +15043,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N202" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.RECEIVED_FLAG</t>
+        </is>
+      </c>
+      <c r="O202" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -13216,6 +15112,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N203" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.D5_INCREASE_FLAG</t>
+        </is>
+      </c>
+      <c r="O203" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -13275,6 +15181,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N204" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.RECEIVED_FLAG</t>
+        </is>
+      </c>
+      <c r="O204" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -13334,6 +15250,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N205" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.D5_INCREASE_FLAG</t>
+        </is>
+      </c>
+      <c r="O205" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -13393,6 +15319,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N206" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.RECEIVED_FLAG</t>
+        </is>
+      </c>
+      <c r="O206" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -13452,6 +15388,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N207" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.D5_INCREASE_FLAG</t>
+        </is>
+      </c>
+      <c r="O207" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
@@ -13511,6 +15457,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N208" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.RECEIVED_FLAG</t>
+        </is>
+      </c>
+      <c r="O208" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -13570,6 +15526,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N209" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.ACQ_CAMPAIGN_NAME</t>
+        </is>
+      </c>
+      <c r="O209" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -13635,6 +15601,16 @@
       <c r="M210" s="4" t="inlineStr">
         <is>
           <t>실측: `FACT_MESSAGE_DISPATCH.LETTER_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+        </is>
+      </c>
+      <c r="N210" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_LETTER_RATE</t>
+        </is>
+      </c>
+      <c r="O210" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -13696,6 +15672,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N211" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.D5_LETTER_FLAG</t>
+        </is>
+      </c>
+      <c r="O211" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
@@ -13755,6 +15741,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N212" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.D5_LETTER_FLAG</t>
+        </is>
+      </c>
+      <c r="O212" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -13814,6 +15810,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N213" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.D5_LETTER_FLAG</t>
+        </is>
+      </c>
+      <c r="O213" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
@@ -13873,6 +15879,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N214" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.D5_LETTER_FLAG</t>
+        </is>
+      </c>
+      <c r="O214" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -13938,6 +15954,16 @@
       <c r="M215" s="4" t="inlineStr">
         <is>
           <t>실측: `FACT_MESSAGE_DISPATCH.GIFT_PART_MEMBERS` 전건 0 — 설계O·값 미주입</t>
+        </is>
+      </c>
+      <c r="N215" s="4" t="inlineStr">
+        <is>
+          <t>SV_SERVICE.D5_GIFT_RATE</t>
+        </is>
+      </c>
+      <c r="O215" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
         </is>
       </c>
     </row>
@@ -13999,6 +16025,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N216" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.D5_GIFT_FLAG</t>
+        </is>
+      </c>
+      <c r="O216" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
@@ -14058,6 +16094,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N217" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.D5_GIFT_FLAG</t>
+        </is>
+      </c>
+      <c r="O217" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
@@ -14117,6 +16163,16 @@
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
+      <c r="N218" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.D5_GIFT_FLAG</t>
+        </is>
+      </c>
+      <c r="O218" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -14174,6 +16230,16 @@
       <c r="M219" s="4" t="inlineStr">
         <is>
           <t>추정: 배속·원천 계통에 알려진 제약 없음 — 대응 물리 컬럼 미특정</t>
+        </is>
+      </c>
+      <c r="N219" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_SERVICE_COHORT.D5_GIFT_FLAG</t>
+        </is>
+      </c>
+      <c r="O219" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MEMBER</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-16 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-18 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-16</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-18</t>
         </is>
       </c>
     </row>
@@ -1638,8 +1638,16 @@
           <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr"/>
-      <c r="O17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>SV_AD.AD_TYPE_NM · SV_AD.CHANNEL_COMPANY_TYPE</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -4197,8 +4205,16 @@
           <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
-      <c r="N52" s="4" t="inlineStr"/>
-      <c r="O52" s="4" t="inlineStr"/>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>SV_MEMBER_MONTHLY.YEAR_START_ACTIVE_MEMBERS</t>
+        </is>
+      </c>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_EXECUTIVE · AGENT_MEMBER</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6551,7 +6567,7 @@
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>SV_MEMBER_MONTHLY.UNPAID_MEMBERS_EOM</t>
+          <t>SV_MEMBER_MONTHLY.YEAR_START_ACTIVE_MEMBERS</t>
         </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
@@ -7356,28 +7372,20 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>FSE.GIFT_PART_AMT</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="inlineStr">
-        <is>
-          <t>CRM_RELATION_ACTIVITY;CRM_SEND_MEMBER;CRM_SEND_REQUEST;CRM_SPONSOR_RELATION</t>
-        </is>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>SND_MEMBER_LIST;SND_MEMBER_OPEN_LOG;SND_REQ_MST;TC_CMMN_DTL_CD;TD_MS_EMAIL_SNDNG_DTLS;TD_MS_MSG_AT_SNDNG_DTLS;TD_MS_PSTMTR_SNDNG_DTL;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MS_EMAIL_SNDNG;TM_MS_MSG_AT_SNDNG;TM_MS_PSTMTR_SNDNG;TM_RM_RELATNSP_GFTMNEY_INFO;TM_RM_RELATNSP_LETTER_INFO;TM_RM_RELATNSP_MSTR_INFO</t>
-        </is>
-      </c>
+          <t>FSE.D5_GIFT_PART_AMT</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr"/>
+      <c r="J95" s="4" t="inlineStr"/>
       <c r="K95" s="4" t="inlineStr"/>
-      <c r="L95" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L95" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.GIFT_PART_AMT` 전건 0 — 설계O·값 미주입</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.D5_GIFT_PART_AMT` 비영 26,544/44,406,102 (0.1%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -7510,8 +7518,16 @@
           <t>추정: GA4 원천 계통(1일 샤드·identity 4%대) — 물리 컬럼 미특정</t>
         </is>
       </c>
-      <c r="N97" s="4" t="inlineStr"/>
-      <c r="O97" s="4" t="inlineStr"/>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_BEHAVIOR.ACTIVE_USERS_ROWSUM</t>
+        </is>
+      </c>
+      <c r="O97" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -8500,8 +8516,16 @@
           <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 323,161/1,591,255 (20.3%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
-      <c r="N111" s="4" t="inlineStr"/>
-      <c r="O111" s="4" t="inlineStr"/>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_BEHAVIOR.AVG_SCROLL_DEPTH</t>
+        </is>
+      </c>
+      <c r="O111" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -16271,7 +16295,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-16</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-18</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19417,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-16</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-18</t>
         </is>
       </c>
     </row>

--- a/30_output_share/05_지표GOLD매핑.xlsx
+++ b/30_output_share/05_지표GOLD매핑.xlsx
@@ -497,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-18 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-27 — 본 파일은 자동 생성물입니다. 직접 수정 금지 — 생성기 scripts/gen_metric_gold_mapping.py 수정 후 재실행하세요.</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-18</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="M5" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,990,875/4,778,926 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N5" s="4" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,990,875/4,778,926 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_CNT` 비영 1,990,875/4,778,926 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,884,683/42,791,677 (4.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,887,796/42,981,657 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,884,683/42,791,677 (4.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,887,796/42,981,657 (4.4%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 248,133/272,032 (91.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 249,697/274,105 (91.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 248,133/272,032 (91.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 249,697/274,105 (91.1%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 248,133/272,032 (91.2%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AD_COST` 비영 249,697/274,105 (91.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 190,712/272,032 (70.1%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 191,983/274,105 (70.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 50,927/272,032 (18.7%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_AD_PERFORMANCE.AGENCY_CONV_MEMBERS` 비영 50,621/274,105 (18.5%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,565행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_AD_CREATIVE` 9,657행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 213,528/272,032 (78.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.IMPRESSIONS` 비영 215,149/274,105 (78.5%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 190,712/272,032 (70.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.CLICKS` 비영 191,983/274,105 (70.0%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,850/272,032 (8.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_PERFORMANCE.INBOUND_CALL` 비영 22,726/274,105 (8.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_CAMPAIGN_MONTHLY.STOP_CNT` 비영 206,009/1,686,945 (12.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_CAMPAIGN_MONTHLY.STOP_CNT` 비영 206,708/1,687,032 (12.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 4,110,632/42,981,657 (9.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 비영 117,239/42,791,677 (0.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DECREASE_CNT` 비영 117,537/42,981,657 (0.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,884,683/42,791,677 (4.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.DEV_CNT` 비영 1,887,796/42,981,657 (4.4%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 37,993,241/42,791,677 (88.8%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.YEAR_START_ACTIVE_CNT` 비영 38,154,459/42,981,657 (88.8%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.MONTH_END_ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 40,386,853/42,791,677 (94.4%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PREV_MONTH_END_ACTIVE_CNT` 비영 40,573,727/42,981,657 (94.4%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,076,058/4,771,165 (22.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,077,840/4,778,926 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,076,058/4,771,165 (22.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,077,840/4,778,926 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,076,058/4,771,165 (22.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.STOP_CNT` 비영 1,077,840/4,778,926 (22.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="M65" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N65" s="4" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="M66" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N66" s="4" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="M67" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N67" s="4" t="inlineStr">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="M68" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N68" s="4" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="M69" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N69" s="4" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M70" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 37,557,143/42,791,677 (87.8%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.REGULAR_FEE` 비영 37,557,563/42,981,657 (87.4%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N70" s="4" t="inlineStr"/>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="M74" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N74" s="4" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="M75" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 39,845,615/42,791,677 (93.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.BILLED_AMT` 비영 40,037,011/42,981,657 (93.1%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N75" s="4" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="M80" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 4,110,632/42,981,657 (9.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N80" s="4" t="inlineStr">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="M81" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 4,110,632/42,981,657 (9.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N81" s="4" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="M82" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 4,110,632/42,981,657 (9.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N82" s="4" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="M83" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 3,920,784/42,791,677 (9.2%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.UNPAID_CNT` 비영 4,110,632/42,981,657 (9.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N83" s="4" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="M86" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,904행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,917행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N86" s="4" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="M89" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 44,406,102/44,406,102 (100.0%)</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 44,626,415/44,626,415 (100.0%)</t>
         </is>
       </c>
       <c r="N89" s="4" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="M90" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 26,019,188/44,406,102 (58.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 26,127,308/44,626,415 (58.5%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N90" s="4" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="M91" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 2,064,917/44,406,102 (4.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.FAIL_MEMBERS` 비영 2,070,335/44,626,415 (4.6%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N91" s="4" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="M95" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.D5_GIFT_PART_AMT` 비영 26,544/44,406,102 (0.1%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.D5_GIFT_PART_AMT` 비영 26,544/44,626,415 (0.1%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N95" s="4" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="M101" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 1,591,255/1,591,255 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SESSION_CNT` 비영 1,651,036/1,651,036 (100.0%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N101" s="4" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="M103" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 46,255행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 49,892행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N103" s="4" t="inlineStr">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="M104" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 46,255행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 49,892행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N104" s="4" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="M105" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 46,255행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_EVENT` 49,892행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N105" s="4" t="inlineStr">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="M106" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N106" s="4" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="M107" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 440행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 482행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N107" s="4" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="M108" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 440행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 482행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N108" s="4" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="M111" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 323,161/1,591,255 (20.3%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
+          <t>실측: `FACT_BIGQUERY_BEHAVIOR.SCROLL_DEPTH` 비영 339,375/1,651,036 (20.6%) · ⚠️ 채움률은 **적재된 샤드 내부** 기준이다 — GA4 전기간 미입고(G-5)</t>
         </is>
       </c>
       <c r="N111" s="4" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="M113" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 440행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_BIGQUERY_SOURCE` 482행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N113" s="4" t="inlineStr">
@@ -8724,7 +8724,7 @@
       </c>
       <c r="M114" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,801,193행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,803,896행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N114" s="4" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="M115" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,801,193행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,803,896행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N115" s="4" t="inlineStr">
@@ -8870,11 +8870,19 @@
       </c>
       <c r="M116" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,801,193행 실재 — 대응 물리 컬럼 미특정</t>
-        </is>
-      </c>
-      <c r="N116" s="4" t="inlineStr"/>
-      <c r="O116" s="4" t="inlineStr"/>
+          <t>추정: 배속 차원 `DIM_MEMBER_IDENTITY` 1,803,896행 실재 — 대응 물리 컬럼 미특정</t>
+        </is>
+      </c>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>SV_GA_SESSION.MEMBER_DK</t>
+        </is>
+      </c>
+      <c r="O116" s="4" t="inlineStr">
+        <is>
+          <t>AGENT_MARKETING</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -8939,7 +8947,7 @@
       </c>
       <c r="M117" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N117" s="4" t="inlineStr">
@@ -8996,7 +9004,7 @@
       </c>
       <c r="I118" s="4" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="J118" s="4" t="inlineStr">
@@ -9069,7 +9077,7 @@
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
@@ -9142,7 +9150,7 @@
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>CRM_ORG.DEPT_ID</t>
+          <t>CRM_ORG_CLEAN.DEPT_ID</t>
         </is>
       </c>
       <c r="J120" s="4" t="inlineStr">
@@ -9231,7 +9239,7 @@
       </c>
       <c r="M121" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N121" s="4" t="inlineStr">
@@ -9304,7 +9312,7 @@
       </c>
       <c r="M122" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N122" s="4" t="inlineStr">
@@ -9377,7 +9385,7 @@
       </c>
       <c r="M123" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N123" s="4" t="inlineStr">
@@ -9450,7 +9458,7 @@
       </c>
       <c r="M124" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N124" s="4" t="inlineStr">
@@ -10156,7 +10164,7 @@
       </c>
       <c r="M134" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N134" s="4" t="inlineStr">
@@ -10229,7 +10237,7 @@
       </c>
       <c r="M135" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N135" s="4" t="inlineStr">
@@ -10302,7 +10310,7 @@
       </c>
       <c r="M136" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_MEMBER` 1,801,192행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_MEMBER` 1,803,895행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N136" s="4" t="inlineStr">
@@ -10641,8 +10649,16 @@
           <t>DIM_DATE</t>
         </is>
       </c>
-      <c r="I141" s="4" t="inlineStr"/>
-      <c r="J141" s="4" t="inlineStr"/>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>CRM_HOLIDAY.HOLIDAY_DATE</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>TM_CM_SCHDUL_MNG</t>
+        </is>
+      </c>
       <c r="K141" s="4" t="inlineStr"/>
       <c r="L141" s="6" t="inlineStr">
         <is>
@@ -11309,7 +11325,7 @@
       </c>
       <c r="M151" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,300행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_CAMPAIGN` 37,346행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N151" s="4" t="inlineStr"/>
@@ -11374,7 +11390,7 @@
       </c>
       <c r="M152" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,990,875/4,778,926 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N152" s="4" t="inlineStr">
@@ -11447,7 +11463,7 @@
       </c>
       <c r="M153" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_CAMPAIGN_MONTHLY.DEV_CNT` 비영 76,210/1,686,945 (4.5%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_AD_INFLOW_ALLOC.DEV_CNT` 비영 1,290/1,426 (90.5%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N153" s="4" t="inlineStr">
@@ -11520,7 +11536,7 @@
       </c>
       <c r="M154" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 비영 1,859,125/42,791,677 (4.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_MEMBERS` 비영 1,862,172/42,981,657 (4.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N154" s="4" t="inlineStr">
@@ -11593,7 +11609,7 @@
       </c>
       <c r="M155" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 비영 1,859,125/42,791,677 (4.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.INCREASE_CNT` 비영 1,862,172/42,981,657 (4.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N155" s="4" t="inlineStr">
@@ -11645,12 +11661,12 @@
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
-          <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
+          <t>FTG-B.ANNUAL_GOAL_CNT</t>
         </is>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
+          <t>CRM_BIZ_TARGET.TARGET_CNT</t>
         </is>
       </c>
       <c r="J156" s="4" t="inlineStr">
@@ -11659,14 +11675,14 @@
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr"/>
-      <c r="L156" s="7" t="inlineStr">
-        <is>
-          <t>WAIT</t>
+      <c r="L156" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr">
         <is>
-          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
+          <t>실측: `FACT_TARGET_PROJECT.ANNUAL_GOAL_CNT` 비영 2,966/2,966 (100.0%)</t>
         </is>
       </c>
       <c r="N156" s="4" t="inlineStr">
@@ -11718,12 +11734,12 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
+          <t>FTG-B.SUPP_GOAL_CNT</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
+          <t>CRM_BIZ_TARGET.TARGET_CNT</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
@@ -11739,7 +11755,7 @@
       </c>
       <c r="M157" s="4" t="inlineStr">
         <is>
-          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
+          <t>실측: `FACT_TARGET_PROJECT.SUPP_GOAL_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
       <c r="N157" s="4" t="inlineStr"/>
@@ -11783,12 +11799,12 @@
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
-          <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
+          <t>FTG-B.ANNUAL_CUM_GOAL_CNT</t>
         </is>
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
+          <t>CRM_BIZ_TARGET.TARGET_CNT</t>
         </is>
       </c>
       <c r="J158" s="4" t="inlineStr">
@@ -11804,7 +11820,7 @@
       </c>
       <c r="M158" s="4" t="inlineStr">
         <is>
-          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
+          <t>실측: `FACT_TARGET_PROJECT.ANNUAL_CUM_GOAL_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
       <c r="N158" s="4" t="inlineStr">
@@ -11856,12 +11872,12 @@
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>FTG-B (measure — 컬럼 06_DDL.sql 확인)</t>
+          <t>FTG-B.SUPP_CUM_GOAL_CNT</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>CRM_BIZ_TARGET.MONTH_KEY</t>
+          <t>CRM_BIZ_TARGET.TARGET_CNT</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
@@ -11877,7 +11893,7 @@
       </c>
       <c r="M159" s="4" t="inlineStr">
         <is>
-          <t>추정: 원천 미입고(E-6 CRM 사업목표) — `FACT_TARGET_PROJECT` 0행</t>
+          <t>실측: `FACT_TARGET_PROJECT.SUPP_CUM_GOAL_CNT` 전건 0 — 설계O·값 미주입</t>
         </is>
       </c>
       <c r="N159" s="4" t="inlineStr"/>
@@ -11942,7 +11958,7 @@
       </c>
       <c r="M160" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 41,122,461/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_MEMBERS` 비영 41,310,673/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N160" s="4" t="inlineStr">
@@ -12015,7 +12031,7 @@
       </c>
       <c r="M161" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N161" s="4" t="inlineStr">
@@ -12161,7 +12177,7 @@
       </c>
       <c r="M163" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 비영 41,615,513/42,791,677 (97.3%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CUM_CNT` 비영 41,805,091/42,981,657 (97.3%)</t>
         </is>
       </c>
       <c r="N163" s="4" t="inlineStr">
@@ -12380,7 +12396,7 @@
       </c>
       <c r="M166" s="4" t="inlineStr">
         <is>
-          <t>추정: 배속 차원 `DIM_REASON` 5,904행 실재 — 대응 물리 컬럼 미특정</t>
+          <t>추정: 배속 차원 `DIM_REASON` 5,917행 실재 — 대응 물리 컬럼 미특정</t>
         </is>
       </c>
       <c r="N166" s="4" t="inlineStr">
@@ -12672,7 +12688,7 @@
       </c>
       <c r="M170" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,987,631/4,771,165 (41.7%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,990,875/4,778,926 (41.7%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N170" s="4" t="inlineStr">
@@ -13171,7 +13187,7 @@
       </c>
       <c r="M177" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N177" s="4" t="inlineStr">
@@ -13248,7 +13264,7 @@
       </c>
       <c r="M178" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N178" s="4" t="inlineStr">
@@ -13325,7 +13341,7 @@
       </c>
       <c r="M179" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N179" s="4" t="inlineStr">
@@ -13402,7 +13418,7 @@
       </c>
       <c r="M180" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,122,452/42,791,677 (96.1%)</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.ACTIVE_CNT` 비영 41,310,664/42,981,657 (96.1%)</t>
         </is>
       </c>
       <c r="N180" s="4" t="inlineStr">
@@ -13459,12 +13475,12 @@
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
@@ -13479,7 +13495,7 @@
       </c>
       <c r="M181" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N181" s="4" t="inlineStr">
@@ -13536,12 +13552,12 @@
       </c>
       <c r="I182" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J182" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K182" s="4" t="inlineStr">
@@ -13556,7 +13572,7 @@
       </c>
       <c r="M182" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N182" s="4" t="inlineStr">
@@ -13613,12 +13629,12 @@
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K183" s="4" t="inlineStr">
@@ -13633,7 +13649,7 @@
       </c>
       <c r="M183" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N183" s="4" t="inlineStr">
@@ -13690,12 +13706,12 @@
       </c>
       <c r="I184" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J184" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr">
@@ -13710,7 +13726,7 @@
       </c>
       <c r="M184" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N184" s="4" t="inlineStr">
@@ -13767,12 +13783,12 @@
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>CRM_MEMBER_DEV.DVLP_DIV_CD</t>
+          <t>CRM_CAMPAIGN;CRM_CODE;CRM_MEMBER;CRM_MEMBER_DEV;CRM_MEMBER_DISCONTINUE;CRM_MEMBER_SPONSOR_SPAN;CRM_PAYMENT_BILLING</t>
         </is>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
-          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT</t>
+          <t>TC_CMMN_DTL_CD;TC_MKTNG_DTL_CD;TM_CM_BRND_MNG;TM_CM_CMPGN_MNG;TM_MM_FDRM_MBER_DVLP_AMT;TM_MM_FDRM_MBER_INFO;TM_MM_FDRM_MBER_SPNSR;TM_MM_FDRM_MBER_SPNSR_BSNS;TM_MM_FDRM_MBER_SPNSR_DSCNTC;TM_MM_ONCE_MBER_INFO;TM_PM_DNTN_DTLS;TM_PM_MBRFEE_ACMSLT</t>
         </is>
       </c>
       <c r="K185" s="4" t="inlineStr">
@@ -13787,7 +13803,7 @@
       </c>
       <c r="M185" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,005,472/42,791,677 (2.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.STOP_CNT` 비영 1,007,090/42,981,657 (2.3%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N185" s="4" t="inlineStr">
@@ -13864,7 +13880,7 @@
       </c>
       <c r="M186" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,242,457/42,791,677 (2.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,244,416/42,981,657 (2.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N186" s="4" t="inlineStr">
@@ -13941,7 +13957,7 @@
       </c>
       <c r="M187" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,242,457/42,791,677 (2.9%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.CHURN_CNT` 비영 1,244,416/42,981,657 (2.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N187" s="4" t="inlineStr">
@@ -14018,7 +14034,7 @@
       </c>
       <c r="M188" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N188" s="4" t="inlineStr">
@@ -14095,7 +14111,7 @@
       </c>
       <c r="M189" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N189" s="4" t="inlineStr">
@@ -14172,7 +14188,7 @@
       </c>
       <c r="M190" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N190" s="4" t="inlineStr">
@@ -14249,7 +14265,7 @@
       </c>
       <c r="M191" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N191" s="4" t="inlineStr">
@@ -14326,7 +14342,7 @@
       </c>
       <c r="M192" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,217,931/42,791,677 (89.3%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MEMBER_MONTHLY.PAID_FEE` 비영 38,218,610/42,981,657 (88.9%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N192" s="4" t="inlineStr">
@@ -14634,7 +14650,7 @@
       </c>
       <c r="M196" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 44,406,102/44,406,102 (100.0%)</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SEND_MEMBERS` 비영 44,626,415/44,626,415 (100.0%)</t>
         </is>
       </c>
       <c r="N196" s="4" t="inlineStr">
@@ -14711,7 +14727,7 @@
       </c>
       <c r="M197" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 26,019,188/44,406,102 (58.6%) · 채움률 95% 미만</t>
+          <t>실측: `FACT_MESSAGE_DISPATCH.SUCCESS_MEMBERS` 비영 26,127,308/44,626,415 (58.5%) · 채움률 95% 미만</t>
         </is>
       </c>
       <c r="N197" s="4" t="inlineStr">
@@ -14857,7 +14873,7 @@
       </c>
       <c r="M199" s="4" t="inlineStr">
         <is>
-          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,987,631/4,771,165 (41.7%) · GA↔CRM identity 커버리지 종속</t>
+          <t>실측: `FACT_MEMBER_EVENT.DEV_MEMBERS` 비영 1,990,875/4,778,926 (41.7%) · GA↔CRM identity 커버리지 종속</t>
         </is>
       </c>
       <c r="N199" s="4" t="inlineStr">
@@ -16295,7 +16311,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-18</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-27</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19433,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-18</t>
+          <t>⚙️ 생성기: scripts/gen_metric_gold_mapping.py · 측정일 2026-10-27</t>
         </is>
       </c>
     </row>
